--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32262,10 +32262,10 @@
         <x:v>1116</x:v>
       </x:c>
       <x:c r="B1069" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1069" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1069" s="1">
         <x:v>0</x:v>
@@ -32274,10 +32274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1069" s="1">
-        <x:v>11600</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G1069" s="1">
-        <x:v>88880</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="1070" spans="1:7">
@@ -32285,10 +32285,10 @@
         <x:v>1116</x:v>
       </x:c>
       <x:c r="B1070" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1070" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D1070" s="1">
         <x:v>0</x:v>
@@ -32297,10 +32297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1070" s="1">
-        <x:v>5342</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G1070" s="1">
-        <x:v>5342</x:v>
+        <x:v>88880</x:v>
       </x:c>
     </x:row>
     <x:row r="1071" spans="1:7">
@@ -34447,10 +34447,10 @@
         <x:v>1210</x:v>
       </x:c>
       <x:c r="B1164" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1164" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1164" s="1">
         <x:v>0</x:v>
@@ -34459,10 +34459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1164" s="1">
-        <x:v>0</x:v>
+        <x:v>9550</x:v>
       </x:c>
       <x:c r="G1164" s="1">
-        <x:v>2500</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="1165" spans="1:7">
@@ -34470,10 +34470,10 @@
         <x:v>1210</x:v>
       </x:c>
       <x:c r="B1165" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C1165" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1165" s="1">
         <x:v>0</x:v>
@@ -34482,10 +34482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1165" s="1">
-        <x:v>9550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1165" s="1">
-        <x:v>9550</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1166" spans="1:7">
@@ -47442,10 +47442,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -47454,10 +47454,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>13486</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>13486</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -47465,10 +47465,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -47477,10 +47477,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>1000</x:v>
+        <x:v>13486</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>25000</x:v>
+        <x:v>13486</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -52295,7 +52295,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B1940" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1940" s="1">
         <x:v>0</x:v>
@@ -52307,10 +52307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1940" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1940" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1941" spans="1:7">
@@ -52318,7 +52318,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B1941" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1941" s="1">
         <x:v>0</x:v>
@@ -52330,10 +52330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1941" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1941" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1942" spans="1:7">
@@ -60460,7 +60460,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2295" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2295" s="1">
         <x:v>0</x:v>
@@ -60472,10 +60472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2295" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2295" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2296" spans="1:7">
@@ -60483,7 +60483,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2296" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2296" s="1">
         <x:v>0</x:v>
@@ -60495,10 +60495,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2296" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2296" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2297" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -9182,10 +9182,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>22800</x:v>
+        <x:v>23800</x:v>
       </x:c>
       <x:c r="G65" s="1">
-        <x:v>65300</x:v>
+        <x:v>66300</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
@@ -11091,10 +11091,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>7400</x:v>
+        <x:v>1933879</x:v>
       </x:c>
       <x:c r="G148" s="1">
-        <x:v>7400</x:v>
+        <x:v>1933879</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -11643,10 +11643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F172" s="1">
-        <x:v>13350</x:v>
+        <x:v>12350</x:v>
       </x:c>
       <x:c r="G172" s="1">
-        <x:v>140350</x:v>
+        <x:v>139350</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
@@ -12264,10 +12264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F199" s="1">
-        <x:v>0</x:v>
+        <x:v>12944</x:v>
       </x:c>
       <x:c r="G199" s="1">
-        <x:v>26500</x:v>
+        <x:v>39444</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
@@ -12287,10 +12287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>12944</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G200" s="1">
-        <x:v>39444</x:v>
+        <x:v>26500</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
@@ -14886,10 +14886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F313" s="1">
-        <x:v>478437</x:v>
+        <x:v>485187</x:v>
       </x:c>
       <x:c r="G313" s="1">
-        <x:v>483437</x:v>
+        <x:v>490187</x:v>
       </x:c>
     </x:row>
     <x:row r="314" spans="1:7">
@@ -18405,10 +18405,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F466" s="1">
-        <x:v>91223</x:v>
+        <x:v>86223</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>135223</x:v>
+        <x:v>130223</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -19578,10 +19578,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>56200</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>134290</x:v>
+        <x:v>112090</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -19601,10 +19601,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>10000</x:v>
+        <x:v>32200</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>90590</x:v>
+        <x:v>112790</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -23729,7 +23729,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C698" s="1">
         <x:v>0</x:v>
@@ -23741,10 +23741,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -23752,7 +23752,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>0</x:v>
@@ -23764,10 +23764,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -29514,10 +29514,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F949" s="1">
-        <x:v>1967012</x:v>
+        <x:v>40533</x:v>
       </x:c>
       <x:c r="G949" s="1">
-        <x:v>1967012</x:v>
+        <x:v>40533</x:v>
       </x:c>
     </x:row>
     <x:row r="950" spans="1:7">
@@ -36966,10 +36966,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1273" s="1">
-        <x:v>16801</x:v>
+        <x:v>26301</x:v>
       </x:c>
       <x:c r="G1273" s="1">
-        <x:v>71801</x:v>
+        <x:v>81301</x:v>
       </x:c>
     </x:row>
     <x:row r="1274" spans="1:7">
@@ -44303,10 +44303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1592" s="1">
-        <x:v>11150</x:v>
+        <x:v>16150</x:v>
       </x:c>
       <x:c r="G1592" s="1">
-        <x:v>21150</x:v>
+        <x:v>26150</x:v>
       </x:c>
     </x:row>
     <x:row r="1593" spans="1:7">
@@ -51065,10 +51065,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1886" s="1">
-        <x:v>159266</x:v>
+        <x:v>152516</x:v>
       </x:c>
       <x:c r="G1886" s="1">
-        <x:v>250266</x:v>
+        <x:v>243516</x:v>
       </x:c>
     </x:row>
     <x:row r="1887" spans="1:7">
@@ -51582,10 +51582,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1909" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1909" s="1">
-        <x:v>33500</x:v>
+        <x:v>68000</x:v>
       </x:c>
       <x:c r="D1909" s="1">
         <x:v>0</x:v>
@@ -51594,10 +51594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1909" s="1">
-        <x:v>0</x:v>
+        <x:v>59493</x:v>
       </x:c>
       <x:c r="G1909" s="1">
-        <x:v>33500</x:v>
+        <x:v>127493</x:v>
       </x:c>
     </x:row>
     <x:row r="1910" spans="1:7">
@@ -51605,10 +51605,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1910" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1910" s="1">
-        <x:v>68000</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1910" s="1">
         <x:v>0</x:v>
@@ -51617,10 +51617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1910" s="1">
-        <x:v>59493</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1910" s="1">
-        <x:v>127493</x:v>
+        <x:v>33500</x:v>
       </x:c>
     </x:row>
     <x:row r="1911" spans="1:7">
@@ -53917,10 +53917,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2010" s="1">
-        <x:v>41139</x:v>
+        <x:v>31639</x:v>
       </x:c>
       <x:c r="G2010" s="1">
-        <x:v>108139</x:v>
+        <x:v>98639</x:v>
       </x:c>
     </x:row>
     <x:row r="2011" spans="1:7">
@@ -58954,10 +58954,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2229" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2229" s="1">
-        <x:v>54200</x:v>
+        <x:v>49000</x:v>
       </x:c>
     </x:row>
     <x:row r="2230" spans="1:7">
@@ -59000,10 +59000,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2231" s="1">
-        <x:v>10400</x:v>
+        <x:v>15600</x:v>
       </x:c>
       <x:c r="G2231" s="1">
-        <x:v>47400</x:v>
+        <x:v>52600</x:v>
       </x:c>
     </x:row>
     <x:row r="2232" spans="1:7">
@@ -60460,7 +60460,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2295" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2295" s="1">
         <x:v>0</x:v>
@@ -60472,10 +60472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2295" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2295" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2296" spans="1:7">
@@ -60483,7 +60483,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2296" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2296" s="1">
         <x:v>0</x:v>
@@ -60495,10 +60495,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2296" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2296" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2297" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -1828,7 +1828,7 @@
     <x:t>DELANEY, APRIL MCCLAIN</x:t>
   </x:si>
   <x:si>
-    <x:t>DELANEY, JOHN K</x:t>
+    <x:t>DELANEY, JOHN K.</x:t>
   </x:si>
   <x:si>
     <x:t>DELAURO, ROSA L</x:t>
@@ -2251,7 +2251,7 @@
     <x:t>FIMIAN, KEITH S.</x:t>
   </x:si>
   <x:si>
-    <x:t>FINCHER, STEVE MR.</x:t>
+    <x:t>FINCHER, STEPHEN</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, LAURA</x:t>
@@ -10665,10 +10665,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10677,10 +10677,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -10688,10 +10688,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C131" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D131" s="1">
         <x:v>0</x:v>
@@ -10700,10 +10700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G131" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
@@ -12264,10 +12264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F199" s="1">
-        <x:v>12944</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G199" s="1">
-        <x:v>39444</x:v>
+        <x:v>26500</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
@@ -12287,10 +12287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F200" s="1">
-        <x:v>0</x:v>
+        <x:v>12944</x:v>
       </x:c>
       <x:c r="G200" s="1">
-        <x:v>26500</x:v>
+        <x:v>39444</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
@@ -20348,7 +20348,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C551" s="1">
         <x:v>0</x:v>
@@ -21268,10 +21268,10 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C591" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D591" s="1">
         <x:v>0</x:v>
@@ -21280,10 +21280,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F591" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G591" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:7">
@@ -21291,10 +21291,10 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C592" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D592" s="1">
         <x:v>0</x:v>
@@ -21303,10 +21303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F592" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -21510,10 +21510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>0</x:v>
+        <x:v>18475</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>30500</x:v>
+        <x:v>48975</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -21533,10 +21533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>18475</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>46475</x:v>
+        <x:v>28000</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -23729,7 +23729,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C698" s="1">
         <x:v>0</x:v>
@@ -23741,10 +23741,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -23752,7 +23752,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>0</x:v>
@@ -23764,10 +23764,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -28663,10 +28663,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F912" s="1">
-        <x:v>15434</x:v>
+        <x:v>24934</x:v>
       </x:c>
       <x:c r="G912" s="1">
-        <x:v>51934</x:v>
+        <x:v>61434</x:v>
       </x:c>
     </x:row>
     <x:row r="913" spans="1:7">
@@ -32262,10 +32262,10 @@
         <x:v>1116</x:v>
       </x:c>
       <x:c r="B1069" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1069" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D1069" s="1">
         <x:v>0</x:v>
@@ -32274,10 +32274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1069" s="1">
-        <x:v>5342</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G1069" s="1">
-        <x:v>5342</x:v>
+        <x:v>88880</x:v>
       </x:c>
     </x:row>
     <x:row r="1070" spans="1:7">
@@ -32285,10 +32285,10 @@
         <x:v>1116</x:v>
       </x:c>
       <x:c r="B1070" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1070" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1070" s="1">
         <x:v>0</x:v>
@@ -32297,10 +32297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1070" s="1">
-        <x:v>11600</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G1070" s="1">
-        <x:v>88880</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="1071" spans="1:7">
@@ -34447,10 +34447,10 @@
         <x:v>1210</x:v>
       </x:c>
       <x:c r="B1164" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C1164" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1164" s="1">
         <x:v>0</x:v>
@@ -34459,10 +34459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1164" s="1">
-        <x:v>9550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1164" s="1">
-        <x:v>9550</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1165" spans="1:7">
@@ -34470,10 +34470,10 @@
         <x:v>1210</x:v>
       </x:c>
       <x:c r="B1165" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1165" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1165" s="1">
         <x:v>0</x:v>
@@ -34482,10 +34482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1165" s="1">
-        <x:v>0</x:v>
+        <x:v>9550</x:v>
       </x:c>
       <x:c r="G1165" s="1">
-        <x:v>2500</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="1166" spans="1:7">
@@ -36966,10 +36966,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1273" s="1">
-        <x:v>26301</x:v>
+        <x:v>16801</x:v>
       </x:c>
       <x:c r="G1273" s="1">
-        <x:v>81301</x:v>
+        <x:v>71801</x:v>
       </x:c>
     </x:row>
     <x:row r="1274" spans="1:7">
@@ -38242,10 +38242,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1329" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1329" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1329" s="1">
         <x:v>0</x:v>
@@ -38254,10 +38254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1329" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1329" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1330" spans="1:7">
@@ -38265,10 +38265,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1330" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1330" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1330" s="1">
         <x:v>0</x:v>
@@ -38277,10 +38277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1330" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1330" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1331" spans="1:7">
@@ -42302,10 +42302,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1505" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1505" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="1506" spans="1:7">
@@ -42325,10 +42325,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1506" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1506" s="1">
-        <x:v>3000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1507" spans="1:7">
@@ -44119,10 +44119,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1584" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1584" s="1">
-        <x:v>54860</x:v>
+        <x:v>55360</x:v>
       </x:c>
     </x:row>
     <x:row r="1585" spans="1:7">
@@ -44142,10 +44142,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1585" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1585" s="1">
-        <x:v>55360</x:v>
+        <x:v>54860</x:v>
       </x:c>
     </x:row>
     <x:row r="1586" spans="1:7">
@@ -47442,10 +47442,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -47454,10 +47454,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>1000</x:v>
+        <x:v>13486</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>25000</x:v>
+        <x:v>13486</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -47465,10 +47465,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -47477,10 +47477,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>13486</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>13486</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -51582,10 +51582,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1909" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1909" s="1">
-        <x:v>68000</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1909" s="1">
         <x:v>0</x:v>
@@ -51594,10 +51594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1909" s="1">
-        <x:v>59493</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1909" s="1">
-        <x:v>127493</x:v>
+        <x:v>33500</x:v>
       </x:c>
     </x:row>
     <x:row r="1910" spans="1:7">
@@ -51605,10 +51605,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1910" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1910" s="1">
-        <x:v>33500</x:v>
+        <x:v>68000</x:v>
       </x:c>
       <x:c r="D1910" s="1">
         <x:v>0</x:v>
@@ -51617,10 +51617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1910" s="1">
-        <x:v>0</x:v>
+        <x:v>59493</x:v>
       </x:c>
       <x:c r="G1910" s="1">
-        <x:v>33500</x:v>
+        <x:v>127493</x:v>
       </x:c>
     </x:row>
     <x:row r="1911" spans="1:7">
@@ -57424,10 +57424,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57436,10 +57436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57447,10 +57447,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57459,10 +57459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -61898,10 +61898,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2357" s="1">
-        <x:v>2094</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2357" s="1">
-        <x:v>22344</x:v>
+        <x:v>20250</x:v>
       </x:c>
     </x:row>
     <x:row r="2358" spans="1:7">
@@ -61921,10 +61921,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2358" s="1">
-        <x:v>0</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="G2358" s="1">
-        <x:v>20250</x:v>
+        <x:v>22344</x:v>
       </x:c>
     </x:row>
     <x:row r="2359" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -1828,7 +1828,7 @@
     <x:t>DELANEY, APRIL MCCLAIN</x:t>
   </x:si>
   <x:si>
-    <x:t>DELANEY, JOHN K.</x:t>
+    <x:t>DELANEY, JOHN K</x:t>
   </x:si>
   <x:si>
     <x:t>DELAURO, ROSA L</x:t>
@@ -2251,7 +2251,7 @@
     <x:t>FIMIAN, KEITH S.</x:t>
   </x:si>
   <x:si>
-    <x:t>FINCHER, STEPHEN</x:t>
+    <x:t>FINCHER, STEVE MR.</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, LAURA</x:t>
@@ -10665,10 +10665,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10677,10 +10677,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -10688,10 +10688,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C131" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D131" s="1">
         <x:v>0</x:v>
@@ -10700,10 +10700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G131" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
@@ -20348,7 +20348,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C551" s="1">
         <x:v>0</x:v>
@@ -21268,10 +21268,10 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C591" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D591" s="1">
         <x:v>0</x:v>
@@ -21280,10 +21280,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F591" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G591" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:7">
@@ -21291,10 +21291,10 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C592" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D592" s="1">
         <x:v>0</x:v>
@@ -21303,10 +21303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F592" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -21510,10 +21510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>18475</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>48975</x:v>
+        <x:v>30500</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -21533,10 +21533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>0</x:v>
+        <x:v>18475</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>28000</x:v>
+        <x:v>46475</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -28663,10 +28663,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F912" s="1">
-        <x:v>24934</x:v>
+        <x:v>15434</x:v>
       </x:c>
       <x:c r="G912" s="1">
-        <x:v>61434</x:v>
+        <x:v>51934</x:v>
       </x:c>
     </x:row>
     <x:row r="913" spans="1:7">
@@ -36966,10 +36966,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1273" s="1">
-        <x:v>16801</x:v>
+        <x:v>26301</x:v>
       </x:c>
       <x:c r="G1273" s="1">
-        <x:v>71801</x:v>
+        <x:v>81301</x:v>
       </x:c>
     </x:row>
     <x:row r="1274" spans="1:7">
@@ -38242,10 +38242,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1329" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1329" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1329" s="1">
         <x:v>0</x:v>
@@ -38254,10 +38254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1329" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1329" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1330" spans="1:7">
@@ -38265,10 +38265,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1330" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1330" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1330" s="1">
         <x:v>0</x:v>
@@ -38277,10 +38277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1330" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1330" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1331" spans="1:7">
@@ -42302,10 +42302,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1505" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1505" s="1">
-        <x:v>3000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1506" spans="1:7">
@@ -42325,10 +42325,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1506" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1506" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="1507" spans="1:7">
@@ -44119,10 +44119,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1584" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1584" s="1">
-        <x:v>55360</x:v>
+        <x:v>54860</x:v>
       </x:c>
     </x:row>
     <x:row r="1585" spans="1:7">
@@ -44142,10 +44142,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1585" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1585" s="1">
-        <x:v>54860</x:v>
+        <x:v>55360</x:v>
       </x:c>
     </x:row>
     <x:row r="1586" spans="1:7">
@@ -52295,7 +52295,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B1940" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1940" s="1">
         <x:v>0</x:v>
@@ -52307,10 +52307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1940" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1940" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1941" spans="1:7">
@@ -52318,7 +52318,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B1941" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1941" s="1">
         <x:v>0</x:v>
@@ -52330,10 +52330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1941" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1941" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1942" spans="1:7">
@@ -57424,10 +57424,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57436,10 +57436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57447,10 +57447,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57459,10 +57459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -60460,7 +60460,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2295" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2295" s="1">
         <x:v>0</x:v>
@@ -60472,10 +60472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2295" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2295" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2296" spans="1:7">
@@ -60483,7 +60483,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2296" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2296" s="1">
         <x:v>0</x:v>
@@ -60495,10 +60495,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2296" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2296" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2297" spans="1:7">
@@ -61898,10 +61898,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2357" s="1">
-        <x:v>0</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="G2357" s="1">
-        <x:v>20250</x:v>
+        <x:v>22344</x:v>
       </x:c>
     </x:row>
     <x:row r="2358" spans="1:7">
@@ -61921,10 +61921,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2358" s="1">
-        <x:v>2094</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2358" s="1">
-        <x:v>22344</x:v>
+        <x:v>20250</x:v>
       </x:c>
     </x:row>
     <x:row r="2359" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -4531,7 +4531,7 @@
     <x:t>MCDERMOTT, JAMES JOSEPH</x:t>
   </x:si>
   <x:si>
-    <x:t>MCDERMOTT, THOMAS M. JR</x:t>
+    <x:t>MCDERMOTT, THOMAS</x:t>
   </x:si>
   <x:si>
     <x:t>MCDONALD RIVET, KRISTEN</x:t>
@@ -10665,10 +10665,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10677,10 +10677,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -10688,10 +10688,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C131" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D131" s="1">
         <x:v>0</x:v>
@@ -10700,10 +10700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G131" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
@@ -21510,10 +21510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>0</x:v>
+        <x:v>18475</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>30500</x:v>
+        <x:v>48975</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -21533,10 +21533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>18475</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>46475</x:v>
+        <x:v>28000</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -28226,10 +28226,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F893" s="1">
-        <x:v>13744</x:v>
+        <x:v>64744</x:v>
       </x:c>
       <x:c r="G893" s="1">
-        <x:v>13744</x:v>
+        <x:v>64744</x:v>
       </x:c>
     </x:row>
     <x:row r="894" spans="1:7">
@@ -29721,10 +29721,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F958" s="1">
-        <x:v>750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G958" s="1">
-        <x:v>2750</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="959" spans="1:7">
@@ -29744,10 +29744,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F959" s="1">
-        <x:v>0</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G959" s="1">
-        <x:v>2000</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="960" spans="1:7">
@@ -34183,10 +34183,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1152" s="1">
-        <x:v>4705</x:v>
+        <x:v>15705</x:v>
       </x:c>
       <x:c r="G1152" s="1">
-        <x:v>4705</x:v>
+        <x:v>15705</x:v>
       </x:c>
     </x:row>
     <x:row r="1153" spans="1:7">
@@ -38242,10 +38242,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1329" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1329" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1329" s="1">
         <x:v>0</x:v>
@@ -38254,10 +38254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1329" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1329" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1330" spans="1:7">
@@ -38265,10 +38265,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1330" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1330" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1330" s="1">
         <x:v>0</x:v>
@@ -38277,10 +38277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1330" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1330" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1331" spans="1:7">
@@ -38576,10 +38576,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1343" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1343" s="1">
-        <x:v>33750</x:v>
+        <x:v>32750</x:v>
       </x:c>
     </x:row>
     <x:row r="1344" spans="1:7">
@@ -38599,10 +38599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1344" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1344" s="1">
-        <x:v>32750</x:v>
+        <x:v>33750</x:v>
       </x:c>
     </x:row>
     <x:row r="1345" spans="1:7">
@@ -44441,10 +44441,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>750378</x:v>
+        <x:v>739378</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>879128</x:v>
+        <x:v>868128</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -47442,10 +47442,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -47454,10 +47454,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>13486</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>13486</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -47465,10 +47465,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -47477,10 +47477,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>1000</x:v>
+        <x:v>13486</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>25000</x:v>
+        <x:v>13486</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -51582,10 +51582,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1909" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1909" s="1">
-        <x:v>33500</x:v>
+        <x:v>68000</x:v>
       </x:c>
       <x:c r="D1909" s="1">
         <x:v>0</x:v>
@@ -51594,10 +51594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1909" s="1">
-        <x:v>0</x:v>
+        <x:v>59493</x:v>
       </x:c>
       <x:c r="G1909" s="1">
-        <x:v>33500</x:v>
+        <x:v>127493</x:v>
       </x:c>
     </x:row>
     <x:row r="1910" spans="1:7">
@@ -51605,10 +51605,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1910" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1910" s="1">
-        <x:v>68000</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1910" s="1">
         <x:v>0</x:v>
@@ -51617,10 +51617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1910" s="1">
-        <x:v>59493</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1910" s="1">
-        <x:v>127493</x:v>
+        <x:v>33500</x:v>
       </x:c>
     </x:row>
     <x:row r="1911" spans="1:7">
@@ -57160,10 +57160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2151" s="1">
-        <x:v>54001</x:v>
+        <x:v>3001</x:v>
       </x:c>
       <x:c r="G2151" s="1">
-        <x:v>54001</x:v>
+        <x:v>3001</x:v>
       </x:c>
     </x:row>
     <x:row r="2152" spans="1:7">
@@ -57424,10 +57424,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57436,10 +57436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57447,10 +57447,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57459,10 +57459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -38242,10 +38242,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1329" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1329" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1329" s="1">
         <x:v>0</x:v>
@@ -38254,10 +38254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1329" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1329" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1330" spans="1:7">
@@ -38265,10 +38265,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1330" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1330" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1330" s="1">
         <x:v>0</x:v>
@@ -38277,10 +38277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1330" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1330" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1331" spans="1:7">
@@ -47442,10 +47442,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -47454,10 +47454,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>1000</x:v>
+        <x:v>13486</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>25000</x:v>
+        <x:v>13486</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -47465,10 +47465,10 @@
         <x:v>1770</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -47477,10 +47477,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>13486</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>13486</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -51582,10 +51582,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1909" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1909" s="1">
-        <x:v>68000</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1909" s="1">
         <x:v>0</x:v>
@@ -51594,10 +51594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1909" s="1">
-        <x:v>59493</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1909" s="1">
-        <x:v>127493</x:v>
+        <x:v>33500</x:v>
       </x:c>
     </x:row>
     <x:row r="1910" spans="1:7">
@@ -51605,10 +51605,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1910" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1910" s="1">
-        <x:v>33500</x:v>
+        <x:v>68000</x:v>
       </x:c>
       <x:c r="D1910" s="1">
         <x:v>0</x:v>
@@ -51617,10 +51617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1910" s="1">
-        <x:v>0</x:v>
+        <x:v>59493</x:v>
       </x:c>
       <x:c r="G1910" s="1">
-        <x:v>33500</x:v>
+        <x:v>127493</x:v>
       </x:c>
     </x:row>
     <x:row r="1911" spans="1:7">
@@ -57424,10 +57424,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57436,10 +57436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57447,10 +57447,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57459,10 +57459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -4531,7 +4531,7 @@
     <x:t>MCDERMOTT, JAMES JOSEPH</x:t>
   </x:si>
   <x:si>
-    <x:t>MCDERMOTT, THOMAS</x:t>
+    <x:t>MCDERMOTT, THOMAS M. JR</x:t>
   </x:si>
   <x:si>
     <x:t>MCDONALD RIVET, KRISTEN</x:t>
@@ -9182,10 +9182,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>23800</x:v>
+        <x:v>22800</x:v>
       </x:c>
       <x:c r="G65" s="1">
-        <x:v>66300</x:v>
+        <x:v>65300</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
@@ -11091,10 +11091,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>1933879</x:v>
+        <x:v>7400</x:v>
       </x:c>
       <x:c r="G148" s="1">
-        <x:v>1933879</x:v>
+        <x:v>7400</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -11643,10 +11643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F172" s="1">
-        <x:v>12350</x:v>
+        <x:v>13350</x:v>
       </x:c>
       <x:c r="G172" s="1">
-        <x:v>139350</x:v>
+        <x:v>140350</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
@@ -14886,10 +14886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F313" s="1">
-        <x:v>485187</x:v>
+        <x:v>478437</x:v>
       </x:c>
       <x:c r="G313" s="1">
-        <x:v>490187</x:v>
+        <x:v>483437</x:v>
       </x:c>
     </x:row>
     <x:row r="314" spans="1:7">
@@ -18405,10 +18405,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F466" s="1">
-        <x:v>86223</x:v>
+        <x:v>91223</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>130223</x:v>
+        <x:v>135223</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -19578,10 +19578,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>34000</x:v>
+        <x:v>56200</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>112090</x:v>
+        <x:v>134290</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -19601,10 +19601,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>32200</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>112790</x:v>
+        <x:v>90590</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -21510,10 +21510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>18475</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>48975</x:v>
+        <x:v>30500</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -21533,10 +21533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>0</x:v>
+        <x:v>18475</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>28000</x:v>
+        <x:v>46475</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -28226,10 +28226,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F893" s="1">
-        <x:v>64744</x:v>
+        <x:v>13744</x:v>
       </x:c>
       <x:c r="G893" s="1">
-        <x:v>64744</x:v>
+        <x:v>13744</x:v>
       </x:c>
     </x:row>
     <x:row r="894" spans="1:7">
@@ -29514,10 +29514,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F949" s="1">
-        <x:v>40533</x:v>
+        <x:v>1967012</x:v>
       </x:c>
       <x:c r="G949" s="1">
-        <x:v>40533</x:v>
+        <x:v>1967012</x:v>
       </x:c>
     </x:row>
     <x:row r="950" spans="1:7">
@@ -29721,10 +29721,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F958" s="1">
-        <x:v>0</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G958" s="1">
-        <x:v>2000</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="959" spans="1:7">
@@ -29744,10 +29744,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F959" s="1">
-        <x:v>750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G959" s="1">
-        <x:v>2750</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="960" spans="1:7">
@@ -30652,7 +30652,7 @@
         <x:v>1047</x:v>
       </x:c>
       <x:c r="B999" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C999" s="1">
         <x:v>0</x:v>
@@ -30664,10 +30664,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F999" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G999" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="1000" spans="1:7">
@@ -30675,7 +30675,7 @@
         <x:v>1047</x:v>
       </x:c>
       <x:c r="B1000" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C1000" s="1">
         <x:v>0</x:v>
@@ -30687,10 +30687,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1000" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
       <x:c r="G1000" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
     </x:row>
     <x:row r="1001" spans="1:7">
@@ -34183,10 +34183,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1152" s="1">
-        <x:v>15705</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="G1152" s="1">
-        <x:v>15705</x:v>
+        <x:v>4705</x:v>
       </x:c>
     </x:row>
     <x:row r="1153" spans="1:7">
@@ -36966,10 +36966,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1273" s="1">
-        <x:v>26301</x:v>
+        <x:v>16801</x:v>
       </x:c>
       <x:c r="G1273" s="1">
-        <x:v>81301</x:v>
+        <x:v>71801</x:v>
       </x:c>
     </x:row>
     <x:row r="1274" spans="1:7">
@@ -38242,10 +38242,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1329" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1329" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1329" s="1">
         <x:v>0</x:v>
@@ -38254,10 +38254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1329" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1329" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1330" spans="1:7">
@@ -38265,10 +38265,10 @@
         <x:v>1373</x:v>
       </x:c>
       <x:c r="B1330" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1330" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1330" s="1">
         <x:v>0</x:v>
@@ -38277,10 +38277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1330" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1330" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1331" spans="1:7">
@@ -38576,10 +38576,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1343" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1343" s="1">
-        <x:v>32750</x:v>
+        <x:v>33750</x:v>
       </x:c>
     </x:row>
     <x:row r="1344" spans="1:7">
@@ -38599,10 +38599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1344" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1344" s="1">
-        <x:v>33750</x:v>
+        <x:v>32750</x:v>
       </x:c>
     </x:row>
     <x:row r="1345" spans="1:7">
@@ -44303,10 +44303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1592" s="1">
-        <x:v>16150</x:v>
+        <x:v>11150</x:v>
       </x:c>
       <x:c r="G1592" s="1">
-        <x:v>26150</x:v>
+        <x:v>21150</x:v>
       </x:c>
     </x:row>
     <x:row r="1593" spans="1:7">
@@ -44441,10 +44441,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>739378</x:v>
+        <x:v>750378</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>868128</x:v>
+        <x:v>879128</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -51065,10 +51065,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1886" s="1">
-        <x:v>152516</x:v>
+        <x:v>159266</x:v>
       </x:c>
       <x:c r="G1886" s="1">
-        <x:v>243516</x:v>
+        <x:v>250266</x:v>
       </x:c>
     </x:row>
     <x:row r="1887" spans="1:7">
@@ -51582,10 +51582,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1909" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1909" s="1">
-        <x:v>33500</x:v>
+        <x:v>68000</x:v>
       </x:c>
       <x:c r="D1909" s="1">
         <x:v>0</x:v>
@@ -51594,10 +51594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1909" s="1">
-        <x:v>0</x:v>
+        <x:v>59493</x:v>
       </x:c>
       <x:c r="G1909" s="1">
-        <x:v>33500</x:v>
+        <x:v>127493</x:v>
       </x:c>
     </x:row>
     <x:row r="1910" spans="1:7">
@@ -51605,10 +51605,10 @@
         <x:v>1949</x:v>
       </x:c>
       <x:c r="B1910" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1910" s="1">
-        <x:v>68000</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1910" s="1">
         <x:v>0</x:v>
@@ -51617,10 +51617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1910" s="1">
-        <x:v>59493</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1910" s="1">
-        <x:v>127493</x:v>
+        <x:v>33500</x:v>
       </x:c>
     </x:row>
     <x:row r="1911" spans="1:7">
@@ -52295,7 +52295,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B1940" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1940" s="1">
         <x:v>0</x:v>
@@ -52307,10 +52307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1940" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1940" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1941" spans="1:7">
@@ -52318,7 +52318,7 @@
         <x:v>1979</x:v>
       </x:c>
       <x:c r="B1941" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1941" s="1">
         <x:v>0</x:v>
@@ -52330,10 +52330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1941" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1941" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1942" spans="1:7">
@@ -53917,10 +53917,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2010" s="1">
-        <x:v>31639</x:v>
+        <x:v>41139</x:v>
       </x:c>
       <x:c r="G2010" s="1">
-        <x:v>98639</x:v>
+        <x:v>108139</x:v>
       </x:c>
     </x:row>
     <x:row r="2011" spans="1:7">
@@ -54262,10 +54262,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2025" s="1">
-        <x:v>1025</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="G2025" s="1">
-        <x:v>1025</x:v>
+        <x:v>1125</x:v>
       </x:c>
     </x:row>
     <x:row r="2026" spans="1:7">
@@ -57160,10 +57160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2151" s="1">
-        <x:v>3001</x:v>
+        <x:v>54001</x:v>
       </x:c>
       <x:c r="G2151" s="1">
-        <x:v>3001</x:v>
+        <x:v>54001</x:v>
       </x:c>
     </x:row>
     <x:row r="2152" spans="1:7">
@@ -57424,10 +57424,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57436,10 +57436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57447,10 +57447,10 @@
         <x:v>2201</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57459,10 +57459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -58954,10 +58954,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2229" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G2229" s="1">
-        <x:v>49000</x:v>
+        <x:v>54200</x:v>
       </x:c>
     </x:row>
     <x:row r="2230" spans="1:7">
@@ -59000,10 +59000,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2231" s="1">
-        <x:v>15600</x:v>
+        <x:v>10400</x:v>
       </x:c>
       <x:c r="G2231" s="1">
-        <x:v>52600</x:v>
+        <x:v>47400</x:v>
       </x:c>
     </x:row>
     <x:row r="2232" spans="1:7">
@@ -60460,7 +60460,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2295" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2295" s="1">
         <x:v>0</x:v>
@@ -60472,10 +60472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2295" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2295" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2296" spans="1:7">
@@ -60483,7 +60483,7 @@
         <x:v>2331</x:v>
       </x:c>
       <x:c r="B2296" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2296" s="1">
         <x:v>0</x:v>
@@ -60495,10 +60495,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2296" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2296" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2297" spans="1:7">
@@ -61484,10 +61484,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2339" s="1">
-        <x:v>1500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2339" s="1">
-        <x:v>1500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="2340" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10546,10 +10546,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C129" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D129" s="1">
         <x:v>0</x:v>
@@ -10558,10 +10558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G129" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
@@ -10569,10 +10569,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10581,10 +10581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -40515,10 +40515,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1432" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -40527,10 +40527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>70075</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>240715</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -40538,10 +40538,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1433" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1433" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1433" s="1">
         <x:v>0</x:v>
@@ -40550,10 +40550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1433" s="1">
-        <x:v>70075</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1433" s="1">
-        <x:v>240715</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1434" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10546,10 +10546,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C129" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D129" s="1">
         <x:v>0</x:v>
@@ -10558,10 +10558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G129" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
@@ -10569,10 +10569,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10581,10 +10581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -61974,10 +61974,10 @@
         <x:v>2386</x:v>
       </x:c>
       <x:c r="B2365" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2365" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2365" s="1">
         <x:v>0</x:v>
@@ -61986,10 +61986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2365" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2365" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2366" spans="1:7">
@@ -61997,10 +61997,10 @@
         <x:v>2386</x:v>
       </x:c>
       <x:c r="B2366" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C2366" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D2366" s="1">
         <x:v>0</x:v>
@@ -62009,10 +62009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2366" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2366" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="2367" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10546,10 +10546,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C129" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D129" s="1">
         <x:v>0</x:v>
@@ -10558,10 +10558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G129" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
@@ -10569,10 +10569,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10581,10 +10581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -50980,10 +50980,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -50992,10 +50992,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>11928</x:v>
+        <x:v>47565</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>46428</x:v>
+        <x:v>81065</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">
@@ -51003,10 +51003,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1888" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1888" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1888" s="1">
         <x:v>0</x:v>
@@ -51015,10 +51015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1888" s="1">
-        <x:v>47565</x:v>
+        <x:v>11928</x:v>
       </x:c>
       <x:c r="G1888" s="1">
-        <x:v>81065</x:v>
+        <x:v>46428</x:v>
       </x:c>
     </x:row>
     <x:row r="1889" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -37778,10 +37778,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1313" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1313" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1313" s="1">
         <x:v>0</x:v>
@@ -37790,10 +37790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1313" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1313" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1314" spans="1:7">
@@ -37801,10 +37801,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1314" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1314" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1314" s="1">
         <x:v>0</x:v>
@@ -37813,10 +37813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1314" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1314" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1315" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -46863,10 +46863,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1708" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1708" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1708" s="1">
         <x:v>0</x:v>
@@ -46875,10 +46875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1708" s="1">
-        <x:v>1000</x:v>
+        <x:v>13486</x:v>
       </x:c>
       <x:c r="G1708" s="1">
-        <x:v>25000</x:v>
+        <x:v>13486</x:v>
       </x:c>
     </x:row>
     <x:row r="1709" spans="1:7">
@@ -46886,10 +46886,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -46898,10 +46898,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>13486</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>13486</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -50980,10 +50980,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -50992,10 +50992,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>47565</x:v>
+        <x:v>11928</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>81065</x:v>
+        <x:v>46428</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">
@@ -51003,10 +51003,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1888" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1888" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1888" s="1">
         <x:v>0</x:v>
@@ -51015,10 +51015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1888" s="1">
-        <x:v>11928</x:v>
+        <x:v>47565</x:v>
       </x:c>
       <x:c r="G1888" s="1">
-        <x:v>46428</x:v>
+        <x:v>81065</x:v>
       </x:c>
     </x:row>
     <x:row r="1889" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -54545,10 +54545,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2042" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C2042" s="1">
-        <x:v>0</x:v>
+        <x:v>39000</x:v>
       </x:c>
       <x:c r="D2042" s="1">
         <x:v>0</x:v>
@@ -54557,10 +54557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2042" s="1">
-        <x:v>6750</x:v>
+        <x:v>18040</x:v>
       </x:c>
       <x:c r="G2042" s="1">
-        <x:v>6750</x:v>
+        <x:v>57040</x:v>
       </x:c>
     </x:row>
     <x:row r="2043" spans="1:7">
@@ -54568,10 +54568,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2043" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2043" s="1">
-        <x:v>39000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2043" s="1">
         <x:v>0</x:v>
@@ -54580,10 +54580,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2043" s="1">
-        <x:v>18040</x:v>
+        <x:v>6750</x:v>
       </x:c>
       <x:c r="G2043" s="1">
-        <x:v>57040</x:v>
+        <x:v>6750</x:v>
       </x:c>
     </x:row>
     <x:row r="2044" spans="1:7">
@@ -56914,10 +56914,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2145" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2145" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2145" s="1">
         <x:v>0</x:v>
@@ -56926,10 +56926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2145" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2145" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2146" spans="1:7">
@@ -56937,10 +56937,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2146" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2146" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2146" s="1">
         <x:v>0</x:v>
@@ -56949,10 +56949,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2146" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2146" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2147" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -31844,10 +31844,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -31856,10 +31856,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>11600</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>88880</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -31867,10 +31867,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -31879,10 +31879,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>5342</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>5342</x:v>
+        <x:v>88880</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -34029,10 +34029,10 @@
         <x:v>1196</x:v>
       </x:c>
       <x:c r="B1150" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1150" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1150" s="1">
         <x:v>0</x:v>
@@ -34041,10 +34041,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1150" s="1">
-        <x:v>0</x:v>
+        <x:v>9550</x:v>
       </x:c>
       <x:c r="G1150" s="1">
-        <x:v>2500</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="1151" spans="1:7">
@@ -34052,10 +34052,10 @@
         <x:v>1196</x:v>
       </x:c>
       <x:c r="B1151" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C1151" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1151" s="1">
         <x:v>0</x:v>
@@ -34064,10 +34064,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1151" s="1">
-        <x:v>9550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1151" s="1">
-        <x:v>9550</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1152" spans="1:7">
@@ -37778,10 +37778,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1313" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1313" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1313" s="1">
         <x:v>0</x:v>
@@ -37790,10 +37790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1313" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1313" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1314" spans="1:7">
@@ -37801,10 +37801,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1314" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1314" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1314" s="1">
         <x:v>0</x:v>
@@ -37813,10 +37813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1314" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1314" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1315" spans="1:7">
@@ -38537,10 +38537,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1346" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1346" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1346" s="1">
         <x:v>0</x:v>
@@ -38549,10 +38549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1346" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1346" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1347" spans="1:7">
@@ -38560,10 +38560,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1347" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1347" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1347" s="1">
         <x:v>0</x:v>
@@ -38572,10 +38572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1347" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1347" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1348" spans="1:7">
@@ -46863,10 +46863,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1708" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1708" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1708" s="1">
         <x:v>0</x:v>
@@ -46875,10 +46875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1708" s="1">
-        <x:v>13486</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1708" s="1">
-        <x:v>13486</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1709" spans="1:7">
@@ -46886,10 +46886,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -46898,10 +46898,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>1000</x:v>
+        <x:v>13486</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>25000</x:v>
+        <x:v>13486</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -50980,10 +50980,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -50992,10 +50992,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>11928</x:v>
+        <x:v>47565</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>46428</x:v>
+        <x:v>81065</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">
@@ -51003,10 +51003,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1888" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1888" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1888" s="1">
         <x:v>0</x:v>
@@ -51015,10 +51015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1888" s="1">
-        <x:v>47565</x:v>
+        <x:v>11928</x:v>
       </x:c>
       <x:c r="G1888" s="1">
-        <x:v>81065</x:v>
+        <x:v>46428</x:v>
       </x:c>
     </x:row>
     <x:row r="1889" spans="1:7">
@@ -52958,10 +52958,10 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B1973" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1973" s="1">
-        <x:v>86500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1973" s="1">
         <x:v>0</x:v>
@@ -52970,10 +52970,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1973" s="1">
-        <x:v>23019</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G1973" s="1">
-        <x:v>109519</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="1974" spans="1:7">
@@ -52981,10 +52981,10 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B1974" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C1974" s="1">
-        <x:v>0</x:v>
+        <x:v>86500</x:v>
       </x:c>
       <x:c r="D1974" s="1">
         <x:v>0</x:v>
@@ -52993,10 +52993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1974" s="1">
-        <x:v>3550</x:v>
+        <x:v>23019</x:v>
       </x:c>
       <x:c r="G1974" s="1">
-        <x:v>3550</x:v>
+        <x:v>109519</x:v>
       </x:c>
     </x:row>
     <x:row r="1975" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -54545,10 +54545,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2042" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2042" s="1">
-        <x:v>39000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2042" s="1">
         <x:v>0</x:v>
@@ -54557,10 +54557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2042" s="1">
-        <x:v>18040</x:v>
+        <x:v>6750</x:v>
       </x:c>
       <x:c r="G2042" s="1">
-        <x:v>57040</x:v>
+        <x:v>6750</x:v>
       </x:c>
     </x:row>
     <x:row r="2043" spans="1:7">
@@ -54568,10 +54568,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2043" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C2043" s="1">
-        <x:v>0</x:v>
+        <x:v>39000</x:v>
       </x:c>
       <x:c r="D2043" s="1">
         <x:v>0</x:v>
@@ -54580,10 +54580,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2043" s="1">
-        <x:v>6750</x:v>
+        <x:v>18040</x:v>
       </x:c>
       <x:c r="G2043" s="1">
-        <x:v>6750</x:v>
+        <x:v>57040</x:v>
       </x:c>
     </x:row>
     <x:row r="2044" spans="1:7">
@@ -56914,10 +56914,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2145" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2145" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2145" s="1">
         <x:v>0</x:v>
@@ -56926,10 +56926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2145" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2145" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2146" spans="1:7">
@@ -56937,10 +56937,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2146" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2146" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2146" s="1">
         <x:v>0</x:v>
@@ -56949,10 +56949,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2146" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2146" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2147" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -9845,10 +9845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>37300</x:v>
+        <x:v>44300</x:v>
       </x:c>
       <x:c r="G98" s="1">
-        <x:v>154300</x:v>
+        <x:v>161300</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -31844,10 +31844,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -31856,10 +31856,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>5342</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>5342</x:v>
+        <x:v>88880</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -31867,10 +31867,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -31879,10 +31879,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>11600</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>88880</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -34029,10 +34029,10 @@
         <x:v>1196</x:v>
       </x:c>
       <x:c r="B1150" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C1150" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1150" s="1">
         <x:v>0</x:v>
@@ -34041,10 +34041,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1150" s="1">
-        <x:v>9550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1150" s="1">
-        <x:v>9550</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1151" spans="1:7">
@@ -34052,10 +34052,10 @@
         <x:v>1196</x:v>
       </x:c>
       <x:c r="B1151" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1151" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1151" s="1">
         <x:v>0</x:v>
@@ -34064,10 +34064,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1151" s="1">
-        <x:v>0</x:v>
+        <x:v>9550</x:v>
       </x:c>
       <x:c r="G1151" s="1">
-        <x:v>2500</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="1152" spans="1:7">
@@ -37778,10 +37778,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1313" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1313" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1313" s="1">
         <x:v>0</x:v>
@@ -37790,10 +37790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1313" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1313" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1314" spans="1:7">
@@ -37801,10 +37801,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1314" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1314" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1314" s="1">
         <x:v>0</x:v>
@@ -37813,10 +37813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1314" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1314" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1315" spans="1:7">
@@ -38537,10 +38537,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1346" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1346" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1346" s="1">
         <x:v>0</x:v>
@@ -38549,10 +38549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1346" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1346" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1347" spans="1:7">
@@ -38560,10 +38560,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1347" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1347" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1347" s="1">
         <x:v>0</x:v>
@@ -38572,10 +38572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1347" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1347" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1348" spans="1:7">
@@ -39814,10 +39814,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1401" s="1">
-        <x:v>50</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G1401" s="1">
-        <x:v>17685</x:v>
+        <x:v>24285</x:v>
       </x:c>
     </x:row>
     <x:row r="1402" spans="1:7">
@@ -40515,10 +40515,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1432" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -40527,10 +40527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1432" s="1">
-        <x:v>70075</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>240715</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -40538,10 +40538,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1433" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1433" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1433" s="1">
         <x:v>0</x:v>
@@ -40550,10 +40550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1433" s="1">
-        <x:v>5000</x:v>
+        <x:v>70075</x:v>
       </x:c>
       <x:c r="G1433" s="1">
-        <x:v>5000</x:v>
+        <x:v>240715</x:v>
       </x:c>
     </x:row>
     <x:row r="1434" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -51383,10 +51383,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1904" s="1">
-        <x:v>3545</x:v>
+        <x:v>3605</x:v>
       </x:c>
       <x:c r="G1904" s="1">
-        <x:v>3545</x:v>
+        <x:v>3605</x:v>
       </x:c>
     </x:row>
     <x:row r="1905" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -52958,10 +52958,10 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B1973" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C1973" s="1">
-        <x:v>0</x:v>
+        <x:v>86500</x:v>
       </x:c>
       <x:c r="D1973" s="1">
         <x:v>0</x:v>
@@ -52970,10 +52970,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1973" s="1">
-        <x:v>3550</x:v>
+        <x:v>23019</x:v>
       </x:c>
       <x:c r="G1973" s="1">
-        <x:v>3550</x:v>
+        <x:v>109519</x:v>
       </x:c>
     </x:row>
     <x:row r="1974" spans="1:7">
@@ -52981,10 +52981,10 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B1974" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1974" s="1">
-        <x:v>86500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1974" s="1">
         <x:v>0</x:v>
@@ -52993,10 +52993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1974" s="1">
-        <x:v>23019</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G1974" s="1">
-        <x:v>109519</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="1975" spans="1:7">
@@ -54545,10 +54545,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2042" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C2042" s="1">
-        <x:v>0</x:v>
+        <x:v>39000</x:v>
       </x:c>
       <x:c r="D2042" s="1">
         <x:v>0</x:v>
@@ -54557,10 +54557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2042" s="1">
-        <x:v>6750</x:v>
+        <x:v>18040</x:v>
       </x:c>
       <x:c r="G2042" s="1">
-        <x:v>6750</x:v>
+        <x:v>57040</x:v>
       </x:c>
     </x:row>
     <x:row r="2043" spans="1:7">
@@ -54568,10 +54568,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2043" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2043" s="1">
-        <x:v>39000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2043" s="1">
         <x:v>0</x:v>
@@ -54580,10 +54580,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2043" s="1">
-        <x:v>18040</x:v>
+        <x:v>6750</x:v>
       </x:c>
       <x:c r="G2043" s="1">
-        <x:v>57040</x:v>
+        <x:v>6750</x:v>
       </x:c>
     </x:row>
     <x:row r="2044" spans="1:7">
@@ -56914,10 +56914,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2145" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2145" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2145" s="1">
         <x:v>0</x:v>
@@ -56926,10 +56926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2145" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2145" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2146" spans="1:7">
@@ -56937,10 +56937,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2146" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2146" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2146" s="1">
         <x:v>0</x:v>
@@ -56949,10 +56949,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2146" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2146" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2147" spans="1:7">
@@ -61974,10 +61974,10 @@
         <x:v>2386</x:v>
       </x:c>
       <x:c r="B2365" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C2365" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D2365" s="1">
         <x:v>0</x:v>
@@ -61986,10 +61986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2365" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2365" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="2366" spans="1:7">
@@ -61997,10 +61997,10 @@
         <x:v>2386</x:v>
       </x:c>
       <x:c r="B2366" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2366" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2366" s="1">
         <x:v>0</x:v>
@@ -62009,10 +62009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2366" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2366" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2367" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -37778,10 +37778,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1313" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1313" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1313" s="1">
         <x:v>0</x:v>
@@ -37790,10 +37790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1313" s="1">
-        <x:v>16750</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1313" s="1">
-        <x:v>16750</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1314" spans="1:7">
@@ -37801,10 +37801,10 @@
         <x:v>1357</x:v>
       </x:c>
       <x:c r="B1314" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1314" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1314" s="1">
         <x:v>0</x:v>
@@ -37813,10 +37813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1314" s="1">
-        <x:v>12750</x:v>
+        <x:v>16750</x:v>
       </x:c>
       <x:c r="G1314" s="1">
-        <x:v>25750</x:v>
+        <x:v>16750</x:v>
       </x:c>
     </x:row>
     <x:row r="1315" spans="1:7">
@@ -38537,10 +38537,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1346" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1346" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1346" s="1">
         <x:v>0</x:v>
@@ -38549,10 +38549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1346" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1346" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1347" spans="1:7">
@@ -38560,10 +38560,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1347" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1347" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1347" s="1">
         <x:v>0</x:v>
@@ -38572,10 +38572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1347" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1347" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1348" spans="1:7">
@@ -50980,10 +50980,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -50992,10 +50992,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>47565</x:v>
+        <x:v>11928</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>81065</x:v>
+        <x:v>46428</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">
@@ -51003,10 +51003,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1888" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1888" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1888" s="1">
         <x:v>0</x:v>
@@ -51015,10 +51015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1888" s="1">
-        <x:v>11928</x:v>
+        <x:v>47565</x:v>
       </x:c>
       <x:c r="G1888" s="1">
-        <x:v>46428</x:v>
+        <x:v>81065</x:v>
       </x:c>
     </x:row>
     <x:row r="1889" spans="1:7">
@@ -54545,10 +54545,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2042" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2042" s="1">
-        <x:v>39000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2042" s="1">
         <x:v>0</x:v>
@@ -54557,10 +54557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2042" s="1">
-        <x:v>18040</x:v>
+        <x:v>6750</x:v>
       </x:c>
       <x:c r="G2042" s="1">
-        <x:v>57040</x:v>
+        <x:v>6750</x:v>
       </x:c>
     </x:row>
     <x:row r="2043" spans="1:7">
@@ -54568,10 +54568,10 @@
         <x:v>2073</x:v>
       </x:c>
       <x:c r="B2043" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C2043" s="1">
-        <x:v>0</x:v>
+        <x:v>39000</x:v>
       </x:c>
       <x:c r="D2043" s="1">
         <x:v>0</x:v>
@@ -54580,10 +54580,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2043" s="1">
-        <x:v>6750</x:v>
+        <x:v>18040</x:v>
       </x:c>
       <x:c r="G2043" s="1">
-        <x:v>6750</x:v>
+        <x:v>57040</x:v>
       </x:c>
     </x:row>
     <x:row r="2044" spans="1:7">
@@ -56914,10 +56914,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2145" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2145" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2145" s="1">
         <x:v>0</x:v>
@@ -56926,10 +56926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2145" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2145" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2146" spans="1:7">
@@ -56937,10 +56937,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2146" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2146" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2146" s="1">
         <x:v>0</x:v>
@@ -56949,10 +56949,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2146" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2146" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2147" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30303,7 +30303,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B988" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C988" s="1">
         <x:v>0</x:v>
@@ -30315,10 +30315,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F988" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G988" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="989" spans="1:7">
@@ -30326,7 +30326,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B989" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C989" s="1">
         <x:v>0</x:v>
@@ -30338,10 +30338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F989" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
       <x:c r="G989" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
     </x:row>
     <x:row r="990" spans="1:7">
@@ -38537,10 +38537,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1346" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1346" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1346" s="1">
         <x:v>0</x:v>
@@ -38549,10 +38549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1346" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1346" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1347" spans="1:7">
@@ -38560,10 +38560,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1347" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1347" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1347" s="1">
         <x:v>0</x:v>
@@ -38572,10 +38572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1347" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1347" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1348" spans="1:7">
@@ -40515,10 +40515,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1432" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -40527,10 +40527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>70075</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>240715</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -40538,10 +40538,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1433" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1433" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1433" s="1">
         <x:v>0</x:v>
@@ -40550,10 +40550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1433" s="1">
-        <x:v>70075</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1433" s="1">
-        <x:v>240715</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1434" spans="1:7">
@@ -56914,10 +56914,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2145" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2145" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2145" s="1">
         <x:v>0</x:v>
@@ -56926,10 +56926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2145" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2145" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2146" spans="1:7">
@@ -56937,10 +56937,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2146" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2146" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2146" s="1">
         <x:v>0</x:v>
@@ -56949,10 +56949,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2146" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2146" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2147" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30303,7 +30303,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B988" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C988" s="1">
         <x:v>0</x:v>
@@ -30315,10 +30315,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F988" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
       <x:c r="G988" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
     </x:row>
     <x:row r="989" spans="1:7">
@@ -30326,7 +30326,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B989" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C989" s="1">
         <x:v>0</x:v>
@@ -30338,10 +30338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F989" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G989" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="990" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -56914,10 +56914,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2145" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2145" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2145" s="1">
         <x:v>0</x:v>
@@ -56926,10 +56926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2145" s="1">
-        <x:v>3800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2145" s="1">
-        <x:v>3800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2146" spans="1:7">
@@ -56937,10 +56937,10 @@
         <x:v>2173</x:v>
       </x:c>
       <x:c r="B2146" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2146" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2146" s="1">
         <x:v>0</x:v>
@@ -56949,10 +56949,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2146" s="1">
-        <x:v>0</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="G2146" s="1">
-        <x:v>2500</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="2147" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -40515,10 +40515,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1432" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -40527,10 +40527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1432" s="1">
-        <x:v>70075</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>240715</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -40538,10 +40538,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1433" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1433" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1433" s="1">
         <x:v>0</x:v>
@@ -40550,10 +40550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1433" s="1">
-        <x:v>5000</x:v>
+        <x:v>70075</x:v>
       </x:c>
       <x:c r="G1433" s="1">
-        <x:v>5000</x:v>
+        <x:v>240715</x:v>
       </x:c>
     </x:row>
     <x:row r="1434" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -46495,10 +46495,10 @@
         <x:v>1730</x:v>
       </x:c>
       <x:c r="B1692" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1692" s="1">
-        <x:v>0</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="D1692" s="1">
         <x:v>0</x:v>
@@ -46507,10 +46507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1692" s="1">
-        <x:v>802</x:v>
+        <x:v>18850</x:v>
       </x:c>
       <x:c r="G1692" s="1">
-        <x:v>802</x:v>
+        <x:v>60350</x:v>
       </x:c>
     </x:row>
     <x:row r="1693" spans="1:7">
@@ -46518,10 +46518,10 @@
         <x:v>1730</x:v>
       </x:c>
       <x:c r="B1693" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1693" s="1">
-        <x:v>41500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1693" s="1">
         <x:v>0</x:v>
@@ -46530,10 +46530,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1693" s="1">
-        <x:v>18850</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="G1693" s="1">
-        <x:v>60350</x:v>
+        <x:v>802</x:v>
       </x:c>
     </x:row>
     <x:row r="1694" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -54913,10 +54913,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2058" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C2058" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D2058" s="1">
         <x:v>0</x:v>
@@ -54925,10 +54925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2058" s="1">
-        <x:v>0</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G2058" s="1">
-        <x:v>7000</x:v>
+        <x:v>63000</x:v>
       </x:c>
     </x:row>
     <x:row r="2059" spans="1:7">
@@ -54936,10 +54936,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2059" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2059" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2059" s="1">
         <x:v>0</x:v>
@@ -54948,10 +54948,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2059" s="1">
-        <x:v>26500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2059" s="1">
-        <x:v>63000</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2060" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -40515,10 +40515,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1432" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -40527,10 +40527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>70075</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>240715</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -40538,10 +40538,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1433" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1433" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1433" s="1">
         <x:v>0</x:v>
@@ -40550,10 +40550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1433" s="1">
-        <x:v>70075</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1433" s="1">
-        <x:v>240715</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1434" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -46495,10 +46495,10 @@
         <x:v>1730</x:v>
       </x:c>
       <x:c r="B1692" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1692" s="1">
-        <x:v>41500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1692" s="1">
         <x:v>0</x:v>
@@ -46507,10 +46507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1692" s="1">
-        <x:v>18850</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="G1692" s="1">
-        <x:v>60350</x:v>
+        <x:v>802</x:v>
       </x:c>
     </x:row>
     <x:row r="1693" spans="1:7">
@@ -46518,10 +46518,10 @@
         <x:v>1730</x:v>
       </x:c>
       <x:c r="B1693" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1693" s="1">
-        <x:v>0</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="D1693" s="1">
         <x:v>0</x:v>
@@ -46530,10 +46530,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1693" s="1">
-        <x:v>802</x:v>
+        <x:v>18850</x:v>
       </x:c>
       <x:c r="G1693" s="1">
-        <x:v>802</x:v>
+        <x:v>60350</x:v>
       </x:c>
     </x:row>
     <x:row r="1694" spans="1:7">
@@ -55396,10 +55396,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2079" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2079" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2079" s="1">
         <x:v>0</x:v>
@@ -55408,10 +55408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2079" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2079" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="2080" spans="1:7">
@@ -55419,10 +55419,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2080" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2080" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2080" s="1">
         <x:v>0</x:v>
@@ -55431,10 +55431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2080" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2080" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2081" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -7706,10 +7706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>900</x:v>
+        <x:v>3900</x:v>
       </x:c>
       <x:c r="G5" s="1">
-        <x:v>900</x:v>
+        <x:v>3900</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -9454,10 +9454,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>73632</x:v>
+        <x:v>73782</x:v>
       </x:c>
       <x:c r="G81" s="1">
-        <x:v>135132</x:v>
+        <x:v>135282</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
@@ -29257,10 +29257,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F942" s="1">
-        <x:v>1850</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="G942" s="1">
-        <x:v>1850</x:v>
+        <x:v>1900</x:v>
       </x:c>
     </x:row>
     <x:row r="943" spans="1:7">
@@ -36226,10 +36226,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1245" s="1">
-        <x:v>5800</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G1245" s="1">
-        <x:v>113940</x:v>
+        <x:v>112440</x:v>
       </x:c>
     </x:row>
     <x:row r="1246" spans="1:7">
@@ -37008,10 +37008,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>8600</x:v>
+        <x:v>10600</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>17100</x:v>
+        <x:v>19100</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -51958,10 +51958,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1929" s="1">
-        <x:v>1278</x:v>
+        <x:v>1544</x:v>
       </x:c>
       <x:c r="G1929" s="1">
-        <x:v>1278</x:v>
+        <x:v>1544</x:v>
       </x:c>
     </x:row>
     <x:row r="1930" spans="1:7">
@@ -54913,10 +54913,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2058" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2058" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2058" s="1">
         <x:v>0</x:v>
@@ -54925,10 +54925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2058" s="1">
-        <x:v>26500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2058" s="1">
-        <x:v>63000</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2059" spans="1:7">
@@ -54936,10 +54936,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2059" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C2059" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D2059" s="1">
         <x:v>0</x:v>
@@ -54948,10 +54948,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2059" s="1">
-        <x:v>0</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G2059" s="1">
-        <x:v>7000</x:v>
+        <x:v>63000</x:v>
       </x:c>
     </x:row>
     <x:row r="2060" spans="1:7">
@@ -55396,10 +55396,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2079" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2079" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2079" s="1">
         <x:v>0</x:v>
@@ -55408,10 +55408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2079" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2079" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2080" spans="1:7">
@@ -55419,10 +55419,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2080" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2080" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2080" s="1">
         <x:v>0</x:v>
@@ -55431,10 +55431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2080" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2080" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="2081" spans="1:7">
@@ -55753,10 +55753,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2094" s="1">
-        <x:v>112993</x:v>
+        <x:v>116993</x:v>
       </x:c>
       <x:c r="G2094" s="1">
-        <x:v>173083</x:v>
+        <x:v>177083</x:v>
       </x:c>
     </x:row>
     <x:row r="2095" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -58122,10 +58122,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2197" s="1">
-        <x:v>250</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G2197" s="1">
-        <x:v>250</x:v>
+        <x:v>7250</x:v>
       </x:c>
     </x:row>
     <x:row r="2198" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">
@@ -61974,10 +61974,10 @@
         <x:v>2386</x:v>
       </x:c>
       <x:c r="B2365" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2365" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2365" s="1">
         <x:v>0</x:v>
@@ -61986,10 +61986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2365" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2365" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2366" spans="1:7">
@@ -61997,10 +61997,10 @@
         <x:v>2386</x:v>
       </x:c>
       <x:c r="B2366" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C2366" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D2366" s="1">
         <x:v>0</x:v>
@@ -62009,10 +62009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2366" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2366" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="2367" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10546,10 +10546,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C129" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D129" s="1">
         <x:v>0</x:v>
@@ -10558,10 +10558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G129" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
@@ -10569,10 +10569,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10581,10 +10581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -21034,10 +21034,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -21046,10 +21046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>11400</x:v>
+        <x:v>7950</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>11400</x:v>
+        <x:v>21050</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -21057,10 +21057,10 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -21069,10 +21069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>7950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>21050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -30303,7 +30303,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B988" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C988" s="1">
         <x:v>0</x:v>
@@ -30315,10 +30315,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F988" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G988" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="989" spans="1:7">
@@ -30326,7 +30326,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B989" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C989" s="1">
         <x:v>0</x:v>
@@ -30338,10 +30338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F989" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
       <x:c r="G989" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
     </x:row>
     <x:row r="990" spans="1:7">
@@ -31844,10 +31844,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -31856,10 +31856,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>11600</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>88880</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -31867,10 +31867,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -31879,10 +31879,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>5342</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>5342</x:v>
+        <x:v>88880</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -50589,7 +50589,7 @@
         <x:v>1906</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C1870" s="1">
         <x:v>0</x:v>
@@ -50601,10 +50601,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>16000</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>16000</x:v>
+        <x:v>11000</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -50612,7 +50612,7 @@
         <x:v>1906</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1871" s="1">
         <x:v>0</x:v>
@@ -50624,10 +50624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>11000</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>11000</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">
@@ -50980,10 +50980,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -50992,10 +50992,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>11928</x:v>
+        <x:v>47565</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>46428</x:v>
+        <x:v>81065</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">
@@ -51003,10 +51003,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1888" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1888" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1888" s="1">
         <x:v>0</x:v>
@@ -51015,10 +51015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1888" s="1">
-        <x:v>47565</x:v>
+        <x:v>11928</x:v>
       </x:c>
       <x:c r="G1888" s="1">
-        <x:v>81065</x:v>
+        <x:v>46428</x:v>
       </x:c>
     </x:row>
     <x:row r="1889" spans="1:7">
@@ -51693,7 +51693,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1918" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1918" s="1">
         <x:v>0</x:v>
@@ -51705,10 +51705,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
       <x:c r="G1918" s="1">
-        <x:v>4017</x:v>
+        <x:v>52039</x:v>
       </x:c>
     </x:row>
     <x:row r="1919" spans="1:7">
@@ -51716,7 +51716,7 @@
         <x:v>1952</x:v>
       </x:c>
       <x:c r="B1919" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C1919" s="1">
         <x:v>0</x:v>
@@ -51728,10 +51728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
       <x:c r="G1919" s="1">
-        <x:v>52039</x:v>
+        <x:v>4017</x:v>
       </x:c>
     </x:row>
     <x:row r="1920" spans="1:7">
@@ -54913,10 +54913,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2058" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C2058" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D2058" s="1">
         <x:v>0</x:v>
@@ -54925,10 +54925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2058" s="1">
-        <x:v>0</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G2058" s="1">
-        <x:v>7000</x:v>
+        <x:v>63000</x:v>
       </x:c>
     </x:row>
     <x:row r="2059" spans="1:7">
@@ -54936,10 +54936,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2059" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2059" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2059" s="1">
         <x:v>0</x:v>
@@ -54948,10 +54948,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2059" s="1">
-        <x:v>26500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2059" s="1">
-        <x:v>63000</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2060" spans="1:7">
@@ -55396,10 +55396,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2079" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2079" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2079" s="1">
         <x:v>0</x:v>
@@ -55408,10 +55408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2079" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2079" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="2080" spans="1:7">
@@ -55419,10 +55419,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2080" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2080" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2080" s="1">
         <x:v>0</x:v>
@@ -55431,10 +55431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2080" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2080" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2081" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30303,7 +30303,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B988" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C988" s="1">
         <x:v>0</x:v>
@@ -30315,10 +30315,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F988" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
       <x:c r="G988" s="1">
-        <x:v>600</x:v>
+        <x:v>86829</x:v>
       </x:c>
     </x:row>
     <x:row r="989" spans="1:7">
@@ -30326,7 +30326,7 @@
         <x:v>1036</x:v>
       </x:c>
       <x:c r="B989" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C989" s="1">
         <x:v>0</x:v>
@@ -30338,10 +30338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F989" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G989" s="1">
-        <x:v>86829</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="990" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -54913,10 +54913,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2058" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2058" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2058" s="1">
         <x:v>0</x:v>
@@ -54925,10 +54925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2058" s="1">
-        <x:v>26500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2058" s="1">
-        <x:v>63000</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2059" spans="1:7">
@@ -54936,10 +54936,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2059" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C2059" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D2059" s="1">
         <x:v>0</x:v>
@@ -54948,10 +54948,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2059" s="1">
-        <x:v>0</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G2059" s="1">
-        <x:v>7000</x:v>
+        <x:v>63000</x:v>
       </x:c>
     </x:row>
     <x:row r="2060" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -23472,7 +23472,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C691" s="1">
         <x:v>0</x:v>
@@ -23484,10 +23484,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -23495,7 +23495,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C692" s="1">
         <x:v>0</x:v>
@@ -23507,10 +23507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -25841,10 +25841,10 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C794" s="1">
-        <x:v>0</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="D794" s="1">
         <x:v>0</x:v>
@@ -25853,10 +25853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F794" s="1">
-        <x:v>6100</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G794" s="1">
-        <x:v>6100</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:7">
@@ -25864,10 +25864,10 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C795" s="1">
-        <x:v>19000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D795" s="1">
         <x:v>0</x:v>
@@ -25876,10 +25876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F795" s="1">
-        <x:v>1500</x:v>
+        <x:v>6100</x:v>
       </x:c>
       <x:c r="G795" s="1">
-        <x:v>20500</x:v>
+        <x:v>6100</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:7">
@@ -31844,10 +31844,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -31856,10 +31856,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>5342</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>5342</x:v>
+        <x:v>88880</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -31867,10 +31867,10 @@
         <x:v>1102</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -31879,10 +31879,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>11600</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>88880</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -40515,10 +40515,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1432" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -40527,10 +40527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1432" s="1">
-        <x:v>70075</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>240715</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -40538,10 +40538,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1433" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1433" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1433" s="1">
         <x:v>0</x:v>
@@ -40550,10 +40550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1433" s="1">
-        <x:v>5000</x:v>
+        <x:v>70075</x:v>
       </x:c>
       <x:c r="G1433" s="1">
-        <x:v>5000</x:v>
+        <x:v>240715</x:v>
       </x:c>
     </x:row>
     <x:row r="1434" spans="1:7">
@@ -44586,10 +44586,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1609" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1609" s="1">
         <x:v>0</x:v>
@@ -44598,10 +44598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1609" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1609" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1610" spans="1:7">
@@ -44609,10 +44609,10 @@
         <x:v>1648</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -44621,10 +44621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -50589,7 +50589,7 @@
         <x:v>1906</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1870" s="1">
         <x:v>0</x:v>
@@ -50601,10 +50601,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>11000</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>11000</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -50612,7 +50612,7 @@
         <x:v>1906</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C1871" s="1">
         <x:v>0</x:v>
@@ -50624,10 +50624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>16000</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>16000</x:v>
+        <x:v>11000</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">
@@ -50980,10 +50980,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -50992,10 +50992,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>47565</x:v>
+        <x:v>11928</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>81065</x:v>
+        <x:v>46428</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">
@@ -51003,10 +51003,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1888" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1888" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1888" s="1">
         <x:v>0</x:v>
@@ -51015,10 +51015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1888" s="1">
-        <x:v>11928</x:v>
+        <x:v>47565</x:v>
       </x:c>
       <x:c r="G1888" s="1">
-        <x:v>46428</x:v>
+        <x:v>81065</x:v>
       </x:c>
     </x:row>
     <x:row r="1889" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -54913,10 +54913,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2058" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C2058" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D2058" s="1">
         <x:v>0</x:v>
@@ -54925,10 +54925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2058" s="1">
-        <x:v>0</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G2058" s="1">
-        <x:v>7000</x:v>
+        <x:v>63000</x:v>
       </x:c>
     </x:row>
     <x:row r="2059" spans="1:7">
@@ -54936,10 +54936,10 @@
         <x:v>2088</x:v>
       </x:c>
       <x:c r="B2059" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C2059" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2059" s="1">
         <x:v>0</x:v>
@@ -54948,10 +54948,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2059" s="1">
-        <x:v>26500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2059" s="1">
-        <x:v>63000</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2060" spans="1:7">
@@ -55396,10 +55396,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2079" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2079" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D2079" s="1">
         <x:v>0</x:v>
@@ -55408,10 +55408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2079" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2079" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="2080" spans="1:7">
@@ -55419,10 +55419,10 @@
         <x:v>2108</x:v>
       </x:c>
       <x:c r="B2080" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2080" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2080" s="1">
         <x:v>0</x:v>
@@ -55431,10 +55431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2080" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2080" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="2081" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -57328,10 +57328,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2163" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D2163" s="1">
         <x:v>0</x:v>
@@ -57340,10 +57340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2163" s="1">
-        <x:v>0</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="G2163" s="1">
-        <x:v>7500</x:v>
+        <x:v>86330</x:v>
       </x:c>
     </x:row>
     <x:row r="2164" spans="1:7">
@@ -57351,10 +57351,10 @@
         <x:v>2189</x:v>
       </x:c>
       <x:c r="B2164" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C2164" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D2164" s="1">
         <x:v>0</x:v>
@@ -57363,10 +57363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2164" s="1">
-        <x:v>12050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2164" s="1">
-        <x:v>86330</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="2165" spans="1:7">
@@ -59329,10 +59329,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2250" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D2250" s="1">
         <x:v>0</x:v>
@@ -59341,10 +59341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2250" s="1">
-        <x:v>0</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="G2250" s="1">
-        <x:v>8500</x:v>
+        <x:v>22357</x:v>
       </x:c>
     </x:row>
     <x:row r="2251" spans="1:7">
@@ -59352,10 +59352,10 @@
         <x:v>2275</x:v>
       </x:c>
       <x:c r="B2251" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2251" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D2251" s="1">
         <x:v>0</x:v>
@@ -59364,10 +59364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2251" s="1">
-        <x:v>1857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2251" s="1">
-        <x:v>22357</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="2252" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10546,10 +10546,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C129" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D129" s="1">
         <x:v>0</x:v>
@@ -10558,10 +10558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>13450</x:v>
+        <x:v>89949</x:v>
       </x:c>
       <x:c r="G129" s="1">
-        <x:v>13450</x:v>
+        <x:v>145649</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
@@ -10569,10 +10569,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -10581,10 +10581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>89949</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>145649</x:v>
+        <x:v>13450</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -23472,7 +23472,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C691" s="1">
         <x:v>0</x:v>
@@ -23484,10 +23484,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -23495,7 +23495,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C692" s="1">
         <x:v>0</x:v>
@@ -23507,10 +23507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>3050</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -25841,10 +25841,10 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C794" s="1">
-        <x:v>19000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D794" s="1">
         <x:v>0</x:v>
@@ -25853,10 +25853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F794" s="1">
-        <x:v>1500</x:v>
+        <x:v>6100</x:v>
       </x:c>
       <x:c r="G794" s="1">
-        <x:v>20500</x:v>
+        <x:v>6100</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:7">
@@ -25864,10 +25864,10 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C795" s="1">
-        <x:v>0</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="D795" s="1">
         <x:v>0</x:v>
@@ -25876,10 +25876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F795" s="1">
-        <x:v>6100</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G795" s="1">
-        <x:v>6100</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:7">
@@ -57098,10 +57098,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2153" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C2153" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2153" s="1">
         <x:v>0</x:v>
@@ -57110,10 +57110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2153" s="1">
-        <x:v>52651</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2153" s="1">
-        <x:v>165291</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2154" spans="1:7">
@@ -57121,10 +57121,10 @@
         <x:v>2180</x:v>
       </x:c>
       <x:c r="B2154" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D2154" s="1">
         <x:v>0</x:v>
@@ -57133,10 +57133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2154" s="1">
-        <x:v>0</x:v>
+        <x:v>52651</x:v>
       </x:c>
       <x:c r="G2154" s="1">
-        <x:v>5000</x:v>
+        <x:v>165291</x:v>
       </x:c>
     </x:row>
     <x:row r="2155" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -40515,10 +40515,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1432" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -40527,10 +40527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>70075</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>5000</x:v>
+        <x:v>240715</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -40538,10 +40538,10 @@
         <x:v>1474</x:v>
       </x:c>
       <x:c r="B1433" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C1433" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1433" s="1">
         <x:v>0</x:v>
@@ -40550,10 +40550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1433" s="1">
-        <x:v>70075</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1433" s="1">
-        <x:v>240715</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1434" spans="1:7">
@@ -50980,10 +50980,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -50992,10 +50992,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>11928</x:v>
+        <x:v>47565</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>46428</x:v>
+        <x:v>81065</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">
@@ -51003,10 +51003,10 @@
         <x:v>1922</x:v>
       </x:c>
       <x:c r="B1888" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1888" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1888" s="1">
         <x:v>0</x:v>
@@ -51015,10 +51015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1888" s="1">
-        <x:v>47565</x:v>
+        <x:v>11928</x:v>
       </x:c>
       <x:c r="G1888" s="1">
-        <x:v>81065</x:v>
+        <x:v>46428</x:v>
       </x:c>
     </x:row>
     <x:row r="1889" spans="1:7">
@@ -53970,10 +53970,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2017" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2017" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D2017" s="1">
         <x:v>0</x:v>
@@ -53982,10 +53982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2017" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2017" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="2018" spans="1:7">
@@ -53993,10 +53993,10 @@
         <x:v>2049</x:v>
       </x:c>
       <x:c r="B2018" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D2018" s="1">
         <x:v>0</x:v>
@@ -54005,10 +54005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2018" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G2018" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="2019" spans="1:7">
@@ -59950,7 +59950,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2277" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2277" s="1">
         <x:v>0</x:v>
@@ -59962,10 +59962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
       <x:c r="G2277" s="1">
-        <x:v>11781</x:v>
+        <x:v>63417</x:v>
       </x:c>
     </x:row>
     <x:row r="2278" spans="1:7">
@@ -59973,7 +59973,7 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="B2278" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2278" s="1">
         <x:v>0</x:v>
@@ -59985,10 +59985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
       <x:c r="G2278" s="1">
-        <x:v>63417</x:v>
+        <x:v>11781</x:v>
       </x:c>
     </x:row>
     <x:row r="2279" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -29979,10 +29979,10 @@
         <x:v>1085</x:v>
       </x:c>
       <x:c r="B1039" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1039" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1039" s="1">
         <x:v>0</x:v>
@@ -29991,10 +29991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1039" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1039" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1040" spans="1:7">
@@ -30002,10 +30002,10 @@
         <x:v>1085</x:v>
       </x:c>
       <x:c r="B1040" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1040" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1040" s="1">
         <x:v>0</x:v>
@@ -30014,10 +30014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1040" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1040" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1041" spans="1:7">
@@ -30577,10 +30577,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1065" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1065" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1065" s="1">
         <x:v>0</x:v>
@@ -30589,10 +30589,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1065" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1065" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1066" spans="1:7">
@@ -30600,10 +30600,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1066" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1066" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1066" s="1">
         <x:v>0</x:v>
@@ -30612,10 +30612,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1066" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1066" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1067" spans="1:7">
@@ -32095,10 +32095,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1131" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1131" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1131" s="1">
         <x:v>0</x:v>
@@ -32107,10 +32107,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1131" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1131" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1132" spans="1:7">
@@ -32118,10 +32118,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32130,10 +32130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -35315,10 +35315,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1271" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1271" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1271" s="1">
         <x:v>0</x:v>
@@ -35327,10 +35327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1271" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1271" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1272" spans="1:7">
@@ -35338,10 +35338,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35350,10 +35350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -35752,7 +35752,7 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1290" s="1">
         <x:v>0</x:v>
@@ -35764,10 +35764,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35775,7 +35775,7 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1291" s="1">
         <x:v>0</x:v>
@@ -35787,10 +35787,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -36787,10 +36787,10 @@
         <x:v>1376</x:v>
       </x:c>
       <x:c r="B1335" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1335" s="1">
-        <x:v>0</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="D1335" s="1">
         <x:v>0</x:v>
@@ -36799,10 +36799,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1335" s="1">
-        <x:v>250</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="G1335" s="1">
-        <x:v>250</x:v>
+        <x:v>50600</x:v>
       </x:c>
     </x:row>
     <x:row r="1336" spans="1:7">
@@ -36810,10 +36810,10 @@
         <x:v>1376</x:v>
       </x:c>
       <x:c r="B1336" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1336" s="1">
-        <x:v>41500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1336" s="1">
         <x:v>0</x:v>
@@ -36822,10 +36822,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1336" s="1">
-        <x:v>9100</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G1336" s="1">
-        <x:v>50600</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="1337" spans="1:7">
@@ -40329,10 +40329,10 @@
         <x:v>1529</x:v>
       </x:c>
       <x:c r="B1489" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1489" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1489" s="1">
         <x:v>0</x:v>
@@ -40341,10 +40341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1489" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1489" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1490" spans="1:7">
@@ -40352,10 +40352,10 @@
         <x:v>1529</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40364,10 +40364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -43434,10 +43434,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1624" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1624" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1624" s="1">
         <x:v>0</x:v>
@@ -43446,10 +43446,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1624" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1624" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1625" spans="1:7">
@@ -43457,10 +43457,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1625" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1625" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1625" s="1">
         <x:v>0</x:v>
@@ -43469,10 +43469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1625" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1625" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1626" spans="1:7">
@@ -45113,10 +45113,10 @@
         <x:v>1731</x:v>
       </x:c>
       <x:c r="B1697" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1697" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1697" s="1">
         <x:v>0</x:v>
@@ -45125,10 +45125,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1697" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1697" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1698" spans="1:7">
@@ -45136,10 +45136,10 @@
         <x:v>1731</x:v>
       </x:c>
       <x:c r="B1698" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1698" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1698" s="1">
         <x:v>0</x:v>
@@ -45148,10 +45148,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1698" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1698" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1699" spans="1:7">
@@ -48908,10 +48908,10 @@
         <x:v>1891</x:v>
       </x:c>
       <x:c r="B1862" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1862" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1862" s="1">
         <x:v>0</x:v>
@@ -48920,10 +48920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1862" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1862" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1863" spans="1:7">
@@ -48931,10 +48931,10 @@
         <x:v>1891</x:v>
       </x:c>
       <x:c r="B1863" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1863" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1863" s="1">
         <x:v>0</x:v>
@@ -48943,10 +48943,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1863" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1863" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1864" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -18847,7 +18847,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>0</x:v>
@@ -18859,10 +18859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F555" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -18870,7 +18870,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>0</x:v>
@@ -18882,10 +18882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -30577,10 +30577,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1065" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1065" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1065" s="1">
         <x:v>0</x:v>
@@ -30589,10 +30589,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1065" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1065" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1066" spans="1:7">
@@ -30600,10 +30600,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1066" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1066" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1066" s="1">
         <x:v>0</x:v>
@@ -30612,10 +30612,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1066" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1066" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1067" spans="1:7">
@@ -35315,10 +35315,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1271" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1271" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1271" s="1">
         <x:v>0</x:v>
@@ -35327,10 +35327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1271" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1271" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1272" spans="1:7">
@@ -35338,10 +35338,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35350,10 +35350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -36787,10 +36787,10 @@
         <x:v>1376</x:v>
       </x:c>
       <x:c r="B1335" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1335" s="1">
-        <x:v>41500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1335" s="1">
         <x:v>0</x:v>
@@ -36799,10 +36799,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1335" s="1">
-        <x:v>9100</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G1335" s="1">
-        <x:v>50600</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="1336" spans="1:7">
@@ -36810,10 +36810,10 @@
         <x:v>1376</x:v>
       </x:c>
       <x:c r="B1336" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1336" s="1">
-        <x:v>0</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="D1336" s="1">
         <x:v>0</x:v>
@@ -36822,10 +36822,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1336" s="1">
-        <x:v>250</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="G1336" s="1">
-        <x:v>250</x:v>
+        <x:v>50600</x:v>
       </x:c>
     </x:row>
     <x:row r="1337" spans="1:7">
@@ -37109,10 +37109,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1349" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1349" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1349" s="1">
         <x:v>0</x:v>
@@ -37121,10 +37121,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1349" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1349" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1350" spans="1:7">
@@ -37132,10 +37132,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1350" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1350" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1350" s="1">
         <x:v>0</x:v>
@@ -37144,10 +37144,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1351" spans="1:7">
@@ -40329,10 +40329,10 @@
         <x:v>1529</x:v>
       </x:c>
       <x:c r="B1489" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1489" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1489" s="1">
         <x:v>0</x:v>
@@ -40341,10 +40341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1489" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1489" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1490" spans="1:7">
@@ -40352,10 +40352,10 @@
         <x:v>1529</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40364,10 +40364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -43434,10 +43434,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1624" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1624" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1624" s="1">
         <x:v>0</x:v>
@@ -43446,10 +43446,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1624" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1624" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1625" spans="1:7">
@@ -43457,10 +43457,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1625" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1625" s="1">
         <x:v>0</x:v>
@@ -43469,10 +43469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1625" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1626" spans="1:7">
@@ -45274,10 +45274,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1704" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45286,10 +45286,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1704" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -45297,10 +45297,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1705" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1705" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1705" s="1">
         <x:v>0</x:v>
@@ -45309,10 +45309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1705" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1705" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1706" spans="1:7">
@@ -48908,10 +48908,10 @@
         <x:v>1891</x:v>
       </x:c>
       <x:c r="B1862" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1862" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1862" s="1">
         <x:v>0</x:v>
@@ -48920,10 +48920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1862" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1862" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1863" spans="1:7">
@@ -48931,10 +48931,10 @@
         <x:v>1891</x:v>
       </x:c>
       <x:c r="B1863" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1863" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1863" s="1">
         <x:v>0</x:v>
@@ -48943,10 +48943,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1863" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1863" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1864" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -18847,7 +18847,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>0</x:v>
@@ -18859,10 +18859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F555" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -18870,7 +18870,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>0</x:v>
@@ -18882,10 +18882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -29979,10 +29979,10 @@
         <x:v>1085</x:v>
       </x:c>
       <x:c r="B1039" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1039" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1039" s="1">
         <x:v>0</x:v>
@@ -29991,10 +29991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1039" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1039" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1040" spans="1:7">
@@ -30002,10 +30002,10 @@
         <x:v>1085</x:v>
       </x:c>
       <x:c r="B1040" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1040" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1040" s="1">
         <x:v>0</x:v>
@@ -30014,10 +30014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1040" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1040" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1041" spans="1:7">
@@ -42652,10 +42652,10 @@
         <x:v>1627</x:v>
       </x:c>
       <x:c r="B1590" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1590" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1590" s="1">
         <x:v>0</x:v>
@@ -42664,10 +42664,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1590" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1590" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1591" spans="1:7">
@@ -42675,10 +42675,10 @@
         <x:v>1627</x:v>
       </x:c>
       <x:c r="B1591" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1591" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1591" s="1">
         <x:v>0</x:v>
@@ -42687,10 +42687,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1591" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1591" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1592" spans="1:7">
@@ -45113,10 +45113,10 @@
         <x:v>1731</x:v>
       </x:c>
       <x:c r="B1697" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1697" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1697" s="1">
         <x:v>0</x:v>
@@ -45125,10 +45125,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1697" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1697" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1698" spans="1:7">
@@ -45136,10 +45136,10 @@
         <x:v>1731</x:v>
       </x:c>
       <x:c r="B1698" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1698" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1698" s="1">
         <x:v>0</x:v>
@@ -45148,10 +45148,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1698" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1698" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1699" spans="1:7">
@@ -45458,10 +45458,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45470,10 +45470,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45481,10 +45481,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45493,10 +45493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -29979,10 +29979,10 @@
         <x:v>1085</x:v>
       </x:c>
       <x:c r="B1039" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1039" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1039" s="1">
         <x:v>0</x:v>
@@ -29991,10 +29991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1039" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1039" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1040" spans="1:7">
@@ -30002,10 +30002,10 @@
         <x:v>1085</x:v>
       </x:c>
       <x:c r="B1040" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1040" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1040" s="1">
         <x:v>0</x:v>
@@ -30014,10 +30014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1040" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1040" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1041" spans="1:7">
@@ -32095,10 +32095,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1131" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1131" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1131" s="1">
         <x:v>0</x:v>
@@ -32107,10 +32107,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1131" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1131" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1132" spans="1:7">
@@ -32118,10 +32118,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32130,10 +32130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -35315,10 +35315,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1271" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1271" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1271" s="1">
         <x:v>0</x:v>
@@ -35327,10 +35327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1271" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1271" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1272" spans="1:7">
@@ -35338,10 +35338,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35350,10 +35350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -35752,7 +35752,7 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1290" s="1">
         <x:v>0</x:v>
@@ -35764,10 +35764,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35775,7 +35775,7 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1291" s="1">
         <x:v>0</x:v>
@@ -35787,10 +35787,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -37109,10 +37109,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1349" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1349" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1349" s="1">
         <x:v>0</x:v>
@@ -37121,10 +37121,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1349" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1349" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1350" spans="1:7">
@@ -37132,10 +37132,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1350" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1350" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1350" s="1">
         <x:v>0</x:v>
@@ -37144,10 +37144,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1350" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1350" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1351" spans="1:7">
@@ -45113,10 +45113,10 @@
         <x:v>1731</x:v>
       </x:c>
       <x:c r="B1697" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1697" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1697" s="1">
         <x:v>0</x:v>
@@ -45125,10 +45125,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1697" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1697" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1698" spans="1:7">
@@ -45136,10 +45136,10 @@
         <x:v>1731</x:v>
       </x:c>
       <x:c r="B1698" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1698" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1698" s="1">
         <x:v>0</x:v>
@@ -45148,10 +45148,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1698" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1698" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1699" spans="1:7">
@@ -45458,10 +45458,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45470,10 +45470,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45481,10 +45481,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45493,10 +45493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21722,10 +21722,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -21734,10 +21734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -21745,10 +21745,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -21757,10 +21757,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -32095,10 +32095,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1131" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1131" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1131" s="1">
         <x:v>0</x:v>
@@ -32107,10 +32107,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1131" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1131" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1132" spans="1:7">
@@ -32118,10 +32118,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32130,10 +32130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -35315,10 +35315,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1271" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1271" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1271" s="1">
         <x:v>0</x:v>
@@ -35327,10 +35327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1271" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1271" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1272" spans="1:7">
@@ -35338,10 +35338,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35350,10 +35350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -35752,7 +35752,7 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1290" s="1">
         <x:v>0</x:v>
@@ -35764,10 +35764,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35775,7 +35775,7 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1291" s="1">
         <x:v>0</x:v>
@@ -35787,10 +35787,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -45274,10 +45274,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1704" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45286,10 +45286,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1704" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -45297,10 +45297,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1705" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1705" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1705" s="1">
         <x:v>0</x:v>
@@ -45309,10 +45309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1705" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1705" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1706" spans="1:7">
@@ -45458,10 +45458,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45470,10 +45470,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45481,10 +45481,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45493,10 +45493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -48908,10 +48908,10 @@
         <x:v>1891</x:v>
       </x:c>
       <x:c r="B1862" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1862" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1862" s="1">
         <x:v>0</x:v>
@@ -48920,10 +48920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1862" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1862" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1863" spans="1:7">
@@ -48931,10 +48931,10 @@
         <x:v>1891</x:v>
       </x:c>
       <x:c r="B1863" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1863" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1863" s="1">
         <x:v>0</x:v>
@@ -48943,10 +48943,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1863" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1863" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1864" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -19997,10 +19997,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -20009,10 +20009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -20020,10 +20020,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -20032,10 +20032,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -30577,10 +30577,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1065" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1065" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1065" s="1">
         <x:v>0</x:v>
@@ -30589,10 +30589,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1065" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1065" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1066" spans="1:7">
@@ -30600,10 +30600,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1066" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1066" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1066" s="1">
         <x:v>0</x:v>
@@ -30612,10 +30612,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1066" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1066" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1067" spans="1:7">
@@ -45274,10 +45274,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1704" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45286,10 +45286,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1704" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -45297,10 +45297,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1705" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1705" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1705" s="1">
         <x:v>0</x:v>
@@ -45309,10 +45309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1705" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1705" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1706" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16846,10 +16846,10 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D468" s="1">
         <x:v>0</x:v>
@@ -16858,10 +16858,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F468" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -16869,10 +16869,10 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16881,10 +16881,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -19997,10 +19997,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -20009,10 +20009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -20020,10 +20020,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -20032,10 +20032,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -21722,10 +21722,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -21734,10 +21734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -21745,10 +21745,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -21757,10 +21757,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -30577,10 +30577,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1065" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1065" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1065" s="1">
         <x:v>0</x:v>
@@ -30589,10 +30589,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1065" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1065" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1066" spans="1:7">
@@ -30600,10 +30600,10 @@
         <x:v>1110</x:v>
       </x:c>
       <x:c r="B1066" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1066" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1066" s="1">
         <x:v>0</x:v>
@@ -30612,10 +30612,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1066" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1066" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1067" spans="1:7">
@@ -32095,10 +32095,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1131" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1131" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1131" s="1">
         <x:v>0</x:v>
@@ -32107,10 +32107,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1131" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1131" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1132" spans="1:7">
@@ -32118,10 +32118,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32130,10 +32130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -35315,10 +35315,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1271" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1271" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1271" s="1">
         <x:v>0</x:v>
@@ -35327,10 +35327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1271" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1271" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1272" spans="1:7">
@@ -35338,10 +35338,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35350,10 +35350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -37109,10 +37109,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1349" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1349" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1349" s="1">
         <x:v>0</x:v>
@@ -37121,10 +37121,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1349" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1349" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1350" spans="1:7">
@@ -37132,10 +37132,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1350" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1350" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1350" s="1">
         <x:v>0</x:v>
@@ -37144,10 +37144,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1351" spans="1:7">
@@ -42652,10 +42652,10 @@
         <x:v>1627</x:v>
       </x:c>
       <x:c r="B1590" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1590" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1590" s="1">
         <x:v>0</x:v>
@@ -42664,10 +42664,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1590" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1590" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1591" spans="1:7">
@@ -42675,10 +42675,10 @@
         <x:v>1627</x:v>
       </x:c>
       <x:c r="B1591" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1591" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1591" s="1">
         <x:v>0</x:v>
@@ -42687,10 +42687,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1591" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1591" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1592" spans="1:7">
@@ -43434,10 +43434,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1624" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1624" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1624" s="1">
         <x:v>0</x:v>
@@ -43446,10 +43446,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1624" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1624" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1625" spans="1:7">
@@ -43457,10 +43457,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1625" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1625" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1625" s="1">
         <x:v>0</x:v>
@@ -43469,10 +43469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1625" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1625" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1626" spans="1:7">
@@ -45458,10 +45458,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45470,10 +45470,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45481,10 +45481,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45493,10 +45493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -46861,10 +46861,10 @@
         <x:v>1804</x:v>
       </x:c>
       <x:c r="B1773" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1773" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1773" s="1">
         <x:v>0</x:v>
@@ -46876,7 +46876,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1773" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1774" spans="1:7">
@@ -46884,10 +46884,10 @@
         <x:v>1804</x:v>
       </x:c>
       <x:c r="B1774" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1774" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1774" s="1">
         <x:v>0</x:v>
@@ -46899,7 +46899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1774" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1775" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16846,10 +16846,10 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D468" s="1">
         <x:v>0</x:v>
@@ -16858,10 +16858,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F468" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -16869,10 +16869,10 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16881,10 +16881,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -21722,10 +21722,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -21734,10 +21734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -21745,10 +21745,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -21757,10 +21757,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -32095,10 +32095,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1131" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1131" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1131" s="1">
         <x:v>0</x:v>
@@ -32107,10 +32107,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1131" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1131" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1132" spans="1:7">
@@ -32118,10 +32118,10 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32130,10 +32130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -35315,10 +35315,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1271" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C1271" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1271" s="1">
         <x:v>0</x:v>
@@ -35327,10 +35327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1271" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1271" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1272" spans="1:7">
@@ -35338,10 +35338,10 @@
         <x:v>1313</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>469</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35350,10 +35350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -37109,10 +37109,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1349" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1349" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1349" s="1">
         <x:v>0</x:v>
@@ -37121,10 +37121,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1349" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1349" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1350" spans="1:7">
@@ -37132,10 +37132,10 @@
         <x:v>1389</x:v>
       </x:c>
       <x:c r="B1350" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1350" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1350" s="1">
         <x:v>0</x:v>
@@ -37144,10 +37144,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1350" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1350" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1351" spans="1:7">
@@ -40329,10 +40329,10 @@
         <x:v>1529</x:v>
       </x:c>
       <x:c r="B1489" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1489" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1489" s="1">
         <x:v>0</x:v>
@@ -40341,10 +40341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1489" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1489" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1490" spans="1:7">
@@ -40352,10 +40352,10 @@
         <x:v>1529</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40364,10 +40364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -43434,10 +43434,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1624" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1624" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1624" s="1">
         <x:v>0</x:v>
@@ -43446,10 +43446,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1624" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1624" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1625" spans="1:7">
@@ -43457,10 +43457,10 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="B1625" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1625" s="1">
         <x:v>0</x:v>
@@ -43469,10 +43469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1625" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1626" spans="1:7">
@@ -45458,10 +45458,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45470,10 +45470,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45481,10 +45481,10 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45493,10 +45493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -46861,10 +46861,10 @@
         <x:v>1804</x:v>
       </x:c>
       <x:c r="B1773" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1773" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1773" s="1">
         <x:v>0</x:v>
@@ -46876,7 +46876,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1773" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1774" spans="1:7">
@@ -46884,10 +46884,10 @@
         <x:v>1804</x:v>
       </x:c>
       <x:c r="B1774" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1774" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1774" s="1">
         <x:v>0</x:v>
@@ -46899,7 +46899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1774" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1775" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30008,10 +30008,10 @@
         <x:v>1086</x:v>
       </x:c>
       <x:c r="B1040" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1040" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1040" s="1">
         <x:v>0</x:v>
@@ -30020,10 +30020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1040" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1040" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1041" spans="1:7">
@@ -30031,10 +30031,10 @@
         <x:v>1086</x:v>
       </x:c>
       <x:c r="B1041" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1041" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1041" s="1">
         <x:v>0</x:v>
@@ -30043,10 +30043,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1041" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1041" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1042" spans="1:7">
@@ -35344,10 +35344,10 @@
         <x:v>1314</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35356,10 +35356,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -35367,10 +35367,10 @@
         <x:v>1314</x:v>
       </x:c>
       <x:c r="B1273" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1273" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1273" s="1">
         <x:v>0</x:v>
@@ -35379,10 +35379,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1273" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1273" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1274" spans="1:7">
@@ -35781,7 +35781,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1291" s="1">
         <x:v>0</x:v>
@@ -35793,10 +35793,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35804,7 +35804,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1292" s="1">
         <x:v>0</x:v>
@@ -35816,10 +35816,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37138,10 +37138,10 @@
         <x:v>1390</x:v>
       </x:c>
       <x:c r="B1350" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1350" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1350" s="1">
         <x:v>0</x:v>
@@ -37150,10 +37150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1351" spans="1:7">
@@ -37161,10 +37161,10 @@
         <x:v>1390</x:v>
       </x:c>
       <x:c r="B1351" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1351" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1351" s="1">
         <x:v>0</x:v>
@@ -37173,10 +37173,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1351" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1351" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1352" spans="1:7">
@@ -40358,10 +40358,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40370,10 +40370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -40381,10 +40381,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1491" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1491" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1491" s="1">
         <x:v>0</x:v>
@@ -40393,10 +40393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1491" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1491" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1492" spans="1:7">
@@ -45165,10 +45165,10 @@
         <x:v>1733</x:v>
       </x:c>
       <x:c r="B1699" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1699" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1699" s="1">
         <x:v>0</x:v>
@@ -45177,10 +45177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1699" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1699" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1700" spans="1:7">
@@ -45188,10 +45188,10 @@
         <x:v>1733</x:v>
       </x:c>
       <x:c r="B1700" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1700" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1700" s="1">
         <x:v>0</x:v>
@@ -45200,10 +45200,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1700" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1700" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1701" spans="1:7">
@@ -45326,10 +45326,10 @@
         <x:v>1739</x:v>
       </x:c>
       <x:c r="B1706" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1706" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1706" s="1">
         <x:v>0</x:v>
@@ -45338,10 +45338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1706" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1706" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1707" spans="1:7">
@@ -45349,10 +45349,10 @@
         <x:v>1739</x:v>
       </x:c>
       <x:c r="B1707" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1707" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1707" s="1">
         <x:v>0</x:v>
@@ -45361,10 +45361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1707" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1707" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1708" spans="1:7">
@@ -46913,10 +46913,10 @@
         <x:v>1806</x:v>
       </x:c>
       <x:c r="B1775" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1775" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1775" s="1">
         <x:v>0</x:v>
@@ -46928,7 +46928,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1775" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1776" spans="1:7">
@@ -46936,10 +46936,10 @@
         <x:v>1806</x:v>
       </x:c>
       <x:c r="B1776" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1776" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1776" s="1">
         <x:v>0</x:v>
@@ -46951,7 +46951,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1776" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1777" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32124,10 +32124,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32136,10 +32136,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -32147,10 +32147,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1133" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1133" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1133" s="1">
         <x:v>0</x:v>
@@ -32159,10 +32159,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1133" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1133" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1134" spans="1:7">
@@ -35344,10 +35344,10 @@
         <x:v>1314</x:v>
       </x:c>
       <x:c r="B1272" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1272" s="1">
         <x:v>0</x:v>
@@ -35356,10 +35356,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1272" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1272" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1273" spans="1:7">
@@ -35367,10 +35367,10 @@
         <x:v>1314</x:v>
       </x:c>
       <x:c r="B1273" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1273" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1273" s="1">
         <x:v>0</x:v>
@@ -35379,10 +35379,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1273" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1273" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1274" spans="1:7">
@@ -40358,10 +40358,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40370,10 +40370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -40381,10 +40381,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1491" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1491" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1491" s="1">
         <x:v>0</x:v>
@@ -40393,10 +40393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1491" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1491" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1492" spans="1:7">
@@ -46913,10 +46913,10 @@
         <x:v>1806</x:v>
       </x:c>
       <x:c r="B1775" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1775" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1775" s="1">
         <x:v>0</x:v>
@@ -46928,7 +46928,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1775" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1776" spans="1:7">
@@ -46936,10 +46936,10 @@
         <x:v>1806</x:v>
       </x:c>
       <x:c r="B1776" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1776" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1776" s="1">
         <x:v>0</x:v>
@@ -46951,7 +46951,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1776" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1777" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8457,10 +8457,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C103" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>0</x:v>
@@ -8469,10 +8469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G103" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -8480,10 +8480,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8492,10 +8492,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -25178,10 +25178,10 @@
         <x:v>879</x:v>
       </x:c>
       <x:c r="B830" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C830" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D830" s="1">
         <x:v>0</x:v>
@@ -25190,10 +25190,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F830" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G830" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="831" spans="1:7">
@@ -25201,10 +25201,10 @@
         <x:v>879</x:v>
       </x:c>
       <x:c r="B831" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C831" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D831" s="1">
         <x:v>0</x:v>
@@ -25213,10 +25213,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F831" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G831" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="832" spans="1:7">
@@ -32124,10 +32124,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32136,10 +32136,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -32147,10 +32147,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1133" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1133" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1133" s="1">
         <x:v>0</x:v>
@@ -32159,10 +32159,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1133" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1133" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1134" spans="1:7">
@@ -35781,7 +35781,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1291" s="1">
         <x:v>0</x:v>
@@ -35793,10 +35793,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35804,7 +35804,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1292" s="1">
         <x:v>0</x:v>
@@ -35816,10 +35816,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -42681,10 +42681,10 @@
         <x:v>1628</x:v>
       </x:c>
       <x:c r="B1591" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1591" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1591" s="1">
         <x:v>0</x:v>
@@ -42693,10 +42693,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1591" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1591" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1592" spans="1:7">
@@ -42704,10 +42704,10 @@
         <x:v>1628</x:v>
       </x:c>
       <x:c r="B1592" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1592" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1592" s="1">
         <x:v>0</x:v>
@@ -42716,10 +42716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1592" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1592" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1593" spans="1:7">
@@ -43877,10 +43877,10 @@
         <x:v>1678</x:v>
       </x:c>
       <x:c r="B1643" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1643" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1643" s="1">
         <x:v>0</x:v>
@@ -43889,10 +43889,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1643" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1643" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1644" spans="1:7">
@@ -43900,10 +43900,10 @@
         <x:v>1678</x:v>
       </x:c>
       <x:c r="B1644" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1644" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1644" s="1">
         <x:v>0</x:v>
@@ -43912,10 +43912,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1644" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1644" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1645" spans="1:7">
@@ -45510,10 +45510,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1714" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1714" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1714" s="1">
         <x:v>0</x:v>
@@ -45522,10 +45522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1714" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1714" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1715" spans="1:7">
@@ -45533,10 +45533,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45545,10 +45545,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -48960,10 +48960,10 @@
         <x:v>1893</x:v>
       </x:c>
       <x:c r="B1864" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1864" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1864" s="1">
         <x:v>0</x:v>
@@ -48972,10 +48972,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1864" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1864" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1865" spans="1:7">
@@ -48983,10 +48983,10 @@
         <x:v>1893</x:v>
       </x:c>
       <x:c r="B1865" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1865" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1865" s="1">
         <x:v>0</x:v>
@@ -48995,10 +48995,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1865" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1865" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1866" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8457,10 +8457,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C103" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>0</x:v>
@@ -8469,10 +8469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G103" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -8480,10 +8480,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8492,10 +8492,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -25178,10 +25178,10 @@
         <x:v>879</x:v>
       </x:c>
       <x:c r="B830" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C830" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D830" s="1">
         <x:v>0</x:v>
@@ -25190,10 +25190,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F830" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G830" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="831" spans="1:7">
@@ -25201,10 +25201,10 @@
         <x:v>879</x:v>
       </x:c>
       <x:c r="B831" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C831" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D831" s="1">
         <x:v>0</x:v>
@@ -25213,10 +25213,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F831" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G831" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="832" spans="1:7">
@@ -30606,10 +30606,10 @@
         <x:v>1111</x:v>
       </x:c>
       <x:c r="B1066" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1066" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1066" s="1">
         <x:v>0</x:v>
@@ -30618,10 +30618,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1066" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1066" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1067" spans="1:7">
@@ -30629,10 +30629,10 @@
         <x:v>1111</x:v>
       </x:c>
       <x:c r="B1067" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1067" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1067" s="1">
         <x:v>0</x:v>
@@ -30641,10 +30641,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1067" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1067" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1068" spans="1:7">
@@ -35781,7 +35781,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1291" s="1">
         <x:v>0</x:v>
@@ -35793,10 +35793,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35804,7 +35804,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1292" s="1">
         <x:v>0</x:v>
@@ -35816,10 +35816,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37138,10 +37138,10 @@
         <x:v>1390</x:v>
       </x:c>
       <x:c r="B1350" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1350" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1350" s="1">
         <x:v>0</x:v>
@@ -37150,10 +37150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1350" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1350" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1351" spans="1:7">
@@ -37161,10 +37161,10 @@
         <x:v>1390</x:v>
       </x:c>
       <x:c r="B1351" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1351" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1351" s="1">
         <x:v>0</x:v>
@@ -37173,10 +37173,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1351" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1351" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1352" spans="1:7">
@@ -40358,10 +40358,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40370,10 +40370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -40381,10 +40381,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1491" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1491" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1491" s="1">
         <x:v>0</x:v>
@@ -40393,10 +40393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1491" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1491" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1492" spans="1:7">
@@ -42681,10 +42681,10 @@
         <x:v>1628</x:v>
       </x:c>
       <x:c r="B1591" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1591" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1591" s="1">
         <x:v>0</x:v>
@@ -42693,10 +42693,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1591" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1591" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1592" spans="1:7">
@@ -42704,10 +42704,10 @@
         <x:v>1628</x:v>
       </x:c>
       <x:c r="B1592" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1592" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1592" s="1">
         <x:v>0</x:v>
@@ -42716,10 +42716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1592" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1592" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1593" spans="1:7">
@@ -43463,10 +43463,10 @@
         <x:v>1661</x:v>
       </x:c>
       <x:c r="B1625" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1625" s="1">
         <x:v>0</x:v>
@@ -43475,10 +43475,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1625" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1626" spans="1:7">
@@ -43486,10 +43486,10 @@
         <x:v>1661</x:v>
       </x:c>
       <x:c r="B1626" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1626" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1626" s="1">
         <x:v>0</x:v>
@@ -43498,10 +43498,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1626" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1626" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1627" spans="1:7">
@@ -43877,10 +43877,10 @@
         <x:v>1678</x:v>
       </x:c>
       <x:c r="B1643" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1643" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1643" s="1">
         <x:v>0</x:v>
@@ -43889,10 +43889,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1643" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1643" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1644" spans="1:7">
@@ -43900,10 +43900,10 @@
         <x:v>1678</x:v>
       </x:c>
       <x:c r="B1644" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1644" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1644" s="1">
         <x:v>0</x:v>
@@ -43912,10 +43912,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1644" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1644" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1645" spans="1:7">
@@ -45510,10 +45510,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1714" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1714" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1714" s="1">
         <x:v>0</x:v>
@@ -45522,10 +45522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1714" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1714" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1715" spans="1:7">
@@ -45533,10 +45533,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45545,10 +45545,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -46913,10 +46913,10 @@
         <x:v>1806</x:v>
       </x:c>
       <x:c r="B1775" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1775" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1775" s="1">
         <x:v>0</x:v>
@@ -46928,7 +46928,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1775" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1776" spans="1:7">
@@ -46936,10 +46936,10 @@
         <x:v>1806</x:v>
       </x:c>
       <x:c r="B1776" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1776" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1776" s="1">
         <x:v>0</x:v>
@@ -46951,7 +46951,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1776" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1777" spans="1:7">
@@ -48960,10 +48960,10 @@
         <x:v>1893</x:v>
       </x:c>
       <x:c r="B1864" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1864" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1864" s="1">
         <x:v>0</x:v>
@@ -48972,10 +48972,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1864" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1864" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1865" spans="1:7">
@@ -48983,10 +48983,10 @@
         <x:v>1893</x:v>
       </x:c>
       <x:c r="B1865" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1865" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1865" s="1">
         <x:v>0</x:v>
@@ -48995,10 +48995,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1865" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1865" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1866" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30606,10 +30606,10 @@
         <x:v>1111</x:v>
       </x:c>
       <x:c r="B1066" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1066" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1066" s="1">
         <x:v>0</x:v>
@@ -30618,10 +30618,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1066" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1066" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1067" spans="1:7">
@@ -30629,10 +30629,10 @@
         <x:v>1111</x:v>
       </x:c>
       <x:c r="B1067" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1067" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1067" s="1">
         <x:v>0</x:v>
@@ -30641,10 +30641,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1067" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1067" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1068" spans="1:7">
@@ -32124,10 +32124,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32136,10 +32136,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -32147,10 +32147,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1133" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1133" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1133" s="1">
         <x:v>0</x:v>
@@ -32159,10 +32159,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1133" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1133" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1134" spans="1:7">
@@ -35781,7 +35781,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1291" s="1">
         <x:v>0</x:v>
@@ -35793,10 +35793,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35804,7 +35804,7 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1292" s="1">
         <x:v>0</x:v>
@@ -35816,10 +35816,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37138,10 +37138,10 @@
         <x:v>1390</x:v>
       </x:c>
       <x:c r="B1350" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1350" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1350" s="1">
         <x:v>0</x:v>
@@ -37150,10 +37150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1350" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1351" spans="1:7">
@@ -37161,10 +37161,10 @@
         <x:v>1390</x:v>
       </x:c>
       <x:c r="B1351" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1351" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1351" s="1">
         <x:v>0</x:v>
@@ -37173,10 +37173,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1351" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1351" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1352" spans="1:7">
@@ -40358,10 +40358,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40370,10 +40370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -40381,10 +40381,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1491" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1491" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1491" s="1">
         <x:v>0</x:v>
@@ -40393,10 +40393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1491" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1491" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1492" spans="1:7">
@@ -43463,10 +43463,10 @@
         <x:v>1661</x:v>
       </x:c>
       <x:c r="B1625" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1625" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1625" s="1">
         <x:v>0</x:v>
@@ -43475,10 +43475,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1625" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1625" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1626" spans="1:7">
@@ -43486,10 +43486,10 @@
         <x:v>1661</x:v>
       </x:c>
       <x:c r="B1626" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1626" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1626" s="1">
         <x:v>0</x:v>
@@ -43498,10 +43498,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1626" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1626" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1627" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -26949,10 +26949,10 @@
         <x:v>955</x:v>
       </x:c>
       <x:c r="B907" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C907" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D907" s="1">
         <x:v>0</x:v>
@@ -26961,10 +26961,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F907" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G907" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="908" spans="1:7">
@@ -26972,10 +26972,10 @@
         <x:v>955</x:v>
       </x:c>
       <x:c r="B908" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C908" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D908" s="1">
         <x:v>0</x:v>
@@ -26984,10 +26984,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F908" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G908" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="909" spans="1:7">
@@ -32124,10 +32124,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1132" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1132" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1132" s="1">
         <x:v>0</x:v>
@@ -32136,10 +32136,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1132" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1133" spans="1:7">
@@ -32147,10 +32147,10 @@
         <x:v>1176</x:v>
       </x:c>
       <x:c r="B1133" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1133" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1133" s="1">
         <x:v>0</x:v>
@@ -32159,10 +32159,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1133" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1133" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1134" spans="1:7">
@@ -40358,10 +40358,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1490" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1490" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1490" s="1">
         <x:v>0</x:v>
@@ -40370,10 +40370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1490" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1490" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1491" spans="1:7">
@@ -40381,10 +40381,10 @@
         <x:v>1530</x:v>
       </x:c>
       <x:c r="B1491" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1491" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1491" s="1">
         <x:v>0</x:v>
@@ -40393,10 +40393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1491" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1491" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1492" spans="1:7">
@@ -42681,10 +42681,10 @@
         <x:v>1628</x:v>
       </x:c>
       <x:c r="B1591" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1591" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1591" s="1">
         <x:v>0</x:v>
@@ -42693,10 +42693,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1591" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1591" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1592" spans="1:7">
@@ -42704,10 +42704,10 @@
         <x:v>1628</x:v>
       </x:c>
       <x:c r="B1592" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1592" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1592" s="1">
         <x:v>0</x:v>
@@ -42716,10 +42716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1592" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1592" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1593" spans="1:7">
@@ -43463,10 +43463,10 @@
         <x:v>1661</x:v>
       </x:c>
       <x:c r="B1625" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1625" s="1">
         <x:v>0</x:v>
@@ -43475,10 +43475,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1625" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1625" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1626" spans="1:7">
@@ -43486,10 +43486,10 @@
         <x:v>1661</x:v>
       </x:c>
       <x:c r="B1626" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1626" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1626" s="1">
         <x:v>0</x:v>
@@ -43498,10 +43498,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1626" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1626" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1627" spans="1:7">
@@ -45326,10 +45326,10 @@
         <x:v>1739</x:v>
       </x:c>
       <x:c r="B1706" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1706" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1706" s="1">
         <x:v>0</x:v>
@@ -45338,10 +45338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1706" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1706" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1707" spans="1:7">
@@ -45349,10 +45349,10 @@
         <x:v>1739</x:v>
       </x:c>
       <x:c r="B1707" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1707" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1707" s="1">
         <x:v>0</x:v>
@@ -45361,10 +45361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1707" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1707" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1708" spans="1:7">
@@ -45510,10 +45510,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1714" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1714" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1714" s="1">
         <x:v>0</x:v>
@@ -45522,10 +45522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1714" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1714" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1715" spans="1:7">
@@ -45533,10 +45533,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45545,10 +45545,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21089,10 +21089,10 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C659" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D659" s="1">
         <x:v>0</x:v>
@@ -21101,10 +21101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F659" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -21112,10 +21112,10 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D660" s="1">
         <x:v>0</x:v>
@@ -21124,10 +21124,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F660" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -31278,10 +31278,10 @@
         <x:v>1146</x:v>
       </x:c>
       <x:c r="B1102" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1102" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1102" s="1">
         <x:v>0</x:v>
@@ -31290,10 +31290,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1102" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1102" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1103" spans="1:7">
@@ -31301,10 +31301,10 @@
         <x:v>1146</x:v>
       </x:c>
       <x:c r="B1103" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C1103" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1103" s="1">
         <x:v>0</x:v>
@@ -31313,10 +31313,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1103" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1103" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1104" spans="1:7">
@@ -41513,10 +41513,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1547" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C1547" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1547" s="1">
         <x:v>0</x:v>
@@ -41525,10 +41525,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1547" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1547" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1548" spans="1:7">
@@ -41536,10 +41536,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1548" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1548" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1548" s="1">
         <x:v>0</x:v>
@@ -41548,10 +41548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1548" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1548" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1549" spans="1:7">
@@ -42295,10 +42295,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1581" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1581" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1581" s="1">
         <x:v>0</x:v>
@@ -42307,10 +42307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1581" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1581" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1582" spans="1:7">
@@ -42318,10 +42318,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1582" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1582" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1582" s="1">
         <x:v>0</x:v>
@@ -42330,10 +42330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1582" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1582" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1583" spans="1:7">
@@ -47608,10 +47608,10 @@
         <x:v>1841</x:v>
       </x:c>
       <x:c r="B1812" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C1812" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1812" s="1">
         <x:v>0</x:v>
@@ -47620,10 +47620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1812" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1812" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1813" spans="1:7">
@@ -47631,10 +47631,10 @@
         <x:v>1841</x:v>
       </x:c>
       <x:c r="B1813" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1813" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1813" s="1">
         <x:v>0</x:v>
@@ -47643,10 +47643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1813" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1813" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1814" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10578,7 +10578,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C202" s="1">
         <x:v>0</x:v>
@@ -10590,10 +10590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>8878</x:v>
+        <x:v>16758</x:v>
       </x:c>
       <x:c r="G202" s="1">
-        <x:v>8878</x:v>
+        <x:v>16758</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
@@ -10601,7 +10601,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C203" s="1">
         <x:v>0</x:v>
@@ -10613,10 +10613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>16758</x:v>
+        <x:v>8878</x:v>
       </x:c>
       <x:c r="G203" s="1">
-        <x:v>16758</x:v>
+        <x:v>8878</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
@@ -41513,10 +41513,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1547" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1547" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1547" s="1">
         <x:v>0</x:v>
@@ -41525,10 +41525,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1547" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1547" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1548" spans="1:7">
@@ -41536,10 +41536,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1548" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C1548" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1548" s="1">
         <x:v>0</x:v>
@@ -41548,10 +41548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1548" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1548" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1549" spans="1:7">
@@ -44135,10 +44135,10 @@
         <x:v>1694</x:v>
       </x:c>
       <x:c r="B1661" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1661" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1661" s="1">
         <x:v>0</x:v>
@@ -44147,10 +44147,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1661" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1661" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1662" spans="1:7">
@@ -44158,10 +44158,10 @@
         <x:v>1694</x:v>
       </x:c>
       <x:c r="B1662" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C1662" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1662" s="1">
         <x:v>0</x:v>
@@ -44170,10 +44170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1662" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1662" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1663" spans="1:7">
@@ -45653,10 +45653,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45668,7 +45668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -45676,10 +45676,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1728" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1728" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="D1728" s="1">
         <x:v>0</x:v>
@@ -45691,7 +45691,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1728" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1729" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10578,7 +10578,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C202" s="1">
         <x:v>0</x:v>
@@ -10590,10 +10590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>16758</x:v>
+        <x:v>8878</x:v>
       </x:c>
       <x:c r="G202" s="1">
-        <x:v>16758</x:v>
+        <x:v>8878</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
@@ -10601,7 +10601,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C203" s="1">
         <x:v>0</x:v>
@@ -10613,10 +10613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>8878</x:v>
+        <x:v>16758</x:v>
       </x:c>
       <x:c r="G203" s="1">
-        <x:v>8878</x:v>
+        <x:v>16758</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
@@ -21089,10 +21089,10 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C659" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D659" s="1">
         <x:v>0</x:v>
@@ -21101,10 +21101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F659" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -21112,10 +21112,10 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D660" s="1">
         <x:v>0</x:v>
@@ -21124,10 +21124,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F660" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -29185,10 +29185,10 @@
         <x:v>1057</x:v>
       </x:c>
       <x:c r="B1011" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1011" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1011" s="1">
         <x:v>0</x:v>
@@ -29197,10 +29197,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1011" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1011" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1012" spans="1:7">
@@ -29208,10 +29208,10 @@
         <x:v>1057</x:v>
       </x:c>
       <x:c r="B1012" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C1012" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1012" s="1">
         <x:v>0</x:v>
@@ -29220,10 +29220,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1012" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1012" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1013" spans="1:7">
@@ -34774,7 +34774,7 @@
         <x:v>1296</x:v>
       </x:c>
       <x:c r="B1254" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1254" s="1">
         <x:v>0</x:v>
@@ -34786,10 +34786,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1254" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1254" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1255" spans="1:7">
@@ -34797,7 +34797,7 @@
         <x:v>1296</x:v>
       </x:c>
       <x:c r="B1255" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1255" s="1">
         <x:v>0</x:v>
@@ -34809,10 +34809,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1255" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1255" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1256" spans="1:7">
@@ -41513,10 +41513,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1547" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C1547" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1547" s="1">
         <x:v>0</x:v>
@@ -41525,10 +41525,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1547" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1547" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1548" spans="1:7">
@@ -41536,10 +41536,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1548" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1548" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1548" s="1">
         <x:v>0</x:v>
@@ -41548,10 +41548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1548" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1548" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1549" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -29185,10 +29185,10 @@
         <x:v>1057</x:v>
       </x:c>
       <x:c r="B1011" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C1011" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1011" s="1">
         <x:v>0</x:v>
@@ -29197,10 +29197,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1011" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1011" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1012" spans="1:7">
@@ -29208,10 +29208,10 @@
         <x:v>1057</x:v>
       </x:c>
       <x:c r="B1012" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1012" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1012" s="1">
         <x:v>0</x:v>
@@ -29220,10 +29220,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1012" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1012" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1013" spans="1:7">
@@ -31278,10 +31278,10 @@
         <x:v>1146</x:v>
       </x:c>
       <x:c r="B1102" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C1102" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1102" s="1">
         <x:v>0</x:v>
@@ -31290,10 +31290,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1102" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1102" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1103" spans="1:7">
@@ -31301,10 +31301,10 @@
         <x:v>1146</x:v>
       </x:c>
       <x:c r="B1103" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1103" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1103" s="1">
         <x:v>0</x:v>
@@ -31313,10 +31313,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1103" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1103" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1104" spans="1:7">
@@ -34337,10 +34337,10 @@
         <x:v>1277</x:v>
       </x:c>
       <x:c r="B1235" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C1235" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1235" s="1">
         <x:v>0</x:v>
@@ -34349,10 +34349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1235" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1235" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1236" spans="1:7">
@@ -34360,10 +34360,10 @@
         <x:v>1277</x:v>
       </x:c>
       <x:c r="B1236" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C1236" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1236" s="1">
         <x:v>0</x:v>
@@ -34372,10 +34372,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1236" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1236" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1237" spans="1:7">
@@ -34774,7 +34774,7 @@
         <x:v>1296</x:v>
       </x:c>
       <x:c r="B1254" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1254" s="1">
         <x:v>0</x:v>
@@ -34786,10 +34786,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1254" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1254" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1255" spans="1:7">
@@ -34797,7 +34797,7 @@
         <x:v>1296</x:v>
       </x:c>
       <x:c r="B1255" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1255" s="1">
         <x:v>0</x:v>
@@ -34809,10 +34809,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1255" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1255" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1256" spans="1:7">
@@ -39834,7 +39834,7 @@
         <x:v>1513</x:v>
       </x:c>
       <x:c r="B1474" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1474" s="1">
         <x:v>0</x:v>
@@ -39846,10 +39846,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1474" s="1">
-        <x:v>3239</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1474" s="1">
-        <x:v>3239</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1475" spans="1:7">
@@ -39857,7 +39857,7 @@
         <x:v>1513</x:v>
       </x:c>
       <x:c r="B1475" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1475" s="1">
         <x:v>0</x:v>
@@ -39869,10 +39869,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1475" s="1">
-        <x:v>500</x:v>
+        <x:v>3239</x:v>
       </x:c>
       <x:c r="G1475" s="1">
-        <x:v>500</x:v>
+        <x:v>3239</x:v>
       </x:c>
     </x:row>
     <x:row r="1476" spans="1:7">
@@ -42295,10 +42295,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1581" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1581" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1581" s="1">
         <x:v>0</x:v>
@@ -42307,10 +42307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1581" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1581" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1582" spans="1:7">
@@ -42318,10 +42318,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1582" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1582" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1582" s="1">
         <x:v>0</x:v>
@@ -42330,10 +42330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1582" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1582" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1583" spans="1:7">
@@ -45653,10 +45653,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45668,7 +45668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -45676,10 +45676,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1728" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C1728" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1728" s="1">
         <x:v>0</x:v>
@@ -45691,7 +45691,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1728" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1729" spans="1:7">
@@ -47608,10 +47608,10 @@
         <x:v>1841</x:v>
       </x:c>
       <x:c r="B1812" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1812" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1812" s="1">
         <x:v>0</x:v>
@@ -47620,10 +47620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1812" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1812" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1813" spans="1:7">
@@ -47631,10 +47631,10 @@
         <x:v>1841</x:v>
       </x:c>
       <x:c r="B1813" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C1813" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1813" s="1">
         <x:v>0</x:v>
@@ -47643,10 +47643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1813" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1813" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1814" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16466,10 +16466,10 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B458" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C458" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D458" s="1">
         <x:v>0</x:v>
@@ -16478,10 +16478,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F458" s="1">
-        <x:v>6950</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>20050</x:v>
+        <x:v>6800</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -16489,10 +16489,10 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B459" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C459" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D459" s="1">
         <x:v>0</x:v>
@@ -16501,10 +16501,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F459" s="1">
-        <x:v>6800</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G459" s="1">
-        <x:v>6800</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:7">
@@ -18329,7 +18329,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C539" s="1">
         <x:v>0</x:v>
@@ -18341,10 +18341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F539" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -18352,7 +18352,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>0</x:v>
@@ -18364,10 +18364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F540" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -20008,10 +20008,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>19000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D612" s="1">
         <x:v>0</x:v>
@@ -20020,10 +20020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F612" s="1">
-        <x:v>1500</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>20500</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -20031,10 +20031,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>0</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="D613" s="1">
         <x:v>0</x:v>
@@ -20043,10 +20043,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>6000</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>6000</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -34337,10 +34337,10 @@
         <x:v>1277</x:v>
       </x:c>
       <x:c r="B1235" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C1235" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1235" s="1">
         <x:v>0</x:v>
@@ -34349,10 +34349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1235" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1235" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1236" spans="1:7">
@@ -34360,10 +34360,10 @@
         <x:v>1277</x:v>
       </x:c>
       <x:c r="B1236" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C1236" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1236" s="1">
         <x:v>0</x:v>
@@ -34372,10 +34372,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1236" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1236" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1237" spans="1:7">
@@ -39834,7 +39834,7 @@
         <x:v>1513</x:v>
       </x:c>
       <x:c r="B1474" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1474" s="1">
         <x:v>0</x:v>
@@ -39846,10 +39846,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1474" s="1">
-        <x:v>500</x:v>
+        <x:v>3239</x:v>
       </x:c>
       <x:c r="G1474" s="1">
-        <x:v>500</x:v>
+        <x:v>3239</x:v>
       </x:c>
     </x:row>
     <x:row r="1475" spans="1:7">
@@ -39857,7 +39857,7 @@
         <x:v>1513</x:v>
       </x:c>
       <x:c r="B1475" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1475" s="1">
         <x:v>0</x:v>
@@ -39869,10 +39869,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1475" s="1">
-        <x:v>3239</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1475" s="1">
-        <x:v>3239</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1476" spans="1:7">
@@ -42295,10 +42295,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1581" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1581" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1581" s="1">
         <x:v>0</x:v>
@@ -42307,10 +42307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1581" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1581" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1582" spans="1:7">
@@ -42318,10 +42318,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1582" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1582" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1582" s="1">
         <x:v>0</x:v>
@@ -42330,10 +42330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1582" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1582" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1583" spans="1:7">
@@ -45653,10 +45653,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45668,7 +45668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -45676,10 +45676,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1728" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1728" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="D1728" s="1">
         <x:v>0</x:v>
@@ -45691,7 +45691,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1728" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1729" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -10578,7 +10578,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C202" s="1">
         <x:v>0</x:v>
@@ -10590,10 +10590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F202" s="1">
-        <x:v>8878</x:v>
+        <x:v>16758</x:v>
       </x:c>
       <x:c r="G202" s="1">
-        <x:v>8878</x:v>
+        <x:v>16758</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
@@ -10601,7 +10601,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B203" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C203" s="1">
         <x:v>0</x:v>
@@ -10613,10 +10613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F203" s="1">
-        <x:v>16758</x:v>
+        <x:v>8878</x:v>
       </x:c>
       <x:c r="G203" s="1">
-        <x:v>16758</x:v>
+        <x:v>8878</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
@@ -16466,10 +16466,10 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B458" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C458" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D458" s="1">
         <x:v>0</x:v>
@@ -16478,10 +16478,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F458" s="1">
-        <x:v>6800</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>6800</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -16489,10 +16489,10 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B459" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C459" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D459" s="1">
         <x:v>0</x:v>
@@ -16501,10 +16501,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F459" s="1">
-        <x:v>6950</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G459" s="1">
-        <x:v>20050</x:v>
+        <x:v>6800</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:7">
@@ -18329,7 +18329,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C539" s="1">
         <x:v>0</x:v>
@@ -18341,10 +18341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F539" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -18352,7 +18352,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>0</x:v>
@@ -18364,10 +18364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F540" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -20008,10 +20008,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>0</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="D612" s="1">
         <x:v>0</x:v>
@@ -20020,10 +20020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F612" s="1">
-        <x:v>6000</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>6000</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -20031,10 +20031,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>19000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D613" s="1">
         <x:v>0</x:v>
@@ -20043,10 +20043,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>1500</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>20500</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -29783,10 +29783,10 @@
         <x:v>1082</x:v>
       </x:c>
       <x:c r="B1037" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1037" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1037" s="1">
         <x:v>0</x:v>
@@ -29795,10 +29795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1037" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1037" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1038" spans="1:7">
@@ -29806,10 +29806,10 @@
         <x:v>1082</x:v>
       </x:c>
       <x:c r="B1038" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1038" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1038" s="1">
         <x:v>0</x:v>
@@ -29818,10 +29818,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1038" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1038" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1039" spans="1:7">
@@ -34337,10 +34337,10 @@
         <x:v>1277</x:v>
       </x:c>
       <x:c r="B1235" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C1235" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1235" s="1">
         <x:v>0</x:v>
@@ -34349,10 +34349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1235" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1235" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1236" spans="1:7">
@@ -34360,10 +34360,10 @@
         <x:v>1277</x:v>
       </x:c>
       <x:c r="B1236" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C1236" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1236" s="1">
         <x:v>0</x:v>
@@ -34372,10 +34372,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1236" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1236" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1237" spans="1:7">
@@ -39282,10 +39282,10 @@
         <x:v>1490</x:v>
       </x:c>
       <x:c r="B1450" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1450" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1450" s="1">
         <x:v>0</x:v>
@@ -39294,10 +39294,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1450" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1450" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1451" spans="1:7">
@@ -39305,10 +39305,10 @@
         <x:v>1490</x:v>
       </x:c>
       <x:c r="B1451" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1451" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1451" s="1">
         <x:v>0</x:v>
@@ -39317,10 +39317,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1451" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1451" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1452" spans="1:7">
@@ -42295,10 +42295,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1581" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1581" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1581" s="1">
         <x:v>0</x:v>
@@ -42307,10 +42307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1581" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1581" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1582" spans="1:7">
@@ -42318,10 +42318,10 @@
         <x:v>1617</x:v>
       </x:c>
       <x:c r="B1582" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1582" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1582" s="1">
         <x:v>0</x:v>
@@ -42330,10 +42330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1582" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1582" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1583" spans="1:7">
@@ -44135,10 +44135,10 @@
         <x:v>1694</x:v>
       </x:c>
       <x:c r="B1661" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C1661" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1661" s="1">
         <x:v>0</x:v>
@@ -44147,10 +44147,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1661" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1661" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1662" spans="1:7">
@@ -44158,10 +44158,10 @@
         <x:v>1694</x:v>
       </x:c>
       <x:c r="B1662" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1662" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1662" s="1">
         <x:v>0</x:v>
@@ -44170,10 +44170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1662" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1662" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1663" spans="1:7">
@@ -44319,10 +44319,10 @@
         <x:v>1701</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>68280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44331,10 +44331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>73030</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -44342,10 +44342,10 @@
         <x:v>1701</x:v>
       </x:c>
       <x:c r="B1670" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1670" s="1">
-        <x:v>7500</x:v>
+        <x:v>68280</x:v>
       </x:c>
       <x:c r="D1670" s="1">
         <x:v>0</x:v>
@@ -44354,10 +44354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1670" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G1670" s="1">
-        <x:v>7500</x:v>
+        <x:v>73030</x:v>
       </x:c>
     </x:row>
     <x:row r="1671" spans="1:7">
@@ -45653,10 +45653,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45668,7 +45668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>8500</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -45676,10 +45676,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1728" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C1728" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1728" s="1">
         <x:v>0</x:v>
@@ -45691,7 +45691,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1728" s="1">
-        <x:v>15500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1729" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -9547,10 +9547,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C150" s="1">
-        <x:v>0</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D150" s="1">
         <x:v>0</x:v>
@@ -9559,10 +9559,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F150" s="1">
-        <x:v>10854</x:v>
+        <x:v>52400</x:v>
       </x:c>
       <x:c r="G150" s="1">
-        <x:v>10854</x:v>
+        <x:v>86400</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
@@ -9570,10 +9570,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B151" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C151" s="1">
-        <x:v>34000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D151" s="1">
         <x:v>0</x:v>
@@ -9582,10 +9582,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F151" s="1">
-        <x:v>52400</x:v>
+        <x:v>10854</x:v>
       </x:c>
       <x:c r="G151" s="1">
-        <x:v>86400</x:v>
+        <x:v>10854</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
@@ -16884,10 +16884,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16896,10 +16896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16907,10 +16907,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16919,10 +16919,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -20035,10 +20035,10 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -20047,10 +20047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -20058,10 +20058,10 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -20070,10 +20070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F607" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -27694,10 +27694,10 @@
         <x:v>986</x:v>
       </x:c>
       <x:c r="B939" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C939" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D939" s="1">
         <x:v>0</x:v>
@@ -27706,10 +27706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F939" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G939" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="940" spans="1:7">
@@ -27717,10 +27717,10 @@
         <x:v>986</x:v>
       </x:c>
       <x:c r="B940" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C940" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D940" s="1">
         <x:v>0</x:v>
@@ -27729,10 +27729,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F940" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G940" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="941" spans="1:7">
@@ -34755,10 +34755,10 @@
         <x:v>1289</x:v>
       </x:c>
       <x:c r="B1246" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1246" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1246" s="1">
         <x:v>0</x:v>
@@ -34767,10 +34767,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1246" s="1">
-        <x:v>5000</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="G1246" s="1">
-        <x:v>5000</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="1247" spans="1:7">
@@ -34778,22 +34778,22 @@
         <x:v>1289</x:v>
       </x:c>
       <x:c r="B1247" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C1247" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1247" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1247" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F1247" s="1">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D1247" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1247" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F1247" s="1">
-        <x:v>6400</x:v>
-      </x:c>
       <x:c r="G1247" s="1">
-        <x:v>11400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1248" spans="1:7">
@@ -40436,10 +40436,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1493" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1493" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1493" s="1">
         <x:v>0</x:v>
@@ -40448,10 +40448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1493" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1493" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1494" spans="1:7">
@@ -40459,10 +40459,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40471,10 +40471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -43541,10 +43541,10 @@
         <x:v>1664</x:v>
       </x:c>
       <x:c r="B1628" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1628" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1628" s="1">
         <x:v>0</x:v>
@@ -43553,10 +43553,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1628" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1628" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1629" spans="1:7">
@@ -43564,10 +43564,10 @@
         <x:v>1664</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43576,10 +43576,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43955,10 +43955,10 @@
         <x:v>1681</x:v>
       </x:c>
       <x:c r="B1646" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1646" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1646" s="1">
         <x:v>0</x:v>
@@ -43967,10 +43967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1646" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1646" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1647" spans="1:7">
@@ -43978,10 +43978,10 @@
         <x:v>1681</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43990,10 +43990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -45404,10 +45404,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45416,10 +45416,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45427,10 +45427,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45439,10 +45439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45588,10 +45588,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45600,10 +45600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -45611,10 +45611,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45623,10 +45623,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32179,10 +32179,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1134" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1134" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1134" s="1">
         <x:v>0</x:v>
@@ -32191,10 +32191,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1134" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1134" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1135" spans="1:7">
@@ -32202,10 +32202,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1135" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1135" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1135" s="1">
         <x:v>0</x:v>
@@ -32214,10 +32214,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1135" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1135" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1136" spans="1:7">
@@ -35399,10 +35399,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35411,10 +35411,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35422,10 +35422,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35434,10 +35434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -37216,10 +37216,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37228,10 +37228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37239,10 +37239,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37251,10 +37251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -40436,10 +40436,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1493" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1493" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1493" s="1">
         <x:v>0</x:v>
@@ -40448,10 +40448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1493" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1493" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1494" spans="1:7">
@@ -40459,10 +40459,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40471,10 +40471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -43541,10 +43541,10 @@
         <x:v>1664</x:v>
       </x:c>
       <x:c r="B1628" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1628" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1628" s="1">
         <x:v>0</x:v>
@@ -43553,10 +43553,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1628" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1628" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1629" spans="1:7">
@@ -43564,10 +43564,10 @@
         <x:v>1664</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43576,10 +43576,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43955,10 +43955,10 @@
         <x:v>1681</x:v>
       </x:c>
       <x:c r="B1646" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1646" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1646" s="1">
         <x:v>0</x:v>
@@ -43967,10 +43967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1646" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1646" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1647" spans="1:7">
@@ -43978,10 +43978,10 @@
         <x:v>1681</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43990,10 +43990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -45404,10 +45404,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45416,10 +45416,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45427,10 +45427,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45439,10 +45439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45588,10 +45588,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45600,10 +45600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -45611,10 +45611,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45623,10 +45623,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -49038,10 +49038,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1867" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1867" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1867" s="1">
         <x:v>0</x:v>
@@ -49050,10 +49050,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1867" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1867" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1868" spans="1:7">
@@ -49061,10 +49061,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49073,10 +49073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -40436,10 +40436,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1493" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1493" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1493" s="1">
         <x:v>0</x:v>
@@ -40448,10 +40448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1493" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1493" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1494" spans="1:7">
@@ -40459,10 +40459,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40471,10 +40471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -43541,10 +43541,10 @@
         <x:v>1664</x:v>
       </x:c>
       <x:c r="B1628" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1628" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1628" s="1">
         <x:v>0</x:v>
@@ -43553,10 +43553,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1628" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1628" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1629" spans="1:7">
@@ -43564,10 +43564,10 @@
         <x:v>1664</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43576,10 +43576,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -45588,10 +45588,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45600,10 +45600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -45611,10 +45611,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45623,10 +45623,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -49038,10 +49038,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1867" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1867" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1867" s="1">
         <x:v>0</x:v>
@@ -49050,10 +49050,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1867" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1867" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1868" spans="1:7">
@@ -49061,10 +49061,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49073,10 +49073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -45404,10 +45404,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45416,10 +45416,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45427,10 +45427,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45439,10 +45439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45588,10 +45588,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45600,10 +45600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -45611,10 +45611,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45623,10 +45623,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8466,10 +8466,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C103" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>0</x:v>
@@ -8478,10 +8478,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G103" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -8489,10 +8489,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8501,10 +8501,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -16884,10 +16884,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16896,10 +16896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16907,10 +16907,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16919,10 +16919,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -21783,10 +21783,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21795,10 +21795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21806,10 +21806,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21818,10 +21818,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -32179,10 +32179,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1134" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1134" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1134" s="1">
         <x:v>0</x:v>
@@ -32191,10 +32191,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1134" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1134" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1135" spans="1:7">
@@ -32202,10 +32202,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1135" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1135" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1135" s="1">
         <x:v>0</x:v>
@@ -32214,10 +32214,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1135" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1135" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1136" spans="1:7">
@@ -35399,10 +35399,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35411,10 +35411,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35422,10 +35422,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35434,10 +35434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -37216,10 +37216,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37228,10 +37228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37239,10 +37239,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37251,10 +37251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -45404,10 +45404,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45416,10 +45416,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45427,10 +45427,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45439,10 +45439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -49038,10 +49038,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1867" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1867" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1867" s="1">
         <x:v>0</x:v>
@@ -49050,10 +49050,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1867" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1867" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1868" spans="1:7">
@@ -49061,10 +49061,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49073,10 +49073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21783,10 +21783,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21795,10 +21795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21806,10 +21806,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21818,10 +21818,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -30063,10 +30063,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1042" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1042" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1042" s="1">
         <x:v>0</x:v>
@@ -30075,10 +30075,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1042" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1042" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1043" spans="1:7">
@@ -30086,10 +30086,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1043" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1043" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1043" s="1">
         <x:v>0</x:v>
@@ -30098,10 +30098,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1043" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1043" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1044" spans="1:7">
@@ -37216,10 +37216,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37228,10 +37228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37239,10 +37239,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37251,10 +37251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -40436,10 +40436,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1493" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1493" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1493" s="1">
         <x:v>0</x:v>
@@ -40448,10 +40448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1493" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1493" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1494" spans="1:7">
@@ -40459,10 +40459,10 @@
         <x:v>1533</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40471,10 +40471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -45243,10 +45243,10 @@
         <x:v>1736</x:v>
       </x:c>
       <x:c r="B1702" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1702" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1702" s="1">
         <x:v>0</x:v>
@@ -45255,10 +45255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1702" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1702" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1703" spans="1:7">
@@ -45266,10 +45266,10 @@
         <x:v>1736</x:v>
       </x:c>
       <x:c r="B1703" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1703" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1703" s="1">
         <x:v>0</x:v>
@@ -45278,10 +45278,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1703" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1703" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1704" spans="1:7">
@@ -45404,10 +45404,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45416,10 +45416,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45427,10 +45427,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45439,10 +45439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -46991,10 +46991,10 @@
         <x:v>1809</x:v>
       </x:c>
       <x:c r="B1778" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1778" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1778" s="1">
         <x:v>0</x:v>
@@ -47006,7 +47006,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1778" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1779" spans="1:7">
@@ -47014,10 +47014,10 @@
         <x:v>1809</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47029,7 +47029,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -49038,10 +49038,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1867" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1867" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1867" s="1">
         <x:v>0</x:v>
@@ -49050,10 +49050,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1867" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1867" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1868" spans="1:7">
@@ -49061,10 +49061,10 @@
         <x:v>1896</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49073,10 +49073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8469,10 +8469,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C103" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>0</x:v>
@@ -8481,10 +8481,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G103" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -8492,10 +8492,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8504,10 +8504,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -25236,10 +25236,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C832" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D832" s="1">
         <x:v>0</x:v>
@@ -25248,10 +25248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F832" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G832" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="833" spans="1:7">
@@ -25259,10 +25259,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C833" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D833" s="1">
         <x:v>0</x:v>
@@ -25271,10 +25271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F833" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G833" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:7">
@@ -30664,10 +30664,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1068" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1068" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1068" s="1">
         <x:v>0</x:v>
@@ -30676,10 +30676,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1068" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1068" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1069" spans="1:7">
@@ -30687,10 +30687,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1069" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1069" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1069" s="1">
         <x:v>0</x:v>
@@ -30699,10 +30699,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1069" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1069" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1070" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -43981,10 +43981,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43993,10 +43993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44004,10 +44004,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44016,10 +44016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -21786,10 +21786,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21798,10 +21798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21809,10 +21809,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21821,10 +21821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -25236,10 +25236,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C832" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D832" s="1">
         <x:v>0</x:v>
@@ -25248,10 +25248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F832" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G832" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="833" spans="1:7">
@@ -25259,10 +25259,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C833" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D833" s="1">
         <x:v>0</x:v>
@@ -25271,10 +25271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F833" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G833" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:7">
@@ -30664,10 +30664,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1068" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1068" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1068" s="1">
         <x:v>0</x:v>
@@ -30676,10 +30676,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1068" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1068" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1069" spans="1:7">
@@ -30687,10 +30687,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1069" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1069" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1069" s="1">
         <x:v>0</x:v>
@@ -30699,10 +30699,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1069" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1069" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1070" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -43981,10 +43981,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43993,10 +43993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44004,10 +44004,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44016,10 +44016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -21786,10 +21786,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21798,10 +21798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21809,10 +21809,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21821,10 +21821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -35402,10 +35402,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35414,10 +35414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35425,10 +35425,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35437,10 +35437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -21786,10 +21786,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21798,10 +21798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21809,10 +21809,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21821,10 +21821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -35402,10 +35402,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35414,10 +35414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35425,10 +35425,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35437,10 +35437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -43981,10 +43981,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43993,10 +43993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44004,10 +44004,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44016,10 +44016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21786,10 +21786,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21798,10 +21798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21809,10 +21809,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21821,10 +21821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -6310,7 +6310,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>120870</x:v>
+        <x:v>125870</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>0</x:v>
@@ -6322,7 +6322,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="1">
-        <x:v>120870</x:v>
+        <x:v>125870</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
@@ -7552,7 +7552,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C63" s="1">
-        <x:v>53000</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>0</x:v>
@@ -7564,7 +7564,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G63" s="1">
-        <x:v>53000</x:v>
+        <x:v>55500</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
@@ -8242,7 +8242,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C93" s="1">
-        <x:v>56080</x:v>
+        <x:v>58080</x:v>
       </x:c>
       <x:c r="D93" s="1">
         <x:v>0</x:v>
@@ -8254,7 +8254,7 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="G93" s="1">
-        <x:v>56339</x:v>
+        <x:v>58339</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
@@ -8817,7 +8817,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C118" s="1">
-        <x:v>19000</x:v>
+        <x:v>26000</x:v>
       </x:c>
       <x:c r="D118" s="1">
         <x:v>0</x:v>
@@ -8829,7 +8829,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G118" s="1">
-        <x:v>19000</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
@@ -9415,7 +9415,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C144" s="1">
-        <x:v>41000</x:v>
+        <x:v>42000</x:v>
       </x:c>
       <x:c r="D144" s="1">
         <x:v>0</x:v>
@@ -9427,7 +9427,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G144" s="1">
-        <x:v>41000</x:v>
+        <x:v>42000</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
@@ -10749,7 +10749,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C202" s="1">
-        <x:v>13500</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="D202" s="1">
         <x:v>0</x:v>
@@ -10761,7 +10761,7 @@
         <x:v>2900</x:v>
       </x:c>
       <x:c r="G202" s="1">
-        <x:v>16400</x:v>
+        <x:v>19900</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
@@ -11761,7 +11761,7 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="C246" s="1">
-        <x:v>49500</x:v>
+        <x:v>52000</x:v>
       </x:c>
       <x:c r="D246" s="1">
         <x:v>0</x:v>
@@ -11773,7 +11773,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G246" s="1">
-        <x:v>51000</x:v>
+        <x:v>53500</x:v>
       </x:c>
     </x:row>
     <x:row r="247" spans="1:7">
@@ -12405,7 +12405,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C274" s="1">
-        <x:v>22180</x:v>
+        <x:v>23180</x:v>
       </x:c>
       <x:c r="D274" s="1">
         <x:v>0</x:v>
@@ -12417,7 +12417,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G274" s="1">
-        <x:v>22180</x:v>
+        <x:v>23180</x:v>
       </x:c>
     </x:row>
     <x:row r="275" spans="1:7">
@@ -13417,7 +13417,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C318" s="1">
-        <x:v>87520</x:v>
+        <x:v>90020</x:v>
       </x:c>
       <x:c r="D318" s="1">
         <x:v>0</x:v>
@@ -13429,7 +13429,7 @@
         <x:v>5200</x:v>
       </x:c>
       <x:c r="G318" s="1">
-        <x:v>92720</x:v>
+        <x:v>95220</x:v>
       </x:c>
     </x:row>
     <x:row r="319" spans="1:7">
@@ -14176,7 +14176,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C351" s="1">
-        <x:v>98500</x:v>
+        <x:v>101000</x:v>
       </x:c>
       <x:c r="D351" s="1">
         <x:v>0</x:v>
@@ -14188,7 +14188,7 @@
         <x:v>17750</x:v>
       </x:c>
       <x:c r="G351" s="1">
-        <x:v>116250</x:v>
+        <x:v>118750</x:v>
       </x:c>
     </x:row>
     <x:row r="352" spans="1:7">
@@ -15786,7 +15786,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C421" s="1">
-        <x:v>8000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="D421" s="1">
         <x:v>0</x:v>
@@ -15798,7 +15798,7 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="G421" s="1">
-        <x:v>9250</x:v>
+        <x:v>10250</x:v>
       </x:c>
     </x:row>
     <x:row r="422" spans="1:7">
@@ -16269,7 +16269,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C442" s="1">
-        <x:v>162135</x:v>
+        <x:v>167135</x:v>
       </x:c>
       <x:c r="D442" s="1">
         <x:v>0</x:v>
@@ -16281,7 +16281,7 @@
         <x:v>447299</x:v>
       </x:c>
       <x:c r="G442" s="1">
-        <x:v>609434</x:v>
+        <x:v>614434</x:v>
       </x:c>
     </x:row>
     <x:row r="443" spans="1:7">
@@ -16821,7 +16821,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C466" s="1">
-        <x:v>29000</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="D466" s="1">
         <x:v>0</x:v>
@@ -16833,7 +16833,7 @@
         <x:v>5350</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>34350</x:v>
+        <x:v>35350</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -17902,7 +17902,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="C513" s="1">
-        <x:v>101500</x:v>
+        <x:v>112500</x:v>
       </x:c>
       <x:c r="D513" s="1">
         <x:v>0</x:v>
@@ -17914,7 +17914,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>101500</x:v>
+        <x:v>112500</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -18937,7 +18937,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="C558" s="1">
-        <x:v>10500</x:v>
+        <x:v>11500</x:v>
       </x:c>
       <x:c r="D558" s="1">
         <x:v>0</x:v>
@@ -18949,7 +18949,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>10500</x:v>
+        <x:v>11500</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -19029,7 +19029,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C562" s="1">
-        <x:v>16500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D562" s="1">
         <x:v>0</x:v>
@@ -19041,7 +19041,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>16500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -19972,7 +19972,7 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>17000</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D603" s="1">
         <x:v>0</x:v>
@@ -19984,7 +19984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>17000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -20179,7 +20179,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>44135</x:v>
+        <x:v>51635</x:v>
       </x:c>
       <x:c r="D612" s="1">
         <x:v>0</x:v>
@@ -20191,7 +20191,7 @@
         <x:v>6900</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>51035</x:v>
+        <x:v>58535</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -20432,7 +20432,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>11680</x:v>
+        <x:v>12680</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
@@ -20444,7 +20444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>11680</x:v>
+        <x:v>12680</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -21973,7 +21973,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>84500</x:v>
+        <x:v>87000</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -21985,7 +21985,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>84500</x:v>
+        <x:v>87000</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -23468,7 +23468,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>45500</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -23480,7 +23480,7 @@
         <x:v>6400</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>51900</x:v>
+        <x:v>54400</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -23836,7 +23836,7 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="C771" s="1">
-        <x:v>87000</x:v>
+        <x:v>89000</x:v>
       </x:c>
       <x:c r="D771" s="1">
         <x:v>0</x:v>
@@ -23848,7 +23848,7 @@
         <x:v>3700</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>90700</x:v>
+        <x:v>92700</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
@@ -24733,7 +24733,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C810" s="1">
-        <x:v>81920</x:v>
+        <x:v>82920</x:v>
       </x:c>
       <x:c r="D810" s="1">
         <x:v>0</x:v>
@@ -24745,7 +24745,7 @@
         <x:v>1300</x:v>
       </x:c>
       <x:c r="G810" s="1">
-        <x:v>83220</x:v>
+        <x:v>84220</x:v>
       </x:c>
     </x:row>
     <x:row r="811" spans="1:7">
@@ -24756,7 +24756,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C811" s="1">
-        <x:v>9000</x:v>
+        <x:v>12500</x:v>
       </x:c>
       <x:c r="D811" s="1">
         <x:v>0</x:v>
@@ -24768,7 +24768,7 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="G811" s="1">
-        <x:v>10250</x:v>
+        <x:v>13750</x:v>
       </x:c>
     </x:row>
     <x:row r="812" spans="1:7">
@@ -24802,7 +24802,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C813" s="1">
-        <x:v>22405</x:v>
+        <x:v>23405</x:v>
       </x:c>
       <x:c r="D813" s="1">
         <x:v>0</x:v>
@@ -24814,7 +24814,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G813" s="1">
-        <x:v>22405</x:v>
+        <x:v>23405</x:v>
       </x:c>
     </x:row>
     <x:row r="814" spans="1:7">
@@ -24894,7 +24894,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C817" s="1">
-        <x:v>89640</x:v>
+        <x:v>92140</x:v>
       </x:c>
       <x:c r="D817" s="1">
         <x:v>0</x:v>
@@ -24906,7 +24906,7 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="G817" s="1">
-        <x:v>93140</x:v>
+        <x:v>95640</x:v>
       </x:c>
     </x:row>
     <x:row r="818" spans="1:7">
@@ -25308,7 +25308,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>13500</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="D835" s="1">
         <x:v>0</x:v>
@@ -25320,7 +25320,7 @@
         <x:v>8500</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>22000</x:v>
+        <x:v>24500</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
@@ -26734,7 +26734,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C897" s="1">
-        <x:v>30000</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D897" s="1">
         <x:v>0</x:v>
@@ -26746,7 +26746,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G897" s="1">
-        <x:v>30000</x:v>
+        <x:v>32500</x:v>
       </x:c>
     </x:row>
     <x:row r="898" spans="1:7">
@@ -28804,7 +28804,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C987" s="1">
-        <x:v>108140</x:v>
+        <x:v>113140</x:v>
       </x:c>
       <x:c r="D987" s="1">
         <x:v>0</x:v>
@@ -28816,7 +28816,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G987" s="1">
-        <x:v>109140</x:v>
+        <x:v>114140</x:v>
       </x:c>
     </x:row>
     <x:row r="988" spans="1:7">
@@ -29149,7 +29149,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C1002" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1002" s="1">
         <x:v>0</x:v>
@@ -29161,7 +29161,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1002" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="1003" spans="1:7">
@@ -29655,7 +29655,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1024" s="1">
-        <x:v>16000</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="D1024" s="1">
         <x:v>0</x:v>
@@ -29667,7 +29667,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1024" s="1">
-        <x:v>16000</x:v>
+        <x:v>18000</x:v>
       </x:c>
     </x:row>
     <x:row r="1025" spans="1:7">
@@ -30046,7 +30046,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1041" s="1">
-        <x:v>6000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1041" s="1">
         <x:v>0</x:v>
@@ -30058,7 +30058,7 @@
         <x:v>24200</x:v>
       </x:c>
       <x:c r="G1041" s="1">
-        <x:v>30200</x:v>
+        <x:v>31200</x:v>
       </x:c>
     </x:row>
     <x:row r="1042" spans="1:7">
@@ -30066,10 +30066,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1042" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1042" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1042" s="1">
         <x:v>0</x:v>
@@ -30078,10 +30078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1042" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1042" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1043" spans="1:7">
@@ -30089,10 +30089,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1043" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1043" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1043" s="1">
         <x:v>0</x:v>
@@ -30101,10 +30101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1043" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1043" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1044" spans="1:7">
@@ -30115,7 +30115,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1044" s="1">
-        <x:v>89000</x:v>
+        <x:v>93000</x:v>
       </x:c>
       <x:c r="D1044" s="1">
         <x:v>0</x:v>
@@ -30127,7 +30127,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="G1044" s="1">
-        <x:v>89750</x:v>
+        <x:v>93750</x:v>
       </x:c>
     </x:row>
     <x:row r="1045" spans="1:7">
@@ -30276,7 +30276,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1051" s="1">
-        <x:v>327275</x:v>
+        <x:v>329775</x:v>
       </x:c>
       <x:c r="D1051" s="1">
         <x:v>0</x:v>
@@ -30288,7 +30288,7 @@
         <x:v>83750</x:v>
       </x:c>
       <x:c r="G1051" s="1">
-        <x:v>411025</x:v>
+        <x:v>413525</x:v>
       </x:c>
     </x:row>
     <x:row r="1052" spans="1:7">
@@ -32047,7 +32047,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C1128" s="1">
-        <x:v>11000</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1128" s="1">
         <x:v>0</x:v>
@@ -32059,7 +32059,7 @@
         <x:v>3300</x:v>
       </x:c>
       <x:c r="G1128" s="1">
-        <x:v>14300</x:v>
+        <x:v>16300</x:v>
       </x:c>
     </x:row>
     <x:row r="1129" spans="1:7">
@@ -33105,7 +33105,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C1174" s="1">
-        <x:v>99000</x:v>
+        <x:v>101500</x:v>
       </x:c>
       <x:c r="D1174" s="1">
         <x:v>0</x:v>
@@ -33117,7 +33117,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1174" s="1">
-        <x:v>99000</x:v>
+        <x:v>101500</x:v>
       </x:c>
     </x:row>
     <x:row r="1175" spans="1:7">
@@ -33473,7 +33473,7 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="C1190" s="1">
-        <x:v>13000</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D1190" s="1">
         <x:v>0</x:v>
@@ -33485,7 +33485,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1190" s="1">
-        <x:v>13000</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="1191" spans="1:7">
@@ -33634,7 +33634,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C1197" s="1">
-        <x:v>3500</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D1197" s="1">
         <x:v>0</x:v>
@@ -33646,7 +33646,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1197" s="1">
-        <x:v>3500</x:v>
+        <x:v>4500</x:v>
       </x:c>
     </x:row>
     <x:row r="1198" spans="1:7">
@@ -33726,7 +33726,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C1201" s="1">
-        <x:v>21090</x:v>
+        <x:v>23090</x:v>
       </x:c>
       <x:c r="D1201" s="1">
         <x:v>0</x:v>
@@ -33738,7 +33738,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="G1201" s="1">
-        <x:v>21340</x:v>
+        <x:v>23340</x:v>
       </x:c>
     </x:row>
     <x:row r="1202" spans="1:7">
@@ -33979,7 +33979,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1212" s="1">
-        <x:v>7000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1212" s="1">
         <x:v>0</x:v>
@@ -33991,7 +33991,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1212" s="1">
-        <x:v>7000</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="1213" spans="1:7">
@@ -34255,7 +34255,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C1224" s="1">
-        <x:v>19590</x:v>
+        <x:v>20590</x:v>
       </x:c>
       <x:c r="D1224" s="1">
         <x:v>0</x:v>
@@ -34267,7 +34267,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1224" s="1">
-        <x:v>19590</x:v>
+        <x:v>20590</x:v>
       </x:c>
     </x:row>
     <x:row r="1225" spans="1:7">
@@ -34370,7 +34370,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1229" s="1">
-        <x:v>5000</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="D1229" s="1">
         <x:v>0</x:v>
@@ -34382,7 +34382,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1229" s="1">
-        <x:v>5000</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="1230" spans="1:7">
@@ -34577,7 +34577,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1238" s="1">
-        <x:v>7000</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1238" s="1">
         <x:v>0</x:v>
@@ -34589,7 +34589,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1238" s="1">
-        <x:v>7000</x:v>
+        <x:v>8000</x:v>
       </x:c>
     </x:row>
     <x:row r="1239" spans="1:7">
@@ -35402,10 +35402,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35414,10 +35414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35425,10 +35425,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35437,10 +35437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -36555,7 +36555,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C1324" s="1">
-        <x:v>206500</x:v>
+        <x:v>211500</x:v>
       </x:c>
       <x:c r="D1324" s="1">
         <x:v>0</x:v>
@@ -36567,7 +36567,7 @@
         <x:v>8200</x:v>
       </x:c>
       <x:c r="G1324" s="1">
-        <x:v>214700</x:v>
+        <x:v>219700</x:v>
       </x:c>
     </x:row>
     <x:row r="1325" spans="1:7">
@@ -36624,7 +36624,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1327" s="1">
-        <x:v>45775</x:v>
+        <x:v>46775</x:v>
       </x:c>
       <x:c r="D1327" s="1">
         <x:v>0</x:v>
@@ -36636,7 +36636,7 @@
         <x:v>3750</x:v>
       </x:c>
       <x:c r="G1327" s="1">
-        <x:v>49525</x:v>
+        <x:v>50525</x:v>
       </x:c>
     </x:row>
     <x:row r="1328" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -38671,7 +38671,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C1416" s="1">
-        <x:v>51590</x:v>
+        <x:v>55590</x:v>
       </x:c>
       <x:c r="D1416" s="1">
         <x:v>0</x:v>
@@ -38683,7 +38683,7 @@
         <x:v>15200</x:v>
       </x:c>
       <x:c r="G1416" s="1">
-        <x:v>66790</x:v>
+        <x:v>70790</x:v>
       </x:c>
     </x:row>
     <x:row r="1417" spans="1:7">
@@ -38786,7 +38786,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C1421" s="1">
-        <x:v>60500</x:v>
+        <x:v>65500</x:v>
       </x:c>
       <x:c r="D1421" s="1">
         <x:v>0</x:v>
@@ -38798,7 +38798,7 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="G1421" s="1">
-        <x:v>63500</x:v>
+        <x:v>68500</x:v>
       </x:c>
     </x:row>
     <x:row r="1422" spans="1:7">
@@ -39039,7 +39039,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C1432" s="1">
-        <x:v>51500</x:v>
+        <x:v>54000</x:v>
       </x:c>
       <x:c r="D1432" s="1">
         <x:v>0</x:v>
@@ -39051,7 +39051,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1432" s="1">
-        <x:v>51500</x:v>
+        <x:v>54000</x:v>
       </x:c>
     </x:row>
     <x:row r="1433" spans="1:7">
@@ -39292,7 +39292,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C1443" s="1">
-        <x:v>29000</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D1443" s="1">
         <x:v>0</x:v>
@@ -39304,7 +39304,7 @@
         <x:v>17100</x:v>
       </x:c>
       <x:c r="G1443" s="1">
-        <x:v>46100</x:v>
+        <x:v>51100</x:v>
       </x:c>
     </x:row>
     <x:row r="1444" spans="1:7">
@@ -40005,7 +40005,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C1474" s="1">
-        <x:v>45500</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D1474" s="1">
         <x:v>0</x:v>
@@ -40017,7 +40017,7 @@
         <x:v>20500</x:v>
       </x:c>
       <x:c r="G1474" s="1">
-        <x:v>66000</x:v>
+        <x:v>68500</x:v>
       </x:c>
     </x:row>
     <x:row r="1475" spans="1:7">
@@ -40120,7 +40120,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C1479" s="1">
-        <x:v>16590</x:v>
+        <x:v>17590</x:v>
       </x:c>
       <x:c r="D1479" s="1">
         <x:v>0</x:v>
@@ -40132,7 +40132,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1479" s="1">
-        <x:v>16590</x:v>
+        <x:v>17590</x:v>
       </x:c>
     </x:row>
     <x:row r="1480" spans="1:7">
@@ -41638,7 +41638,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C1545" s="1">
-        <x:v>10000</x:v>
+        <x:v>12500</x:v>
       </x:c>
       <x:c r="D1545" s="1">
         <x:v>0</x:v>
@@ -41650,7 +41650,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="G1545" s="1">
-        <x:v>10250</x:v>
+        <x:v>12750</x:v>
       </x:c>
     </x:row>
     <x:row r="1546" spans="1:7">
@@ -42282,7 +42282,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C1573" s="1">
-        <x:v>48370</x:v>
+        <x:v>52870</x:v>
       </x:c>
       <x:c r="D1573" s="1">
         <x:v>0</x:v>
@@ -42294,7 +42294,7 @@
         <x:v>8800</x:v>
       </x:c>
       <x:c r="G1573" s="1">
-        <x:v>57170</x:v>
+        <x:v>61670</x:v>
       </x:c>
     </x:row>
     <x:row r="1574" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -43271,7 +43271,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C1616" s="1">
-        <x:v>21640</x:v>
+        <x:v>22640</x:v>
       </x:c>
       <x:c r="D1616" s="1">
         <x:v>0</x:v>
@@ -43283,7 +43283,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1616" s="1">
-        <x:v>21640</x:v>
+        <x:v>22640</x:v>
       </x:c>
     </x:row>
     <x:row r="1617" spans="1:7">
@@ -43981,10 +43981,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43993,10 +43993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44004,10 +44004,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44016,10 +44016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44260,7 +44260,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C1659" s="1">
-        <x:v>60090</x:v>
+        <x:v>65090</x:v>
       </x:c>
       <x:c r="D1659" s="1">
         <x:v>0</x:v>
@@ -44272,7 +44272,7 @@
         <x:v>61001</x:v>
       </x:c>
       <x:c r="G1659" s="1">
-        <x:v>121091</x:v>
+        <x:v>126091</x:v>
       </x:c>
     </x:row>
     <x:row r="1660" spans="1:7">
@@ -44444,7 +44444,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="C1667" s="1">
-        <x:v>66500</x:v>
+        <x:v>70500</x:v>
       </x:c>
       <x:c r="D1667" s="1">
         <x:v>0</x:v>
@@ -44456,7 +44456,7 @@
         <x:v>-5600</x:v>
       </x:c>
       <x:c r="G1667" s="1">
-        <x:v>60900</x:v>
+        <x:v>64900</x:v>
       </x:c>
     </x:row>
     <x:row r="1668" spans="1:7">
@@ -45269,10 +45269,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1703" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1703" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1703" s="1">
         <x:v>0</x:v>
@@ -45281,10 +45281,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1703" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1703" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1704" spans="1:7">
@@ -45292,10 +45292,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1704" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45304,10 +45304,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1704" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>20500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">
@@ -48262,7 +48262,7 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="C1833" s="1">
-        <x:v>98500</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D1833" s="1">
         <x:v>0</x:v>
@@ -48274,7 +48274,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="G1833" s="1">
-        <x:v>103500</x:v>
+        <x:v>105000</x:v>
       </x:c>
     </x:row>
     <x:row r="1834" spans="1:7">
@@ -48722,7 +48722,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C1853" s="1">
-        <x:v>64680</x:v>
+        <x:v>67180</x:v>
       </x:c>
       <x:c r="D1853" s="1">
         <x:v>0</x:v>
@@ -48734,7 +48734,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1853" s="1">
-        <x:v>64680</x:v>
+        <x:v>67180</x:v>
       </x:c>
     </x:row>
     <x:row r="1854" spans="1:7">
@@ -48814,7 +48814,7 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="C1857" s="1">
-        <x:v>20135</x:v>
+        <x:v>22635</x:v>
       </x:c>
       <x:c r="D1857" s="1">
         <x:v>0</x:v>
@@ -48826,7 +48826,7 @@
         <x:v>5200</x:v>
       </x:c>
       <x:c r="G1857" s="1">
-        <x:v>25335</x:v>
+        <x:v>27835</x:v>
       </x:c>
     </x:row>
     <x:row r="1858" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30066,10 +30066,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1042" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1042" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1042" s="1">
         <x:v>0</x:v>
@@ -30078,10 +30078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1042" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1042" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1043" spans="1:7">
@@ -30089,10 +30089,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1043" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1043" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1043" s="1">
         <x:v>0</x:v>
@@ -30101,10 +30101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1043" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1043" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1044" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -45269,10 +45269,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1703" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1703" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1703" s="1">
         <x:v>0</x:v>
@@ -45281,10 +45281,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1703" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1703" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1704" spans="1:7">
@@ -45292,10 +45292,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1704" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45304,10 +45304,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1704" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -21786,10 +21786,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21798,10 +21798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21809,10 +21809,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21821,10 +21821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -35402,10 +35402,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35414,10 +35414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35425,10 +35425,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35437,10 +35437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21786,10 +21786,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -21798,10 +21798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -21809,10 +21809,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -21821,10 +21821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -35402,10 +35402,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35414,10 +35414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35425,10 +35425,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35437,10 +35437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -7874,7 +7874,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C77" s="1">
-        <x:v>45500</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D77" s="1">
         <x:v>0</x:v>
@@ -7886,7 +7886,7 @@
         <x:v>1045</x:v>
       </x:c>
       <x:c r="G77" s="1">
-        <x:v>46545</x:v>
+        <x:v>49045</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
@@ -8469,10 +8469,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C103" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>0</x:v>
@@ -8481,10 +8481,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G103" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -8492,10 +8492,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8504,10 +8504,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -10772,7 +10772,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C203" s="1">
-        <x:v>4000</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="D203" s="1">
         <x:v>0</x:v>
@@ -10784,7 +10784,7 @@
         <x:v>2166</x:v>
       </x:c>
       <x:c r="G203" s="1">
-        <x:v>6166</x:v>
+        <x:v>8666</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
@@ -11255,7 +11255,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C224" s="1">
-        <x:v>4090</x:v>
+        <x:v>4230</x:v>
       </x:c>
       <x:c r="D224" s="1">
         <x:v>0</x:v>
@@ -11267,7 +11267,7 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>5024</x:v>
+        <x:v>5164</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -12336,7 +12336,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C271" s="1">
-        <x:v>31500</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D271" s="1">
         <x:v>0</x:v>
@@ -12348,7 +12348,7 @@
         <x:v>2166</x:v>
       </x:c>
       <x:c r="G271" s="1">
-        <x:v>33666</x:v>
+        <x:v>36166</x:v>
       </x:c>
     </x:row>
     <x:row r="272" spans="1:7">
@@ -12520,7 +12520,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C279" s="1">
-        <x:v>27000</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D279" s="1">
         <x:v>0</x:v>
@@ -12532,7 +12532,7 @@
         <x:v>1940</x:v>
       </x:c>
       <x:c r="G279" s="1">
-        <x:v>28940</x:v>
+        <x:v>31440</x:v>
       </x:c>
     </x:row>
     <x:row r="280" spans="1:7">
@@ -13417,7 +13417,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C318" s="1">
-        <x:v>90020</x:v>
+        <x:v>91020</x:v>
       </x:c>
       <x:c r="D318" s="1">
         <x:v>0</x:v>
@@ -13429,7 +13429,7 @@
         <x:v>5200</x:v>
       </x:c>
       <x:c r="G318" s="1">
-        <x:v>95220</x:v>
+        <x:v>96220</x:v>
       </x:c>
     </x:row>
     <x:row r="319" spans="1:7">
@@ -13946,7 +13946,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C341" s="1">
-        <x:v>65000</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="D341" s="1">
         <x:v>0</x:v>
@@ -13958,7 +13958,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G341" s="1">
-        <x:v>65000</x:v>
+        <x:v>66000</x:v>
       </x:c>
     </x:row>
     <x:row r="342" spans="1:7">
@@ -18155,7 +18155,7 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>34500</x:v>
+        <x:v>35500</x:v>
       </x:c>
       <x:c r="D524" s="1">
         <x:v>0</x:v>
@@ -18167,7 +18167,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>34500</x:v>
+        <x:v>35500</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -19535,7 +19535,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C584" s="1">
-        <x:v>16090</x:v>
+        <x:v>17090</x:v>
       </x:c>
       <x:c r="D584" s="1">
         <x:v>0</x:v>
@@ -19547,7 +19547,7 @@
         <x:v>26050</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>42140</x:v>
+        <x:v>43140</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -19558,7 +19558,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>7500</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -19570,7 +19570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>7500</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -19972,7 +19972,7 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="D603" s="1">
         <x:v>0</x:v>
@@ -19984,7 +19984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>20000</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -20317,7 +20317,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>48000</x:v>
+        <x:v>53000</x:v>
       </x:c>
       <x:c r="D618" s="1">
         <x:v>0</x:v>
@@ -20329,7 +20329,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>50000</x:v>
+        <x:v>55000</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
@@ -22571,7 +22571,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>142000</x:v>
+        <x:v>145500</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -22583,7 +22583,7 @@
         <x:v>18300</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>160300</x:v>
+        <x:v>163800</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -23997,7 +23997,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>18000</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="D778" s="1">
         <x:v>0</x:v>
@@ -24009,7 +24009,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>18000</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -25236,10 +25236,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C832" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D832" s="1">
         <x:v>0</x:v>
@@ -25248,10 +25248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F832" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G832" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="833" spans="1:7">
@@ -25259,10 +25259,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C833" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D833" s="1">
         <x:v>0</x:v>
@@ -25271,10 +25271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F833" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G833" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:7">
@@ -26021,7 +26021,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C866" s="1">
-        <x:v>132590</x:v>
+        <x:v>135090</x:v>
       </x:c>
       <x:c r="D866" s="1">
         <x:v>0</x:v>
@@ -26033,7 +26033,7 @@
         <x:v>8750</x:v>
       </x:c>
       <x:c r="G866" s="1">
-        <x:v>141340</x:v>
+        <x:v>143840</x:v>
       </x:c>
     </x:row>
     <x:row r="867" spans="1:7">
@@ -30621,7 +30621,7 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="C1066" s="1">
-        <x:v>62780</x:v>
+        <x:v>67780</x:v>
       </x:c>
       <x:c r="D1066" s="1">
         <x:v>0</x:v>
@@ -30633,7 +30633,7 @@
         <x:v>14100</x:v>
       </x:c>
       <x:c r="G1066" s="1">
-        <x:v>76880</x:v>
+        <x:v>81880</x:v>
       </x:c>
     </x:row>
     <x:row r="1067" spans="1:7">
@@ -30664,10 +30664,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1068" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1068" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1068" s="1">
         <x:v>0</x:v>
@@ -30676,10 +30676,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1068" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1068" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1069" spans="1:7">
@@ -30687,10 +30687,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1069" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1069" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1069" s="1">
         <x:v>0</x:v>
@@ -30699,10 +30699,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1069" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1069" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1070" spans="1:7">
@@ -31426,7 +31426,7 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="C1101" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="D1101" s="1">
         <x:v>0</x:v>
@@ -31438,7 +31438,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G1101" s="1">
-        <x:v>31000</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="1102" spans="1:7">
@@ -31550,10 +31550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1106" s="1">
-        <x:v>8180</x:v>
+        <x:v>8430</x:v>
       </x:c>
       <x:c r="G1106" s="1">
-        <x:v>16680</x:v>
+        <x:v>16930</x:v>
       </x:c>
     </x:row>
     <x:row r="1107" spans="1:7">
@@ -32024,7 +32024,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C1127" s="1">
-        <x:v>30000</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="D1127" s="1">
         <x:v>0</x:v>
@@ -32036,7 +32036,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="G1127" s="1">
-        <x:v>30500</x:v>
+        <x:v>35500</x:v>
       </x:c>
     </x:row>
     <x:row r="1128" spans="1:7">
@@ -32392,7 +32392,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C1143" s="1">
-        <x:v>6000</x:v>
+        <x:v>6090</x:v>
       </x:c>
       <x:c r="D1143" s="1">
         <x:v>0</x:v>
@@ -32404,7 +32404,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1143" s="1">
-        <x:v>6000</x:v>
+        <x:v>6090</x:v>
       </x:c>
     </x:row>
     <x:row r="1144" spans="1:7">
@@ -33289,7 +33289,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C1182" s="1">
-        <x:v>10000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D1182" s="1">
         <x:v>0</x:v>
@@ -33301,7 +33301,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1182" s="1">
-        <x:v>10000</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="1183" spans="1:7">
@@ -34370,7 +34370,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1229" s="1">
-        <x:v>6000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1229" s="1">
         <x:v>0</x:v>
@@ -34382,7 +34382,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1229" s="1">
-        <x:v>6000</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1230" spans="1:7">
@@ -35402,10 +35402,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35414,10 +35414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35425,10 +35425,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35437,10 +35437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -35681,7 +35681,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C1286" s="1">
-        <x:v>19500</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="D1286" s="1">
         <x:v>0</x:v>
@@ -35693,7 +35693,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1286" s="1">
-        <x:v>19500</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="1287" spans="1:7">
@@ -36049,7 +36049,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C1302" s="1">
-        <x:v>7000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1302" s="1">
         <x:v>0</x:v>
@@ -36061,7 +36061,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1302" s="1">
-        <x:v>7000</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1303" spans="1:7">
@@ -39292,7 +39292,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C1443" s="1">
-        <x:v>34000</x:v>
+        <x:v>39000</x:v>
       </x:c>
       <x:c r="D1443" s="1">
         <x:v>0</x:v>
@@ -39304,7 +39304,7 @@
         <x:v>17100</x:v>
       </x:c>
       <x:c r="G1443" s="1">
-        <x:v>51100</x:v>
+        <x:v>56100</x:v>
       </x:c>
     </x:row>
     <x:row r="1444" spans="1:7">
@@ -40350,7 +40350,7 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="C1489" s="1">
-        <x:v>59500</x:v>
+        <x:v>64500</x:v>
       </x:c>
       <x:c r="D1489" s="1">
         <x:v>0</x:v>
@@ -40362,7 +40362,7 @@
         <x:v>9000</x:v>
       </x:c>
       <x:c r="G1489" s="1">
-        <x:v>68500</x:v>
+        <x:v>73500</x:v>
       </x:c>
     </x:row>
     <x:row r="1490" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -40994,7 +40994,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1517" s="1">
-        <x:v>135500</x:v>
+        <x:v>138000</x:v>
       </x:c>
       <x:c r="D1517" s="1">
         <x:v>0</x:v>
@@ -41006,7 +41006,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1517" s="1">
-        <x:v>135500</x:v>
+        <x:v>138000</x:v>
       </x:c>
     </x:row>
     <x:row r="1518" spans="1:7">
@@ -42673,7 +42673,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C1590" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1590" s="1">
         <x:v>0</x:v>
@@ -42685,7 +42685,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1590" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1591" spans="1:7">
@@ -43432,7 +43432,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1623" s="1">
-        <x:v>43500</x:v>
+        <x:v>46000</x:v>
       </x:c>
       <x:c r="D1623" s="1">
         <x:v>0</x:v>
@@ -43444,7 +43444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1623" s="1">
-        <x:v>43500</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="1624" spans="1:7">
@@ -43924,10 +43924,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1644" s="1">
-        <x:v>1000</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G1644" s="1">
-        <x:v>57000</x:v>
+        <x:v>64000</x:v>
       </x:c>
     </x:row>
     <x:row r="1645" spans="1:7">
@@ -43981,10 +43981,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43993,10 +43993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44004,10 +44004,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44016,10 +44016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -45870,7 +45870,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>40680</x:v>
+        <x:v>41680</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45882,7 +45882,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>40680</x:v>
+        <x:v>41680</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -46514,7 +46514,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1757" s="1">
-        <x:v>57635</x:v>
+        <x:v>60135</x:v>
       </x:c>
       <x:c r="D1757" s="1">
         <x:v>0</x:v>
@@ -46526,7 +46526,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1757" s="1">
-        <x:v>57635</x:v>
+        <x:v>60135</x:v>
       </x:c>
     </x:row>
     <x:row r="1758" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8469,10 +8469,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C103" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>0</x:v>
@@ -8481,10 +8481,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G103" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
@@ -8492,10 +8492,10 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8504,10 +8504,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -25236,10 +25236,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C832" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D832" s="1">
         <x:v>0</x:v>
@@ -25248,10 +25248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F832" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G832" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="833" spans="1:7">
@@ -25259,10 +25259,10 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C833" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D833" s="1">
         <x:v>0</x:v>
@@ -25271,10 +25271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F833" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G833" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:7">
@@ -27007,10 +27007,10 @@
         <x:v>957</x:v>
       </x:c>
       <x:c r="B909" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C909" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D909" s="1">
         <x:v>0</x:v>
@@ -27019,10 +27019,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F909" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G909" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="910" spans="1:7">
@@ -27030,10 +27030,10 @@
         <x:v>957</x:v>
       </x:c>
       <x:c r="B910" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C910" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D910" s="1">
         <x:v>0</x:v>
@@ -27042,10 +27042,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F910" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G910" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="911" spans="1:7">
@@ -30664,10 +30664,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1068" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1068" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1068" s="1">
         <x:v>0</x:v>
@@ -30676,10 +30676,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1068" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1068" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1069" spans="1:7">
@@ -30687,10 +30687,10 @@
         <x:v>1113</x:v>
       </x:c>
       <x:c r="B1069" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1069" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1069" s="1">
         <x:v>0</x:v>
@@ -30699,10 +30699,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1069" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1069" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1070" spans="1:7">
@@ -35402,10 +35402,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1274" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C1274" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1274" s="1">
         <x:v>0</x:v>
@@ -35414,10 +35414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1274" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1274" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1275" spans="1:7">
@@ -35425,10 +35425,10 @@
         <x:v>1316</x:v>
       </x:c>
       <x:c r="B1275" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1275" s="1">
         <x:v>0</x:v>
@@ -35437,10 +35437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1275" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1275" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1276" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -43981,10 +43981,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -43993,10 +43993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44004,10 +44004,10 @@
         <x:v>1682</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44016,10 +44016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -18888,7 +18888,7 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>0</x:v>
@@ -18900,10 +18900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -18911,7 +18911,7 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>0</x:v>
@@ -18923,10 +18923,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -27007,10 +27007,10 @@
         <x:v>957</x:v>
       </x:c>
       <x:c r="B909" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C909" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D909" s="1">
         <x:v>0</x:v>
@@ -27019,10 +27019,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F909" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G909" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="910" spans="1:7">
@@ -27030,10 +27030,10 @@
         <x:v>957</x:v>
       </x:c>
       <x:c r="B910" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C910" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D910" s="1">
         <x:v>0</x:v>
@@ -27042,10 +27042,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F910" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G910" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="911" spans="1:7">
@@ -30066,10 +30066,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1042" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1042" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1042" s="1">
         <x:v>0</x:v>
@@ -30078,10 +30078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1042" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1042" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1043" spans="1:7">
@@ -30089,10 +30089,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1043" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1043" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1043" s="1">
         <x:v>0</x:v>
@@ -30101,10 +30101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1043" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1043" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1044" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -40462,10 +40462,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1494" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1494" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1494" s="1">
         <x:v>0</x:v>
@@ -40474,10 +40474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1494" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1494" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1495" spans="1:7">
@@ -40485,10 +40485,10 @@
         <x:v>1534</x:v>
       </x:c>
       <x:c r="B1495" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40497,10 +40497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1495" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -45269,10 +45269,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1703" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1703" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1703" s="1">
         <x:v>0</x:v>
@@ -45281,10 +45281,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1703" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1703" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1704" spans="1:7">
@@ -45292,10 +45292,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1704" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45304,10 +45304,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1704" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -45614,10 +45614,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45626,10 +45626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45637,10 +45637,10 @@
         <x:v>1750</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45649,10 +45649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -18888,7 +18888,7 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>0</x:v>
@@ -18900,10 +18900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -18911,7 +18911,7 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>0</x:v>
@@ -18923,10 +18923,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -30066,10 +30066,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1042" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1042" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1042" s="1">
         <x:v>0</x:v>
@@ -30078,10 +30078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1042" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1042" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1043" spans="1:7">
@@ -30089,10 +30089,10 @@
         <x:v>1088</x:v>
       </x:c>
       <x:c r="B1043" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1043" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1043" s="1">
         <x:v>0</x:v>
@@ -30101,10 +30101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1043" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1043" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1044" spans="1:7">
@@ -32182,10 +32182,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1134" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1134" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1134" s="1">
         <x:v>0</x:v>
@@ -32194,10 +32194,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1134" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1134" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1135" spans="1:7">
@@ -32205,10 +32205,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1135" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1135" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1135" s="1">
         <x:v>0</x:v>
@@ -32217,10 +32217,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1135" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1135" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1136" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -45269,10 +45269,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1703" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1703" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1703" s="1">
         <x:v>0</x:v>
@@ -45281,10 +45281,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1703" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1703" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1704" spans="1:7">
@@ -45292,10 +45292,10 @@
         <x:v>1737</x:v>
       </x:c>
       <x:c r="B1704" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45304,10 +45304,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1704" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32182,10 +32182,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1134" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1134" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1134" s="1">
         <x:v>0</x:v>
@@ -32194,10 +32194,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1134" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1134" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1135" spans="1:7">
@@ -32205,10 +32205,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1135" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1135" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1135" s="1">
         <x:v>0</x:v>
@@ -32217,10 +32217,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1135" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1135" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1136" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -42785,10 +42785,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1595" s="1">
         <x:v>0</x:v>
@@ -42797,10 +42797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1595" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1595" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1596" spans="1:7">
@@ -42808,10 +42808,10 @@
         <x:v>1632</x:v>
       </x:c>
       <x:c r="B1596" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1596" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1596" s="1">
         <x:v>0</x:v>
@@ -42820,10 +42820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1596" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1596" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1597" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16887,10 +16887,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -16899,10 +16899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -16910,10 +16910,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -16922,10 +16922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -32182,10 +32182,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1134" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1134" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1134" s="1">
         <x:v>0</x:v>
@@ -32194,10 +32194,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1134" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1134" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1135" spans="1:7">
@@ -32205,10 +32205,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1135" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1135" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1135" s="1">
         <x:v>0</x:v>
@@ -32217,10 +32217,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1135" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1135" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1136" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">
@@ -49064,10 +49064,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1868" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1868" s="1">
         <x:v>0</x:v>
@@ -49076,10 +49076,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1868" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1868" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1869" spans="1:7">
@@ -49087,10 +49087,10 @@
         <x:v>1897</x:v>
       </x:c>
       <x:c r="B1869" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1869" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1869" s="1">
         <x:v>0</x:v>
@@ -49099,10 +49099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1869" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1869" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1870" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32182,10 +32182,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1134" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C1134" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1134" s="1">
         <x:v>0</x:v>
@@ -32194,10 +32194,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1134" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1134" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1135" spans="1:7">
@@ -32205,10 +32205,10 @@
         <x:v>1178</x:v>
       </x:c>
       <x:c r="B1135" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1135" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1135" s="1">
         <x:v>0</x:v>
@@ -32217,10 +32217,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1135" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1135" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1136" spans="1:7">
@@ -35839,7 +35839,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1293" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1293" s="1">
         <x:v>0</x:v>
@@ -35851,10 +35851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1293" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1294" spans="1:7">
@@ -35862,7 +35862,7 @@
         <x:v>1335</x:v>
       </x:c>
       <x:c r="B1294" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1294" s="1">
         <x:v>0</x:v>
@@ -35874,10 +35874,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1294" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1295" spans="1:7">
@@ -37219,10 +37219,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1353" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1353" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1353" s="1">
         <x:v>0</x:v>
@@ -37231,10 +37231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1353" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1354" spans="1:7">
@@ -37242,10 +37242,10 @@
         <x:v>1393</x:v>
       </x:c>
       <x:c r="B1354" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C1354" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1354" s="1">
         <x:v>0</x:v>
@@ -37254,10 +37254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1354" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1354" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1355" spans="1:7">
@@ -43567,10 +43567,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1629" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1629" s="1">
         <x:v>0</x:v>
@@ -43579,10 +43579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1629" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1629" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1630" spans="1:7">
@@ -43590,10 +43590,10 @@
         <x:v>1665</x:v>
       </x:c>
       <x:c r="B1630" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1630" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1630" s="1">
         <x:v>0</x:v>
@@ -43602,10 +43602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1630" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1630" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1631" spans="1:7">
@@ -45430,10 +45430,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45442,10 +45442,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45453,10 +45453,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45465,10 +45465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -47017,10 +47017,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -47032,7 +47032,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -47040,10 +47040,10 @@
         <x:v>1810</x:v>
       </x:c>
       <x:c r="B1780" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C1780" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1780" s="1">
         <x:v>0</x:v>
@@ -47055,7 +47055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1780" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1781" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8498,10 +8498,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8510,10 +8510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8521,10 +8521,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8533,10 +8533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -21838,10 +21838,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -21850,10 +21850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -21861,10 +21861,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21873,10 +21873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -27749,10 +27749,10 @@
         <x:v>988</x:v>
       </x:c>
       <x:c r="B941" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C941" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D941" s="1">
         <x:v>0</x:v>
@@ -27761,10 +27761,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F941" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G941" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="942" spans="1:7">
@@ -27772,10 +27772,10 @@
         <x:v>988</x:v>
       </x:c>
       <x:c r="B942" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C942" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D942" s="1">
         <x:v>0</x:v>
@@ -27784,10 +27784,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F942" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G942" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="943" spans="1:7">
@@ -40514,10 +40514,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1496" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1496" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1496" s="1">
         <x:v>0</x:v>
@@ -40526,10 +40526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1496" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1496" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1497" spans="1:7">
@@ -40537,10 +40537,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40549,10 +40549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -40514,10 +40514,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1496" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1496" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1496" s="1">
         <x:v>0</x:v>
@@ -40526,10 +40526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1496" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1496" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1497" spans="1:7">
@@ -40537,10 +40537,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40549,10 +40549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -42837,10 +42837,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1597" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1597" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1597" s="1">
         <x:v>0</x:v>
@@ -42849,10 +42849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1597" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1597" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1598" spans="1:7">
@@ -42860,10 +42860,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42872,10 +42872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -43619,10 +43619,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1631" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1631" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1631" s="1">
         <x:v>0</x:v>
@@ -43631,10 +43631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1631" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1631" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1632" spans="1:7">
@@ -43642,10 +43642,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43654,10 +43654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -45666,10 +45666,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45678,10 +45678,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -45689,10 +45689,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1721" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1721" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1721" s="1">
         <x:v>0</x:v>
@@ -45701,10 +45701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1721" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1721" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1722" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -35454,10 +35454,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1276" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1276" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1276" s="1">
         <x:v>0</x:v>
@@ -35466,10 +35466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1276" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1276" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1277" spans="1:7">
@@ -35477,10 +35477,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35489,10 +35489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -47069,10 +47069,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1781" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1781" s="1">
         <x:v>0</x:v>
@@ -47084,7 +47084,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1782" spans="1:7">
@@ -47092,10 +47092,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47107,7 +47107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16939,10 +16939,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16951,10 +16951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16962,10 +16962,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16974,10 +16974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -35454,10 +35454,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1276" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1276" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1276" s="1">
         <x:v>0</x:v>
@@ -35466,10 +35466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1276" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1276" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1277" spans="1:7">
@@ -35477,10 +35477,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35489,10 +35489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -40514,10 +40514,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1496" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1496" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1496" s="1">
         <x:v>0</x:v>
@@ -40526,10 +40526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1496" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1496" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1497" spans="1:7">
@@ -40537,10 +40537,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40549,10 +40549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -42837,10 +42837,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1597" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1597" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1597" s="1">
         <x:v>0</x:v>
@@ -42849,10 +42849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1597" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1597" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1598" spans="1:7">
@@ -42860,10 +42860,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42872,10 +42872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -45666,10 +45666,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45678,10 +45678,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -45689,10 +45689,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1721" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1721" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1721" s="1">
         <x:v>0</x:v>
@@ -45701,10 +45701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1721" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1721" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1722" spans="1:7">
@@ -47069,10 +47069,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1781" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1781" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1781" s="1">
         <x:v>0</x:v>
@@ -47084,7 +47084,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1781" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1782" spans="1:7">
@@ -47092,10 +47092,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47107,7 +47107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16939,10 +16939,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16951,10 +16951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16962,10 +16962,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16974,10 +16974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -43619,10 +43619,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1631" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1631" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1631" s="1">
         <x:v>0</x:v>
@@ -43631,10 +43631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1631" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1631" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1632" spans="1:7">
@@ -43642,10 +43642,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43654,10 +43654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -35454,10 +35454,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1276" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1276" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1276" s="1">
         <x:v>0</x:v>
@@ -35466,10 +35466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1276" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1276" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1277" spans="1:7">
@@ -35477,10 +35477,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35489,10 +35489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -35891,7 +35891,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1295" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1295" s="1">
         <x:v>0</x:v>
@@ -35903,10 +35903,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1295" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1295" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1296" spans="1:7">
@@ -35914,7 +35914,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35926,10 +35926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -37271,10 +37271,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1355" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1355" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1355" s="1">
         <x:v>0</x:v>
@@ -37283,10 +37283,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1355" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1355" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1356" spans="1:7">
@@ -37294,10 +37294,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37306,10 +37306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -40514,10 +40514,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1496" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1496" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1496" s="1">
         <x:v>0</x:v>
@@ -40526,10 +40526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1496" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1496" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1497" spans="1:7">
@@ -40537,10 +40537,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40549,10 +40549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -42837,10 +42837,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1597" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1597" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1597" s="1">
         <x:v>0</x:v>
@@ -42849,10 +42849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1597" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1597" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1598" spans="1:7">
@@ -42860,10 +42860,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42872,10 +42872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -43619,10 +43619,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1631" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1631" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1631" s="1">
         <x:v>0</x:v>
@@ -43631,10 +43631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1631" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1631" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1632" spans="1:7">
@@ -43642,10 +43642,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43654,10 +43654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -6776,7 +6776,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>13000</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>0</x:v>
@@ -6788,7 +6788,7 @@
         <x:v>8800</x:v>
       </x:c>
       <x:c r="G29" s="1">
-        <x:v>21800</x:v>
+        <x:v>24800</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -7006,7 +7006,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>44000</x:v>
+        <x:v>46000</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>0</x:v>
@@ -7018,7 +7018,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G39" s="1">
-        <x:v>44000</x:v>
+        <x:v>46000</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -11307,7 +11307,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C226" s="1">
-        <x:v>4230</x:v>
+        <x:v>5230</x:v>
       </x:c>
       <x:c r="D226" s="1">
         <x:v>0</x:v>
@@ -11319,7 +11319,7 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="G226" s="1">
-        <x:v>5164</x:v>
+        <x:v>6164</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -12388,7 +12388,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C273" s="1">
-        <x:v>34000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D273" s="1">
         <x:v>0</x:v>
@@ -12400,7 +12400,7 @@
         <x:v>2166</x:v>
       </x:c>
       <x:c r="G273" s="1">
-        <x:v>36166</x:v>
+        <x:v>38666</x:v>
       </x:c>
     </x:row>
     <x:row r="274" spans="1:7">
@@ -13584,7 +13584,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C325" s="1">
-        <x:v>50000</x:v>
+        <x:v>51000</x:v>
       </x:c>
       <x:c r="D325" s="1">
         <x:v>0</x:v>
@@ -13596,7 +13596,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G325" s="1">
-        <x:v>50000</x:v>
+        <x:v>51000</x:v>
       </x:c>
     </x:row>
     <x:row r="326" spans="1:7">
@@ -15746,7 +15746,7 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="C419" s="1">
-        <x:v>27010</x:v>
+        <x:v>28010</x:v>
       </x:c>
       <x:c r="D419" s="1">
         <x:v>0</x:v>
@@ -15758,7 +15758,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G419" s="1">
-        <x:v>27010</x:v>
+        <x:v>28010</x:v>
       </x:c>
     </x:row>
     <x:row r="420" spans="1:7">
@@ -21749,7 +21749,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>41500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -21761,7 +21761,7 @@
         <x:v>73590</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>115090</x:v>
+        <x:v>117590</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -24049,7 +24049,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>22000</x:v>
+        <x:v>23000</x:v>
       </x:c>
       <x:c r="D780" s="1">
         <x:v>0</x:v>
@@ -24061,7 +24061,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>22000</x:v>
+        <x:v>23000</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
@@ -25360,7 +25360,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>16000</x:v>
+        <x:v>21000</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -25372,7 +25372,7 @@
         <x:v>8500</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>24500</x:v>
+        <x:v>29500</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
@@ -29776,7 +29776,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C1029" s="1">
-        <x:v>18500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D1029" s="1">
         <x:v>0</x:v>
@@ -29788,7 +29788,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G1029" s="1">
-        <x:v>19500</x:v>
+        <x:v>20500</x:v>
       </x:c>
     </x:row>
     <x:row r="1030" spans="1:7">
@@ -30118,10 +30118,10 @@
         <x:v>1090</x:v>
       </x:c>
       <x:c r="B1044" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1044" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1044" s="1">
         <x:v>0</x:v>
@@ -30130,10 +30130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1044" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1044" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1045" spans="1:7">
@@ -30141,10 +30141,10 @@
         <x:v>1090</x:v>
       </x:c>
       <x:c r="B1045" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1045" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1045" s="1">
         <x:v>0</x:v>
@@ -30153,10 +30153,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1045" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1045" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1046" spans="1:7">
@@ -30673,7 +30673,7 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="C1068" s="1">
-        <x:v>67780</x:v>
+        <x:v>70280</x:v>
       </x:c>
       <x:c r="D1068" s="1">
         <x:v>0</x:v>
@@ -30685,7 +30685,7 @@
         <x:v>14100</x:v>
       </x:c>
       <x:c r="G1068" s="1">
-        <x:v>81880</x:v>
+        <x:v>84380</x:v>
       </x:c>
     </x:row>
     <x:row r="1069" spans="1:7">
@@ -30716,10 +30716,10 @@
         <x:v>1115</x:v>
       </x:c>
       <x:c r="B1070" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1070" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1070" s="1">
         <x:v>0</x:v>
@@ -30728,10 +30728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1070" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1070" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1071" spans="1:7">
@@ -30739,10 +30739,10 @@
         <x:v>1115</x:v>
       </x:c>
       <x:c r="B1071" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1071" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1071" s="1">
         <x:v>0</x:v>
@@ -30751,10 +30751,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1071" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1071" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1072" spans="1:7">
@@ -32444,7 +32444,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C1145" s="1">
-        <x:v>6090</x:v>
+        <x:v>6230</x:v>
       </x:c>
       <x:c r="D1145" s="1">
         <x:v>0</x:v>
@@ -32456,7 +32456,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1145" s="1">
-        <x:v>6090</x:v>
+        <x:v>6230</x:v>
       </x:c>
     </x:row>
     <x:row r="1146" spans="1:7">
@@ -33249,7 +33249,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C1180" s="1">
-        <x:v>59000</x:v>
+        <x:v>61000</x:v>
       </x:c>
       <x:c r="D1180" s="1">
         <x:v>0</x:v>
@@ -33261,7 +33261,7 @@
         <x:v>5200</x:v>
       </x:c>
       <x:c r="G1180" s="1">
-        <x:v>64200</x:v>
+        <x:v>66200</x:v>
       </x:c>
     </x:row>
     <x:row r="1181" spans="1:7">
@@ -35891,7 +35891,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1295" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1295" s="1">
         <x:v>0</x:v>
@@ -35903,10 +35903,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1295" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1295" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1296" spans="1:7">
@@ -35914,7 +35914,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35926,10 +35926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -41046,7 +41046,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1519" s="1">
-        <x:v>138000</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="D1519" s="1">
         <x:v>0</x:v>
@@ -41058,7 +41058,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1519" s="1">
-        <x:v>138000</x:v>
+        <x:v>140000</x:v>
       </x:c>
     </x:row>
     <x:row r="1520" spans="1:7">
@@ -43619,10 +43619,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1631" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1631" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1631" s="1">
         <x:v>0</x:v>
@@ -43631,10 +43631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1631" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1631" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1632" spans="1:7">
@@ -43642,10 +43642,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43654,10 +43654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -44726,7 +44726,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C1679" s="1">
-        <x:v>7500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1679" s="1">
         <x:v>0</x:v>
@@ -44738,7 +44738,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1679" s="1">
-        <x:v>7500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1680" spans="1:7">
@@ -45301,7 +45301,7 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="C1704" s="1">
-        <x:v>126500</x:v>
+        <x:v>127500</x:v>
       </x:c>
       <x:c r="D1704" s="1">
         <x:v>0</x:v>
@@ -45313,7 +45313,7 @@
         <x:v>7474</x:v>
       </x:c>
       <x:c r="G1704" s="1">
-        <x:v>133974</x:v>
+        <x:v>134974</x:v>
       </x:c>
     </x:row>
     <x:row r="1705" spans="1:7">
@@ -47069,10 +47069,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1781" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1781" s="1">
         <x:v>0</x:v>
@@ -47084,7 +47084,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1782" spans="1:7">
@@ -47092,10 +47092,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47107,7 +47107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -48245,7 +48245,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1832" s="1">
-        <x:v>4000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1832" s="1">
         <x:v>0</x:v>
@@ -48257,7 +48257,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1832" s="1">
-        <x:v>4000</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1833" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16939,10 +16939,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16951,10 +16951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16962,10 +16962,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16974,10 +16974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -21838,10 +21838,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -21850,10 +21850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -21861,10 +21861,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21873,10 +21873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -30118,10 +30118,10 @@
         <x:v>1090</x:v>
       </x:c>
       <x:c r="B1044" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1044" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1044" s="1">
         <x:v>0</x:v>
@@ -30130,10 +30130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1044" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1044" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1045" spans="1:7">
@@ -30141,10 +30141,10 @@
         <x:v>1090</x:v>
       </x:c>
       <x:c r="B1045" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1045" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1045" s="1">
         <x:v>0</x:v>
@@ -30153,10 +30153,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1045" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1045" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1046" spans="1:7">
@@ -30716,10 +30716,10 @@
         <x:v>1115</x:v>
       </x:c>
       <x:c r="B1070" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1070" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1070" s="1">
         <x:v>0</x:v>
@@ -30728,10 +30728,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1070" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1070" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1071" spans="1:7">
@@ -30739,10 +30739,10 @@
         <x:v>1115</x:v>
       </x:c>
       <x:c r="B1071" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1071" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1071" s="1">
         <x:v>0</x:v>
@@ -30751,10 +30751,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1071" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1071" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1072" spans="1:7">
@@ -37271,10 +37271,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1355" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1355" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1355" s="1">
         <x:v>0</x:v>
@@ -37283,10 +37283,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1355" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1355" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1356" spans="1:7">
@@ -37294,10 +37294,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37306,10 +37306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -40514,10 +40514,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1496" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1496" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1496" s="1">
         <x:v>0</x:v>
@@ -40526,10 +40526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1496" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1496" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1497" spans="1:7">
@@ -40537,10 +40537,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40549,10 +40549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -42837,10 +42837,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1597" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1597" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1597" s="1">
         <x:v>0</x:v>
@@ -42849,10 +42849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1597" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1597" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1598" spans="1:7">
@@ -42860,10 +42860,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42872,10 +42872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -44033,10 +44033,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44045,10 +44045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44056,10 +44056,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1650" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1650" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1650" s="1">
         <x:v>0</x:v>
@@ -44068,10 +44068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1650" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1650" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1651" spans="1:7">
@@ -45666,10 +45666,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45678,10 +45678,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -45689,10 +45689,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1721" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1721" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1721" s="1">
         <x:v>0</x:v>
@@ -45701,10 +45701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1721" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1721" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1722" spans="1:7">
@@ -47069,10 +47069,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1781" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1781" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1781" s="1">
         <x:v>0</x:v>
@@ -47084,7 +47084,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1781" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1782" spans="1:7">
@@ -47092,10 +47092,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47107,7 +47107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8498,10 +8498,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8510,10 +8510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8521,10 +8521,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8533,10 +8533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -16939,10 +16939,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16951,10 +16951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16962,10 +16962,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16974,10 +16974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -32234,10 +32234,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1136" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1136" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1136" s="1">
         <x:v>0</x:v>
@@ -32246,10 +32246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1136" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1136" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1137" spans="1:7">
@@ -32257,10 +32257,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1137" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1137" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1137" s="1">
         <x:v>0</x:v>
@@ -32269,10 +32269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1137" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1137" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1138" spans="1:7">
@@ -42837,10 +42837,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1597" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1597" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1597" s="1">
         <x:v>0</x:v>
@@ -42849,10 +42849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1597" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1597" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1598" spans="1:7">
@@ -42860,10 +42860,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42872,10 +42872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -44033,10 +44033,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44045,10 +44045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44056,10 +44056,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1650" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1650" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1650" s="1">
         <x:v>0</x:v>
@@ -44068,10 +44068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1650" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1650" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1651" spans="1:7">
@@ -45666,10 +45666,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45678,10 +45678,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -45689,10 +45689,10 @@
         <x:v>1752</x:v>
       </x:c>
       <x:c r="B1721" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1721" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1721" s="1">
         <x:v>0</x:v>
@@ -45701,10 +45701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1721" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1721" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1722" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8498,10 +8498,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8510,10 +8510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8521,10 +8521,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8533,10 +8533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -16939,10 +16939,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16951,10 +16951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16962,10 +16962,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16974,10 +16974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -21838,10 +21838,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -21850,10 +21850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -21861,10 +21861,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21873,10 +21873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -32234,10 +32234,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1136" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1136" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1136" s="1">
         <x:v>0</x:v>
@@ -32246,10 +32246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1136" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1136" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1137" spans="1:7">
@@ -32257,10 +32257,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1137" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1137" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1137" s="1">
         <x:v>0</x:v>
@@ -32269,10 +32269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1137" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1137" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1138" spans="1:7">
@@ -35454,10 +35454,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1276" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1276" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1276" s="1">
         <x:v>0</x:v>
@@ -35466,10 +35466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1276" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1276" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1277" spans="1:7">
@@ -35477,10 +35477,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35489,10 +35489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -35891,7 +35891,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1295" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1295" s="1">
         <x:v>0</x:v>
@@ -35903,10 +35903,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1295" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1295" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1296" spans="1:7">
@@ -35914,7 +35914,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35926,10 +35926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -42837,10 +42837,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1597" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1597" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1597" s="1">
         <x:v>0</x:v>
@@ -42849,10 +42849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1597" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1597" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1598" spans="1:7">
@@ -42860,10 +42860,10 @@
         <x:v>1634</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42872,10 +42872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16939,10 +16939,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16951,10 +16951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16962,10 +16962,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16974,10 +16974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -18940,7 +18940,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C558" s="1">
         <x:v>0</x:v>
@@ -18952,10 +18952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -18963,7 +18963,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>0</x:v>
@@ -18975,10 +18975,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -35454,10 +35454,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1276" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1276" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1276" s="1">
         <x:v>0</x:v>
@@ -35466,10 +35466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1276" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1276" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1277" spans="1:7">
@@ -35477,10 +35477,10 @@
         <x:v>1318</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35489,10 +35489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -35891,7 +35891,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1295" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1295" s="1">
         <x:v>0</x:v>
@@ -35903,10 +35903,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1295" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1295" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1296" spans="1:7">
@@ -35914,7 +35914,7 @@
         <x:v>1337</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35926,10 +35926,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -40514,10 +40514,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1496" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1496" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1496" s="1">
         <x:v>0</x:v>
@@ -40526,10 +40526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1496" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1496" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1497" spans="1:7">
@@ -40537,10 +40537,10 @@
         <x:v>1536</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40549,10 +40549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -43619,10 +43619,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1631" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1631" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1631" s="1">
         <x:v>0</x:v>
@@ -43631,10 +43631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1631" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1631" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1632" spans="1:7">
@@ -43642,10 +43642,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43654,10 +43654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -44033,10 +44033,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44045,10 +44045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44056,10 +44056,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1650" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1650" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1650" s="1">
         <x:v>0</x:v>
@@ -44068,10 +44068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1650" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1650" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1651" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -47069,10 +47069,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1781" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1781" s="1">
         <x:v>0</x:v>
@@ -47084,7 +47084,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1782" spans="1:7">
@@ -47092,10 +47092,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47107,7 +47107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -18940,7 +18940,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C558" s="1">
         <x:v>0</x:v>
@@ -18952,10 +18952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -18963,7 +18963,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>0</x:v>
@@ -18975,10 +18975,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -27059,10 +27059,10 @@
         <x:v>959</x:v>
       </x:c>
       <x:c r="B911" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C911" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D911" s="1">
         <x:v>0</x:v>
@@ -27071,10 +27071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F911" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G911" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="912" spans="1:7">
@@ -27082,10 +27082,10 @@
         <x:v>959</x:v>
       </x:c>
       <x:c r="B912" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C912" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D912" s="1">
         <x:v>0</x:v>
@@ -27094,10 +27094,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F912" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G912" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="913" spans="1:7">
@@ -32234,10 +32234,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1136" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1136" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1136" s="1">
         <x:v>0</x:v>
@@ -32246,10 +32246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1136" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1136" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1137" spans="1:7">
@@ -32257,10 +32257,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1137" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1137" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1137" s="1">
         <x:v>0</x:v>
@@ -32269,10 +32269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1137" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1137" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1138" spans="1:7">
@@ -37271,10 +37271,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1355" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1355" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1355" s="1">
         <x:v>0</x:v>
@@ -37283,10 +37283,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1355" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1355" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1356" spans="1:7">
@@ -37294,10 +37294,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37306,10 +37306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -44033,10 +44033,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44045,10 +44045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44056,10 +44056,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1650" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1650" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1650" s="1">
         <x:v>0</x:v>
@@ -44068,10 +44068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1650" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1650" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1651" spans="1:7">
@@ -47069,10 +47069,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1781" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1781" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1781" s="1">
         <x:v>0</x:v>
@@ -47084,7 +47084,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1781" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1782" spans="1:7">
@@ -47092,10 +47092,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47107,7 +47107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -49116,10 +49116,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1870" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1870" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1870" s="1">
         <x:v>0</x:v>
@@ -49128,10 +49128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1870" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1870" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1871" spans="1:7">
@@ -49139,10 +49139,10 @@
         <x:v>1899</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49151,10 +49151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8498,10 +8498,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8510,10 +8510,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8521,10 +8521,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8533,10 +8533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -21838,10 +21838,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -21850,10 +21850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -21861,10 +21861,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21873,10 +21873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -32234,10 +32234,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1136" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1136" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1136" s="1">
         <x:v>0</x:v>
@@ -32246,10 +32246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1136" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1136" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1137" spans="1:7">
@@ -32257,10 +32257,10 @@
         <x:v>1180</x:v>
       </x:c>
       <x:c r="B1137" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1137" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1137" s="1">
         <x:v>0</x:v>
@@ -32269,10 +32269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1137" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1137" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1138" spans="1:7">
@@ -37271,10 +37271,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1355" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1355" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1355" s="1">
         <x:v>0</x:v>
@@ -37283,10 +37283,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1355" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1355" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1356" spans="1:7">
@@ -37294,10 +37294,10 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37306,10 +37306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -43619,10 +43619,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1631" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1631" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1631" s="1">
         <x:v>0</x:v>
@@ -43631,10 +43631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1631" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1631" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1632" spans="1:7">
@@ -43642,10 +43642,10 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43654,10 +43654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -45482,10 +45482,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45494,10 +45494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45505,10 +45505,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45517,10 +45517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -47069,10 +47069,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1781" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1781" s="1">
         <x:v>0</x:v>
@@ -47084,7 +47084,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1781" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1782" spans="1:7">
@@ -47092,10 +47092,10 @@
         <x:v>1812</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47107,7 +47107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32260,10 +32260,10 @@
         <x:v>1181</x:v>
       </x:c>
       <x:c r="B1137" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1137" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1137" s="1">
         <x:v>0</x:v>
@@ -32272,10 +32272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1137" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1137" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1138" spans="1:7">
@@ -32283,10 +32283,10 @@
         <x:v>1181</x:v>
       </x:c>
       <x:c r="B1138" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1138" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1138" s="1">
         <x:v>0</x:v>
@@ -32295,10 +32295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1138" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1138" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1139" spans="1:7">
@@ -35480,10 +35480,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35492,10 +35492,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -35503,10 +35503,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1278" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1278" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1278" s="1">
         <x:v>0</x:v>
@@ -35515,10 +35515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1278" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1278" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1279" spans="1:7">
@@ -37297,10 +37297,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37309,10 +37309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -37320,10 +37320,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1357" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1357" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1357" s="1">
         <x:v>0</x:v>
@@ -37332,10 +37332,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1357" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1357" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1358" spans="1:7">
@@ -40540,10 +40540,10 @@
         <x:v>1537</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40552,10 +40552,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -40563,10 +40563,10 @@
         <x:v>1537</x:v>
       </x:c>
       <x:c r="B1498" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1498" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1498" s="1">
         <x:v>0</x:v>
@@ -40575,10 +40575,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1498" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1498" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1499" spans="1:7">
@@ -45508,10 +45508,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45520,10 +45520,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -45531,10 +45531,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1714" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1714" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1714" s="1">
         <x:v>0</x:v>
@@ -45543,10 +45543,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1714" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1714" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1715" spans="1:7">
@@ -47095,10 +47095,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47110,7 +47110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -47118,10 +47118,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1783" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1783" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1783" s="1">
         <x:v>0</x:v>
@@ -47133,7 +47133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1783" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1784" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16942,10 +16942,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16954,10 +16954,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16965,10 +16965,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16977,10 +16977,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -20093,10 +20093,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C608" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D608" s="1">
         <x:v>0</x:v>
@@ -20105,10 +20105,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -20116,10 +20116,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C609" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D609" s="1">
         <x:v>0</x:v>
@@ -20128,10 +20128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -27775,10 +27775,10 @@
         <x:v>989</x:v>
       </x:c>
       <x:c r="B942" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C942" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D942" s="1">
         <x:v>0</x:v>
@@ -27787,10 +27787,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F942" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G942" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="943" spans="1:7">
@@ -27798,10 +27798,10 @@
         <x:v>989</x:v>
       </x:c>
       <x:c r="B943" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C943" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D943" s="1">
         <x:v>0</x:v>
@@ -27810,10 +27810,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F943" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G943" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="944" spans="1:7">
@@ -34836,22 +34836,22 @@
         <x:v>1292</x:v>
       </x:c>
       <x:c r="B1249" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C1249" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1249" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1249" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F1249" s="1">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D1249" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1249" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F1249" s="1">
-        <x:v>6400</x:v>
-      </x:c>
       <x:c r="G1249" s="1">
-        <x:v>11400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1250" spans="1:7">
@@ -34859,10 +34859,10 @@
         <x:v>1292</x:v>
       </x:c>
       <x:c r="B1250" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1250" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1250" s="1">
         <x:v>0</x:v>
@@ -34871,10 +34871,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1250" s="1">
-        <x:v>5000</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="G1250" s="1">
-        <x:v>5000</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="1251" spans="1:7">
@@ -35480,10 +35480,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35492,10 +35492,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -35503,10 +35503,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1278" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1278" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1278" s="1">
         <x:v>0</x:v>
@@ -35515,10 +35515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1278" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1278" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1279" spans="1:7">
@@ -35917,7 +35917,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35929,10 +35929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -35940,7 +35940,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1297" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1297" s="1">
         <x:v>0</x:v>
@@ -35952,10 +35952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1297" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1297" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1298" spans="1:7">
@@ -40540,10 +40540,10 @@
         <x:v>1537</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40552,10 +40552,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -40563,10 +40563,10 @@
         <x:v>1537</x:v>
       </x:c>
       <x:c r="B1498" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1498" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1498" s="1">
         <x:v>0</x:v>
@@ -40575,10 +40575,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1498" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1498" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1499" spans="1:7">
@@ -41115,7 +41115,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1522" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1522" s="1">
         <x:v>0</x:v>
@@ -41127,10 +41127,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1522" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1522" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1523" spans="1:7">
@@ -41138,7 +41138,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1523" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1523" s="1">
         <x:v>0</x:v>
@@ -41150,10 +41150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1523" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1523" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1524" spans="1:7">
@@ -43645,10 +43645,10 @@
         <x:v>1668</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43657,10 +43657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -43668,10 +43668,10 @@
         <x:v>1668</x:v>
       </x:c>
       <x:c r="B1633" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1633" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1633" s="1">
         <x:v>0</x:v>
@@ -43680,10 +43680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1633" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1633" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1634" spans="1:7">
@@ -44059,10 +44059,10 @@
         <x:v>1685</x:v>
       </x:c>
       <x:c r="B1650" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1650" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1650" s="1">
         <x:v>0</x:v>
@@ -44071,10 +44071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1650" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1650" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1651" spans="1:7">
@@ -44082,10 +44082,10 @@
         <x:v>1685</x:v>
       </x:c>
       <x:c r="B1651" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1651" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1651" s="1">
         <x:v>0</x:v>
@@ -44094,10 +44094,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1651" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1651" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1652" spans="1:7">
@@ -45347,10 +45347,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1706" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1706" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1706" s="1">
         <x:v>0</x:v>
@@ -45359,10 +45359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1706" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1706" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1707" spans="1:7">
@@ -45370,10 +45370,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1707" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1707" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1707" s="1">
         <x:v>0</x:v>
@@ -45382,10 +45382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1707" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1707" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1708" spans="1:7">
@@ -45508,10 +45508,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1713" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1713" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1713" s="1">
         <x:v>0</x:v>
@@ -45520,10 +45520,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1713" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1713" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1714" spans="1:7">
@@ -45531,10 +45531,10 @@
         <x:v>1746</x:v>
       </x:c>
       <x:c r="B1714" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1714" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1714" s="1">
         <x:v>0</x:v>
@@ -45543,10 +45543,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1714" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1714" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1715" spans="1:7">
@@ -47095,10 +47095,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47110,7 +47110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -47118,10 +47118,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1783" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1783" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1783" s="1">
         <x:v>0</x:v>
@@ -47133,7 +47133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1783" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1784" spans="1:7">
@@ -49142,10 +49142,10 @@
         <x:v>1900</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49154,10 +49154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">
@@ -49165,10 +49165,10 @@
         <x:v>1900</x:v>
       </x:c>
       <x:c r="B1872" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1872" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1872" s="1">
         <x:v>0</x:v>
@@ -49177,10 +49177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1872" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1872" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1873" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16942,10 +16942,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -16954,10 +16954,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -16965,10 +16965,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16977,10 +16977,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -20093,10 +20093,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C608" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D608" s="1">
         <x:v>0</x:v>
@@ -20105,10 +20105,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -20116,10 +20116,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C609" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D609" s="1">
         <x:v>0</x:v>
@@ -20128,10 +20128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -27775,10 +27775,10 @@
         <x:v>989</x:v>
       </x:c>
       <x:c r="B942" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C942" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D942" s="1">
         <x:v>0</x:v>
@@ -27787,10 +27787,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F942" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G942" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="943" spans="1:7">
@@ -27798,10 +27798,10 @@
         <x:v>989</x:v>
       </x:c>
       <x:c r="B943" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C943" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D943" s="1">
         <x:v>0</x:v>
@@ -27810,10 +27810,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F943" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G943" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="944" spans="1:7">
@@ -34836,10 +34836,10 @@
         <x:v>1292</x:v>
       </x:c>
       <x:c r="B1249" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1249" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1249" s="1">
         <x:v>0</x:v>
@@ -34848,10 +34848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1249" s="1">
-        <x:v>5000</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="G1249" s="1">
-        <x:v>5000</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="1250" spans="1:7">
@@ -34859,22 +34859,22 @@
         <x:v>1292</x:v>
       </x:c>
       <x:c r="B1250" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C1250" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1250" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1250" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F1250" s="1">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D1250" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1250" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F1250" s="1">
-        <x:v>6400</x:v>
-      </x:c>
       <x:c r="G1250" s="1">
-        <x:v>11400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1251" spans="1:7">
@@ -35480,10 +35480,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35492,10 +35492,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -35503,10 +35503,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1278" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1278" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1278" s="1">
         <x:v>0</x:v>
@@ -35515,10 +35515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1278" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1278" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1279" spans="1:7">
@@ -35917,7 +35917,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35929,10 +35929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -35940,7 +35940,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1297" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1297" s="1">
         <x:v>0</x:v>
@@ -35952,10 +35952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1297" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1297" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1298" spans="1:7">
@@ -41115,7 +41115,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1522" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1522" s="1">
         <x:v>0</x:v>
@@ -41127,10 +41127,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1522" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1522" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1523" spans="1:7">
@@ -41138,7 +41138,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1523" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1523" s="1">
         <x:v>0</x:v>
@@ -41150,10 +41150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1523" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1523" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1524" spans="1:7">
@@ -42863,10 +42863,10 @@
         <x:v>1635</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42875,10 +42875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -42886,10 +42886,10 @@
         <x:v>1635</x:v>
       </x:c>
       <x:c r="B1599" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1599" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1599" s="1">
         <x:v>0</x:v>
@@ -42898,10 +42898,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1599" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1599" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1600" spans="1:7">
@@ -43645,10 +43645,10 @@
         <x:v>1668</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43657,10 +43657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -43668,10 +43668,10 @@
         <x:v>1668</x:v>
       </x:c>
       <x:c r="B1633" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1633" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1633" s="1">
         <x:v>0</x:v>
@@ -43680,10 +43680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1633" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1633" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1634" spans="1:7">
@@ -44059,10 +44059,10 @@
         <x:v>1685</x:v>
       </x:c>
       <x:c r="B1650" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1650" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1650" s="1">
         <x:v>0</x:v>
@@ -44071,10 +44071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1650" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1650" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1651" spans="1:7">
@@ -44082,10 +44082,10 @@
         <x:v>1685</x:v>
       </x:c>
       <x:c r="B1651" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1651" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1651" s="1">
         <x:v>0</x:v>
@@ -44094,10 +44094,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1651" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1651" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1652" spans="1:7">
@@ -45347,10 +45347,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1706" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1706" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1706" s="1">
         <x:v>0</x:v>
@@ -45359,10 +45359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1706" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1706" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1707" spans="1:7">
@@ -45370,10 +45370,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1707" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1707" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1707" s="1">
         <x:v>0</x:v>
@@ -45382,10 +45382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1707" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1707" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1708" spans="1:7">
@@ -45692,10 +45692,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1721" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1721" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1721" s="1">
         <x:v>0</x:v>
@@ -45704,10 +45704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1721" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1721" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1722" spans="1:7">
@@ -45715,10 +45715,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45727,10 +45727,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -47095,10 +47095,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47110,7 +47110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -47118,10 +47118,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1783" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1783" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1783" s="1">
         <x:v>0</x:v>
@@ -47133,7 +47133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1783" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1784" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30144,10 +30144,10 @@
         <x:v>1091</x:v>
       </x:c>
       <x:c r="B1045" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1045" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1045" s="1">
         <x:v>0</x:v>
@@ -30156,10 +30156,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1045" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1045" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1046" spans="1:7">
@@ -30167,10 +30167,10 @@
         <x:v>1091</x:v>
       </x:c>
       <x:c r="B1046" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1046" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1046" s="1">
         <x:v>0</x:v>
@@ -30179,10 +30179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1046" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1046" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1047" spans="1:7">
@@ -35917,7 +35917,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35929,10 +35929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -35940,7 +35940,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1297" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1297" s="1">
         <x:v>0</x:v>
@@ -35952,10 +35952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1297" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1297" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1298" spans="1:7">
@@ -37297,10 +37297,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37309,10 +37309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -37320,10 +37320,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1357" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1357" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1357" s="1">
         <x:v>0</x:v>
@@ -37332,10 +37332,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1357" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1357" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1358" spans="1:7">
@@ -41115,7 +41115,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1522" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1522" s="1">
         <x:v>0</x:v>
@@ -41127,10 +41127,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1522" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1522" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1523" spans="1:7">
@@ -41138,7 +41138,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1523" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1523" s="1">
         <x:v>0</x:v>
@@ -41150,10 +41150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1523" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1523" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1524" spans="1:7">
@@ -42863,10 +42863,10 @@
         <x:v>1635</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42875,10 +42875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -42886,10 +42886,10 @@
         <x:v>1635</x:v>
       </x:c>
       <x:c r="B1599" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1599" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1599" s="1">
         <x:v>0</x:v>
@@ -42898,10 +42898,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1599" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1599" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1600" spans="1:7">
@@ -45347,10 +45347,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1706" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1706" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1706" s="1">
         <x:v>0</x:v>
@@ -45359,10 +45359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1706" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1706" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1707" spans="1:7">
@@ -45370,10 +45370,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1707" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1707" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1707" s="1">
         <x:v>0</x:v>
@@ -45382,10 +45382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1707" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1707" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1708" spans="1:7">
@@ -49142,10 +49142,10 @@
         <x:v>1900</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49154,10 +49154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">
@@ -49165,10 +49165,10 @@
         <x:v>1900</x:v>
       </x:c>
       <x:c r="B1872" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1872" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1872" s="1">
         <x:v>0</x:v>
@@ -49177,10 +49177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1872" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1872" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1873" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8501,10 +8501,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8513,10 +8513,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8524,10 +8524,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8536,10 +8536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -21841,10 +21841,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -21853,10 +21853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -21864,10 +21864,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21876,10 +21876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -30144,10 +30144,10 @@
         <x:v>1091</x:v>
       </x:c>
       <x:c r="B1045" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1045" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1045" s="1">
         <x:v>0</x:v>
@@ -30156,10 +30156,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1045" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1045" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1046" spans="1:7">
@@ -30167,10 +30167,10 @@
         <x:v>1091</x:v>
       </x:c>
       <x:c r="B1046" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1046" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1046" s="1">
         <x:v>0</x:v>
@@ -30179,10 +30179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1046" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1046" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1047" spans="1:7">
@@ -35480,10 +35480,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1277" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1277" s="1">
         <x:v>0</x:v>
@@ -35492,10 +35492,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1277" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1277" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1278" spans="1:7">
@@ -35503,10 +35503,10 @@
         <x:v>1319</x:v>
       </x:c>
       <x:c r="B1278" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1278" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1278" s="1">
         <x:v>0</x:v>
@@ -35515,10 +35515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1278" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1278" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1279" spans="1:7">
@@ -35917,7 +35917,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1296" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1296" s="1">
         <x:v>0</x:v>
@@ -35929,10 +35929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1296" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1297" spans="1:7">
@@ -35940,7 +35940,7 @@
         <x:v>1338</x:v>
       </x:c>
       <x:c r="B1297" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1297" s="1">
         <x:v>0</x:v>
@@ -35952,10 +35952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1297" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1297" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1298" spans="1:7">
@@ -37297,10 +37297,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37309,10 +37309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -37320,10 +37320,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1357" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1357" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1357" s="1">
         <x:v>0</x:v>
@@ -37332,10 +37332,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1357" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1357" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1358" spans="1:7">
@@ -40540,10 +40540,10 @@
         <x:v>1537</x:v>
       </x:c>
       <x:c r="B1497" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1497" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1497" s="1">
         <x:v>0</x:v>
@@ -40552,10 +40552,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1497" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1497" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1498" spans="1:7">
@@ -40563,10 +40563,10 @@
         <x:v>1537</x:v>
       </x:c>
       <x:c r="B1498" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1498" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1498" s="1">
         <x:v>0</x:v>
@@ -40575,10 +40575,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1498" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1498" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1499" spans="1:7">
@@ -41115,7 +41115,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1522" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1522" s="1">
         <x:v>0</x:v>
@@ -41127,10 +41127,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1522" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1522" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1523" spans="1:7">
@@ -41138,7 +41138,7 @@
         <x:v>1561</x:v>
       </x:c>
       <x:c r="B1523" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1523" s="1">
         <x:v>0</x:v>
@@ -41150,10 +41150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1523" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1523" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1524" spans="1:7">
@@ -42863,10 +42863,10 @@
         <x:v>1635</x:v>
       </x:c>
       <x:c r="B1598" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1598" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1598" s="1">
         <x:v>0</x:v>
@@ -42875,10 +42875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1598" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1598" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1599" spans="1:7">
@@ -42886,10 +42886,10 @@
         <x:v>1635</x:v>
       </x:c>
       <x:c r="B1599" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1599" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1599" s="1">
         <x:v>0</x:v>
@@ -42898,10 +42898,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1599" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1599" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1600" spans="1:7">
@@ -45347,10 +45347,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1706" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1706" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1706" s="1">
         <x:v>0</x:v>
@@ -45359,10 +45359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1706" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1706" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1707" spans="1:7">
@@ -45370,10 +45370,10 @@
         <x:v>1740</x:v>
       </x:c>
       <x:c r="B1707" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1707" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1707" s="1">
         <x:v>0</x:v>
@@ -45382,10 +45382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1707" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1707" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1708" spans="1:7">
@@ -45692,10 +45692,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1721" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1721" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1721" s="1">
         <x:v>0</x:v>
@@ -45704,10 +45704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1721" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1721" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1722" spans="1:7">
@@ -45715,10 +45715,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45727,10 +45727,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -47095,10 +47095,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47110,7 +47110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -47118,10 +47118,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1783" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1783" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1783" s="1">
         <x:v>0</x:v>
@@ -47133,7 +47133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1783" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1784" spans="1:7">
@@ -49142,10 +49142,10 @@
         <x:v>1900</x:v>
       </x:c>
       <x:c r="B1871" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1871" s="1">
         <x:v>0</x:v>
@@ -49154,10 +49154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1871" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1871" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1872" spans="1:7">
@@ -49165,10 +49165,10 @@
         <x:v>1900</x:v>
       </x:c>
       <x:c r="B1872" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1872" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1872" s="1">
         <x:v>0</x:v>
@@ -49177,10 +49177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1872" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1872" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1873" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8501,10 +8501,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8513,10 +8513,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8524,10 +8524,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8536,10 +8536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -21841,10 +21841,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -21853,10 +21853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -21864,10 +21864,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21876,10 +21876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -37297,10 +37297,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1356" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1356" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1356" s="1">
         <x:v>0</x:v>
@@ -37309,10 +37309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1356" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1356" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1357" spans="1:7">
@@ -37320,10 +37320,10 @@
         <x:v>1396</x:v>
       </x:c>
       <x:c r="B1357" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1357" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1357" s="1">
         <x:v>0</x:v>
@@ -37332,10 +37332,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1357" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1357" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1358" spans="1:7">
@@ -43645,10 +43645,10 @@
         <x:v>1668</x:v>
       </x:c>
       <x:c r="B1632" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1632" s="1">
         <x:v>0</x:v>
@@ -43657,10 +43657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1632" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1632" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1633" spans="1:7">
@@ -43668,10 +43668,10 @@
         <x:v>1668</x:v>
       </x:c>
       <x:c r="B1633" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1633" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1633" s="1">
         <x:v>0</x:v>
@@ -43680,10 +43680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1633" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1633" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1634" spans="1:7">
@@ -47095,10 +47095,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1782" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1782" s="1">
         <x:v>0</x:v>
@@ -47110,7 +47110,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1782" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1783" spans="1:7">
@@ -47118,10 +47118,10 @@
         <x:v>1813</x:v>
       </x:c>
       <x:c r="B1783" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1783" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1783" s="1">
         <x:v>0</x:v>
@@ -47133,7 +47133,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1783" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1784" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16971,10 +16971,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16983,10 +16983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16994,10 +16994,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17006,10 +17006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -21870,10 +21870,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21882,10 +21882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21893,10 +21893,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21905,10 +21905,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -35532,10 +35532,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1279" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1279" s="1">
         <x:v>0</x:v>
@@ -35544,10 +35544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -35555,10 +35555,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35567,10 +35567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -35969,7 +35969,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1298" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1298" s="1">
         <x:v>0</x:v>
@@ -35981,10 +35981,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1298" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1298" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1299" spans="1:7">
@@ -35992,7 +35992,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36004,10 +36004,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -40592,10 +40592,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1499" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1499" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1499" s="1">
         <x:v>0</x:v>
@@ -40604,10 +40604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1499" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1499" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1500" spans="1:7">
@@ -40615,10 +40615,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40627,10 +40627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -42915,10 +42915,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1600" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1600" s="1">
         <x:v>0</x:v>
@@ -42927,10 +42927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1600" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1601" spans="1:7">
@@ -42938,10 +42938,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42950,10 +42950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -45560,10 +45560,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45572,10 +45572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -45583,10 +45583,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45595,10 +45595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -47147,10 +47147,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1784" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1784" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1784" s="1">
         <x:v>0</x:v>
@@ -47162,7 +47162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1784" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1785" spans="1:7">
@@ -47170,10 +47170,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47185,7 +47185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -49194,10 +49194,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1873" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1873" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1873" s="1">
         <x:v>0</x:v>
@@ -49206,10 +49206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1873" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1873" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1874" spans="1:7">
@@ -49217,10 +49217,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49229,10 +49229,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8507,10 +8507,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8519,10 +8519,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8530,10 +8530,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8542,10 +8542,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -21870,10 +21870,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21882,10 +21882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21893,10 +21893,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21905,10 +21905,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -25343,10 +25343,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -25355,10 +25355,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -25366,10 +25366,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -25378,10 +25378,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F837" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
@@ -35969,7 +35969,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1298" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1298" s="1">
         <x:v>0</x:v>
@@ -35981,10 +35981,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1298" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1298" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1299" spans="1:7">
@@ -35992,7 +35992,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36004,10 +36004,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -42915,10 +42915,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1600" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1600" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1600" s="1">
         <x:v>0</x:v>
@@ -42927,10 +42927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1600" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1600" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1601" spans="1:7">
@@ -42938,10 +42938,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42950,10 +42950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -44111,10 +44111,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1652" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1652" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1652" s="1">
         <x:v>0</x:v>
@@ -44123,10 +44123,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1652" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1652" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1653" spans="1:7">
@@ -44134,10 +44134,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44146,10 +44146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -45560,10 +45560,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45572,10 +45572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -45583,10 +45583,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45595,10 +45595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45744,10 +45744,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45756,10 +45756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45767,10 +45767,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45779,10 +45779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -47147,10 +47147,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1784" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1784" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1784" s="1">
         <x:v>0</x:v>
@@ -47162,7 +47162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1784" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1785" spans="1:7">
@@ -47170,10 +47170,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47185,7 +47185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -49194,10 +49194,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1873" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1873" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1873" s="1">
         <x:v>0</x:v>
@@ -49206,10 +49206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1873" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1873" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1874" spans="1:7">
@@ -49217,10 +49217,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49229,10 +49229,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8507,10 +8507,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8519,10 +8519,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8530,10 +8530,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8542,10 +8542,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -25343,10 +25343,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -25355,10 +25355,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -25366,10 +25366,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -25378,10 +25378,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F837" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
@@ -35532,10 +35532,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1279" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1279" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1279" s="1">
         <x:v>0</x:v>
@@ -35544,10 +35544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -35555,10 +35555,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35567,10 +35567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -37349,10 +37349,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1358" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1358" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1358" s="1">
         <x:v>0</x:v>
@@ -37361,10 +37361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1358" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1358" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1359" spans="1:7">
@@ -37372,10 +37372,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37384,10 +37384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">
@@ -43697,10 +43697,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1634" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1634" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1634" s="1">
         <x:v>0</x:v>
@@ -43709,10 +43709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1634" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1634" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1635" spans="1:7">
@@ -43720,10 +43720,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43732,10 +43732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -44111,10 +44111,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1652" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1652" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1652" s="1">
         <x:v>0</x:v>
@@ -44123,10 +44123,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1652" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1652" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1653" spans="1:7">
@@ -44134,10 +44134,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44146,10 +44146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -45399,10 +45399,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1708" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1708" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1708" s="1">
         <x:v>0</x:v>
@@ -45411,10 +45411,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1708" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1708" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1709" spans="1:7">
@@ -45422,10 +45422,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45434,10 +45434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45560,10 +45560,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45572,10 +45572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -45583,10 +45583,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45595,10 +45595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45744,10 +45744,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45756,10 +45756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45767,10 +45767,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45779,10 +45779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30196,10 +30196,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30208,10 +30208,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30219,10 +30219,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30231,10 +30231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -32312,10 +32312,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32324,10 +32324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32335,10 +32335,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32347,10 +32347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35532,10 +35532,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1279" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1279" s="1">
         <x:v>0</x:v>
@@ -35544,10 +35544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -35555,10 +35555,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35567,10 +35567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -37349,10 +37349,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1358" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1358" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1358" s="1">
         <x:v>0</x:v>
@@ -37361,10 +37361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1358" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1358" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1359" spans="1:7">
@@ -37372,10 +37372,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37384,10 +37384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16971,10 +16971,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16983,10 +16983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16994,10 +16994,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17006,10 +17006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -21870,10 +21870,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21882,10 +21882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21893,10 +21893,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21905,10 +21905,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -30196,10 +30196,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30208,10 +30208,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30219,10 +30219,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30231,10 +30231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -30794,10 +30794,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1073" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1073" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1073" s="1">
         <x:v>0</x:v>
@@ -30806,10 +30806,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1073" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1073" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1074" spans="1:7">
@@ -30817,10 +30817,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1074" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1074" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1074" s="1">
         <x:v>0</x:v>
@@ -30829,10 +30829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1074" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1074" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1075" spans="1:7">
@@ -32312,10 +32312,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32324,10 +32324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32335,10 +32335,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32347,10 +32347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -42915,10 +42915,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1600" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1600" s="1">
         <x:v>0</x:v>
@@ -42927,10 +42927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1600" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1601" spans="1:7">
@@ -42938,10 +42938,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42950,10 +42950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -44111,10 +44111,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1652" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1652" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1652" s="1">
         <x:v>0</x:v>
@@ -44123,10 +44123,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1652" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1652" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1653" spans="1:7">
@@ -44134,10 +44134,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44146,10 +44146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -45399,10 +45399,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1708" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1708" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1708" s="1">
         <x:v>0</x:v>
@@ -45411,10 +45411,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1708" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1708" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1709" spans="1:7">
@@ -45422,10 +45422,10 @@
         <x:v>1742</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45434,10 +45434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45560,10 +45560,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45572,10 +45572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -45583,10 +45583,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45595,10 +45595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45744,10 +45744,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45756,10 +45756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45767,10 +45767,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45779,10 +45779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -49194,10 +49194,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1873" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1873" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1873" s="1">
         <x:v>0</x:v>
@@ -49206,10 +49206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1873" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1873" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1874" spans="1:7">
@@ -49217,10 +49217,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49229,10 +49229,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16971,10 +16971,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16983,10 +16983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16994,10 +16994,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17006,10 +17006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -21870,10 +21870,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21882,10 +21882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21893,10 +21893,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21905,10 +21905,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -30794,10 +30794,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1073" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1073" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1073" s="1">
         <x:v>0</x:v>
@@ -30806,10 +30806,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1073" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1073" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1074" spans="1:7">
@@ -30817,10 +30817,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1074" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1074" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1074" s="1">
         <x:v>0</x:v>
@@ -30829,10 +30829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1074" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1074" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1075" spans="1:7">
@@ -32312,10 +32312,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32324,10 +32324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32335,10 +32335,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32347,10 +32347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35969,7 +35969,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1298" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1298" s="1">
         <x:v>0</x:v>
@@ -35981,10 +35981,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1298" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1298" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1299" spans="1:7">
@@ -35992,7 +35992,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36004,10 +36004,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -37349,10 +37349,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1358" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1358" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1358" s="1">
         <x:v>0</x:v>
@@ -37361,10 +37361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1358" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1358" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1359" spans="1:7">
@@ -37372,10 +37372,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37384,10 +37384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">
@@ -40592,10 +40592,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1499" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1499" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1499" s="1">
         <x:v>0</x:v>
@@ -40604,10 +40604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1499" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1499" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1500" spans="1:7">
@@ -40615,10 +40615,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40627,10 +40627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -44111,10 +44111,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1652" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1652" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1652" s="1">
         <x:v>0</x:v>
@@ -44123,10 +44123,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1652" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1652" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1653" spans="1:7">
@@ -44134,10 +44134,10 @@
         <x:v>1687</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44146,10 +44146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -45560,10 +45560,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45572,10 +45572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -45583,10 +45583,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45595,10 +45595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -49194,10 +49194,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1873" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1873" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1873" s="1">
         <x:v>0</x:v>
@@ -49206,10 +49206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1873" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1873" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1874" spans="1:7">
@@ -49217,10 +49217,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49229,10 +49229,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -6785,7 +6785,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>16000</x:v>
+        <x:v>18500</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>0</x:v>
@@ -6797,7 +6797,7 @@
         <x:v>8800</x:v>
       </x:c>
       <x:c r="G29" s="1">
-        <x:v>24800</x:v>
+        <x:v>27300</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -8832,7 +8832,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C118" s="1">
-        <x:v>31710</x:v>
+        <x:v>32710</x:v>
       </x:c>
       <x:c r="D118" s="1">
         <x:v>0</x:v>
@@ -8844,7 +8844,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G118" s="1">
-        <x:v>32710</x:v>
+        <x:v>33710</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
@@ -9476,7 +9476,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C146" s="1">
-        <x:v>42000</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D146" s="1">
         <x:v>0</x:v>
@@ -9488,7 +9488,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G146" s="1">
-        <x:v>42000</x:v>
+        <x:v>43000</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
@@ -9867,7 +9867,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C163" s="1">
-        <x:v>17590</x:v>
+        <x:v>19590</x:v>
       </x:c>
       <x:c r="D163" s="1">
         <x:v>0</x:v>
@@ -9879,7 +9879,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G163" s="1">
-        <x:v>17590</x:v>
+        <x:v>19590</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
@@ -11316,7 +11316,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="C226" s="1">
-        <x:v>5230</x:v>
+        <x:v>5320</x:v>
       </x:c>
       <x:c r="D226" s="1">
         <x:v>0</x:v>
@@ -11328,7 +11328,7 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="G226" s="1">
-        <x:v>6164</x:v>
+        <x:v>6254</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -13524,7 +13524,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C322" s="1">
-        <x:v>79000</x:v>
+        <x:v>80500</x:v>
       </x:c>
       <x:c r="D322" s="1">
         <x:v>0</x:v>
@@ -13536,7 +13536,7 @@
         <x:v>2700</x:v>
       </x:c>
       <x:c r="G322" s="1">
-        <x:v>81700</x:v>
+        <x:v>83200</x:v>
       </x:c>
     </x:row>
     <x:row r="323" spans="1:7">
@@ -14582,7 +14582,7 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="C368" s="1">
-        <x:v>94500</x:v>
+        <x:v>95500</x:v>
       </x:c>
       <x:c r="D368" s="1">
         <x:v>0</x:v>
@@ -14594,7 +14594,7 @@
         <x:v>5350</x:v>
       </x:c>
       <x:c r="G368" s="1">
-        <x:v>99850</x:v>
+        <x:v>100850</x:v>
       </x:c>
     </x:row>
     <x:row r="369" spans="1:7">
@@ -14674,7 +14674,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C372" s="1">
-        <x:v>199500</x:v>
+        <x:v>204500</x:v>
       </x:c>
       <x:c r="D372" s="1">
         <x:v>0</x:v>
@@ -14686,7 +14686,7 @@
         <x:v>35600</x:v>
       </x:c>
       <x:c r="G372" s="1">
-        <x:v>235100</x:v>
+        <x:v>240100</x:v>
       </x:c>
     </x:row>
     <x:row r="373" spans="1:7">
@@ -16146,7 +16146,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C436" s="1">
-        <x:v>15500</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D436" s="1">
         <x:v>0</x:v>
@@ -16158,7 +16158,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G436" s="1">
-        <x:v>15500</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="437" spans="1:7">
@@ -17595,7 +17595,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C499" s="1">
-        <x:v>6000</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D499" s="1">
         <x:v>0</x:v>
@@ -17607,7 +17607,7 @@
         <x:v>38750</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>44750</x:v>
+        <x:v>49750</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -18170,7 +18170,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>29000</x:v>
+        <x:v>30500</x:v>
       </x:c>
       <x:c r="D524" s="1">
         <x:v>0</x:v>
@@ -18182,7 +18182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>29000</x:v>
+        <x:v>30500</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -20493,7 +20493,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>4500</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -20505,7 +20505,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>4500</x:v>
+        <x:v>5500</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -21781,7 +21781,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>44000</x:v>
+        <x:v>46500</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -21793,7 +21793,7 @@
         <x:v>73590</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>117590</x:v>
+        <x:v>120090</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -21919,7 +21919,7 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>75000</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="D687" s="1">
         <x:v>0</x:v>
@@ -21931,7 +21931,7 @@
         <x:v>30750</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>105750</x:v>
+        <x:v>110750</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -22080,7 +22080,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>5000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D694" s="1">
         <x:v>0</x:v>
@@ -22092,7 +22092,7 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>6250</x:v>
+        <x:v>8250</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -22839,7 +22839,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>38000</x:v>
+        <x:v>40500</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -22851,7 +22851,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>38000</x:v>
+        <x:v>40500</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -24081,7 +24081,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>23000</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
@@ -24093,7 +24093,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>23000</x:v>
+        <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -24311,7 +24311,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C791" s="1">
-        <x:v>69500</x:v>
+        <x:v>72500</x:v>
       </x:c>
       <x:c r="D791" s="1">
         <x:v>0</x:v>
@@ -24323,7 +24323,7 @@
         <x:v>20300</x:v>
       </x:c>
       <x:c r="G791" s="1">
-        <x:v>89800</x:v>
+        <x:v>92800</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:7">
@@ -24840,7 +24840,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C814" s="1">
-        <x:v>82920</x:v>
+        <x:v>83920</x:v>
       </x:c>
       <x:c r="D814" s="1">
         <x:v>0</x:v>
@@ -24852,7 +24852,7 @@
         <x:v>1300</x:v>
       </x:c>
       <x:c r="G814" s="1">
-        <x:v>84220</x:v>
+        <x:v>85220</x:v>
       </x:c>
     </x:row>
     <x:row r="815" spans="1:7">
@@ -24863,7 +24863,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C815" s="1">
-        <x:v>12500</x:v>
+        <x:v>17500</x:v>
       </x:c>
       <x:c r="D815" s="1">
         <x:v>0</x:v>
@@ -24875,7 +24875,7 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="G815" s="1">
-        <x:v>13750</x:v>
+        <x:v>18750</x:v>
       </x:c>
     </x:row>
     <x:row r="816" spans="1:7">
@@ -26128,7 +26128,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C870" s="1">
-        <x:v>140090</x:v>
+        <x:v>145090</x:v>
       </x:c>
       <x:c r="D870" s="1">
         <x:v>0</x:v>
@@ -26140,7 +26140,7 @@
         <x:v>8750</x:v>
       </x:c>
       <x:c r="G870" s="1">
-        <x:v>148840</x:v>
+        <x:v>153840</x:v>
       </x:c>
     </x:row>
     <x:row r="871" spans="1:7">
@@ -26427,7 +26427,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="C883" s="1">
-        <x:v>64500</x:v>
+        <x:v>65500</x:v>
       </x:c>
       <x:c r="D883" s="1">
         <x:v>0</x:v>
@@ -26439,7 +26439,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G883" s="1">
-        <x:v>64500</x:v>
+        <x:v>65500</x:v>
       </x:c>
     </x:row>
     <x:row r="884" spans="1:7">
@@ -27025,7 +27025,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C909" s="1">
-        <x:v>24500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D909" s="1">
         <x:v>0</x:v>
@@ -27037,7 +27037,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G909" s="1">
-        <x:v>24500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="910" spans="1:7">
@@ -27393,7 +27393,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C925" s="1">
-        <x:v>40000</x:v>
+        <x:v>42500</x:v>
       </x:c>
       <x:c r="D925" s="1">
         <x:v>0</x:v>
@@ -27405,7 +27405,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="G925" s="1">
-        <x:v>40500</x:v>
+        <x:v>43000</x:v>
       </x:c>
     </x:row>
     <x:row r="926" spans="1:7">
@@ -29417,7 +29417,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C1013" s="1">
-        <x:v>149000</x:v>
+        <x:v>151000</x:v>
       </x:c>
       <x:c r="D1013" s="1">
         <x:v>0</x:v>
@@ -29429,7 +29429,7 @@
         <x:v>94550</x:v>
       </x:c>
       <x:c r="G1013" s="1">
-        <x:v>243550</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="1014" spans="1:7">
@@ -30176,7 +30176,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1046" s="1">
-        <x:v>7000</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D1046" s="1">
         <x:v>0</x:v>
@@ -30188,7 +30188,7 @@
         <x:v>24200</x:v>
       </x:c>
       <x:c r="G1046" s="1">
-        <x:v>31200</x:v>
+        <x:v>34200</x:v>
       </x:c>
     </x:row>
     <x:row r="1047" spans="1:7">
@@ -30245,7 +30245,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1049" s="1">
-        <x:v>95500</x:v>
+        <x:v>101000</x:v>
       </x:c>
       <x:c r="D1049" s="1">
         <x:v>0</x:v>
@@ -30257,7 +30257,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="G1049" s="1">
-        <x:v>96250</x:v>
+        <x:v>101750</x:v>
       </x:c>
     </x:row>
     <x:row r="1050" spans="1:7">
@@ -30406,7 +30406,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>329775</x:v>
+        <x:v>330775</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30418,7 +30418,7 @@
         <x:v>83750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>413525</x:v>
+        <x:v>414525</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -31096,7 +31096,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C1086" s="1">
-        <x:v>2000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1086" s="1">
         <x:v>0</x:v>
@@ -31108,7 +31108,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1086" s="1">
-        <x:v>2000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="1087" spans="1:7">
@@ -31694,7 +31694,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1112" s="1">
-        <x:v>17635</x:v>
+        <x:v>22635</x:v>
       </x:c>
       <x:c r="D1112" s="1">
         <x:v>0</x:v>
@@ -31706,7 +31706,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1112" s="1">
-        <x:v>17635</x:v>
+        <x:v>22635</x:v>
       </x:c>
     </x:row>
     <x:row r="1113" spans="1:7">
@@ -31786,7 +31786,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1116" s="1">
-        <x:v>123850</x:v>
+        <x:v>127850</x:v>
       </x:c>
       <x:c r="D1116" s="1">
         <x:v>0</x:v>
@@ -31798,7 +31798,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="G1116" s="1">
-        <x:v>125850</x:v>
+        <x:v>129850</x:v>
       </x:c>
     </x:row>
     <x:row r="1117" spans="1:7">
@@ -32312,10 +32312,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32324,10 +32324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32335,10 +32335,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32347,10 +32347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -33235,7 +33235,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C1179" s="1">
-        <x:v>101500</x:v>
+        <x:v>102500</x:v>
       </x:c>
       <x:c r="D1179" s="1">
         <x:v>0</x:v>
@@ -33247,7 +33247,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1179" s="1">
-        <x:v>101500</x:v>
+        <x:v>102500</x:v>
       </x:c>
     </x:row>
     <x:row r="1180" spans="1:7">
@@ -33327,7 +33327,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C1183" s="1">
-        <x:v>61000</x:v>
+        <x:v>62000</x:v>
       </x:c>
       <x:c r="D1183" s="1">
         <x:v>0</x:v>
@@ -33339,7 +33339,7 @@
         <x:v>5200</x:v>
       </x:c>
       <x:c r="G1183" s="1">
-        <x:v>66200</x:v>
+        <x:v>67200</x:v>
       </x:c>
     </x:row>
     <x:row r="1184" spans="1:7">
@@ -34615,7 +34615,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C1239" s="1">
-        <x:v>7590</x:v>
+        <x:v>8590</x:v>
       </x:c>
       <x:c r="D1239" s="1">
         <x:v>0</x:v>
@@ -34627,7 +34627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1239" s="1">
-        <x:v>7590</x:v>
+        <x:v>8590</x:v>
       </x:c>
     </x:row>
     <x:row r="1240" spans="1:7">
@@ -35532,10 +35532,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1279" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1279" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1279" s="1">
         <x:v>0</x:v>
@@ -35544,10 +35544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -35555,10 +35555,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35567,10 +35567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -35969,7 +35969,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1298" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1298" s="1">
         <x:v>0</x:v>
@@ -35981,10 +35981,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1298" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1298" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1299" spans="1:7">
@@ -35992,7 +35992,7 @@
         <x:v>1340</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36004,10 +36004,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36064,7 +36064,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1302" s="1">
-        <x:v>30500</x:v>
+        <x:v>31500</x:v>
       </x:c>
       <x:c r="D1302" s="1">
         <x:v>0</x:v>
@@ -36076,7 +36076,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G1302" s="1">
-        <x:v>37500</x:v>
+        <x:v>38500</x:v>
       </x:c>
     </x:row>
     <x:row r="1303" spans="1:7">
@@ -36685,7 +36685,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C1329" s="1">
-        <x:v>211500</x:v>
+        <x:v>219000</x:v>
       </x:c>
       <x:c r="D1329" s="1">
         <x:v>0</x:v>
@@ -36697,7 +36697,7 @@
         <x:v>8200</x:v>
       </x:c>
       <x:c r="G1329" s="1">
-        <x:v>219700</x:v>
+        <x:v>227200</x:v>
       </x:c>
     </x:row>
     <x:row r="1330" spans="1:7">
@@ -37349,10 +37349,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1358" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1358" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1358" s="1">
         <x:v>0</x:v>
@@ -37361,10 +37361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1358" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1358" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1359" spans="1:7">
@@ -37372,10 +37372,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37384,10 +37384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">
@@ -38801,7 +38801,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C1421" s="1">
-        <x:v>55590</x:v>
+        <x:v>57590</x:v>
       </x:c>
       <x:c r="D1421" s="1">
         <x:v>0</x:v>
@@ -38813,7 +38813,7 @@
         <x:v>15200</x:v>
       </x:c>
       <x:c r="G1421" s="1">
-        <x:v>70790</x:v>
+        <x:v>72790</x:v>
       </x:c>
     </x:row>
     <x:row r="1422" spans="1:7">
@@ -40250,7 +40250,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C1484" s="1">
-        <x:v>17590</x:v>
+        <x:v>18590</x:v>
       </x:c>
       <x:c r="D1484" s="1">
         <x:v>0</x:v>
@@ -40262,7 +40262,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1484" s="1">
-        <x:v>17590</x:v>
+        <x:v>18590</x:v>
       </x:c>
     </x:row>
     <x:row r="1485" spans="1:7">
@@ -40503,7 +40503,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C1495" s="1">
-        <x:v>28500</x:v>
+        <x:v>30500</x:v>
       </x:c>
       <x:c r="D1495" s="1">
         <x:v>0</x:v>
@@ -40515,7 +40515,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1495" s="1">
-        <x:v>28500</x:v>
+        <x:v>30500</x:v>
       </x:c>
     </x:row>
     <x:row r="1496" spans="1:7">
@@ -40592,10 +40592,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1499" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1499" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1499" s="1">
         <x:v>0</x:v>
@@ -40604,10 +40604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1499" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1499" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1500" spans="1:7">
@@ -40615,10 +40615,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40627,10 +40627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40664,7 +40664,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1502" s="1">
-        <x:v>57500</x:v>
+        <x:v>58500</x:v>
       </x:c>
       <x:c r="D1502" s="1">
         <x:v>0</x:v>
@@ -40676,7 +40676,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="G1502" s="1">
-        <x:v>58000</x:v>
+        <x:v>59000</x:v>
       </x:c>
     </x:row>
     <x:row r="1503" spans="1:7">
@@ -41515,7 +41515,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C1539" s="1">
-        <x:v>13500</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="D1539" s="1">
         <x:v>0</x:v>
@@ -41527,7 +41527,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>13500</x:v>
+        <x:v>14500</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -43217,7 +43217,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>228500</x:v>
+        <x:v>231000</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43229,7 +43229,7 @@
         <x:v>103100</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>331600</x:v>
+        <x:v>334100</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -44666,7 +44666,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="C1676" s="1">
-        <x:v>15000</x:v>
+        <x:v>18500</x:v>
       </x:c>
       <x:c r="D1676" s="1">
         <x:v>0</x:v>
@@ -44678,7 +44678,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1676" s="1">
-        <x:v>15000</x:v>
+        <x:v>18500</x:v>
       </x:c>
     </x:row>
     <x:row r="1677" spans="1:7">
@@ -45744,10 +45744,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45756,10 +45756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45767,10 +45767,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45779,10 +45779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -46046,7 +46046,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1736" s="1">
-        <x:v>17000</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="D1736" s="1">
         <x:v>0</x:v>
@@ -46058,7 +46058,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1736" s="1">
-        <x:v>17000</x:v>
+        <x:v>18000</x:v>
       </x:c>
     </x:row>
     <x:row r="1737" spans="1:7">
@@ -46897,7 +46897,7 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="C1773" s="1">
-        <x:v>8000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="D1773" s="1">
         <x:v>0</x:v>
@@ -46909,7 +46909,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1773" s="1">
-        <x:v>8000</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="1774" spans="1:7">
@@ -47357,7 +47357,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C1793" s="1">
-        <x:v>7500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1793" s="1">
         <x:v>0</x:v>
@@ -47369,7 +47369,7 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="G1793" s="1">
-        <x:v>9500</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="1794" spans="1:7">
@@ -47587,7 +47587,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>108200</x:v>
+        <x:v>112700</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47599,7 +47599,7 @@
         <x:v>16000</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>124200</x:v>
+        <x:v>128700</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -48323,7 +48323,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1835" s="1">
-        <x:v>7000</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1835" s="1">
         <x:v>0</x:v>
@@ -48335,7 +48335,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1835" s="1">
-        <x:v>7000</x:v>
+        <x:v>8000</x:v>
       </x:c>
     </x:row>
     <x:row r="1836" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8507,10 +8507,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8519,10 +8519,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8530,10 +8530,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8542,10 +8542,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -16971,10 +16971,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16983,10 +16983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16994,10 +16994,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17006,10 +17006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -25343,10 +25343,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -25355,10 +25355,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -25366,10 +25366,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -25378,10 +25378,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F837" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
@@ -35532,10 +35532,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1279" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1279" s="1">
         <x:v>0</x:v>
@@ -35544,10 +35544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -35555,10 +35555,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35567,10 +35567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -40592,10 +40592,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1499" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1499" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1499" s="1">
         <x:v>0</x:v>
@@ -40604,10 +40604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1499" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1499" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1500" spans="1:7">
@@ -40615,10 +40615,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40627,10 +40627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -42915,10 +42915,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1600" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1600" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1600" s="1">
         <x:v>0</x:v>
@@ -42927,10 +42927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1600" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1600" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1601" spans="1:7">
@@ -42938,10 +42938,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42950,10 +42950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -45744,10 +45744,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45756,10 +45756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45767,10 +45767,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45779,10 +45779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -47147,10 +47147,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1784" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1784" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1784" s="1">
         <x:v>0</x:v>
@@ -47162,7 +47162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1784" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1785" spans="1:7">
@@ -47170,10 +47170,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47185,7 +47185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8507,10 +8507,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8519,10 +8519,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8530,10 +8530,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8542,10 +8542,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -16971,10 +16971,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16983,10 +16983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16994,10 +16994,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17006,10 +17006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -25343,10 +25343,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -25355,10 +25355,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -25366,10 +25366,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -25378,10 +25378,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F837" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
@@ -40592,10 +40592,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1499" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1499" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1499" s="1">
         <x:v>0</x:v>
@@ -40604,10 +40604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1499" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1499" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1500" spans="1:7">
@@ -40615,10 +40615,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40627,10 +40627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -43697,10 +43697,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1634" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1634" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1634" s="1">
         <x:v>0</x:v>
@@ -43709,10 +43709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1634" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1634" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1635" spans="1:7">
@@ -43720,10 +43720,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43732,10 +43732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -45744,10 +45744,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45756,10 +45756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45767,10 +45767,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45779,10 +45779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16971,10 +16971,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16983,10 +16983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16994,10 +16994,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17006,10 +17006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -32312,10 +32312,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32324,10 +32324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32335,10 +32335,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32347,10 +32347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35532,10 +35532,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1279" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1279" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1279" s="1">
         <x:v>0</x:v>
@@ -35544,10 +35544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -35555,10 +35555,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35567,10 +35567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -37349,10 +37349,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1358" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1358" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1358" s="1">
         <x:v>0</x:v>
@@ -37361,10 +37361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1358" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1358" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1359" spans="1:7">
@@ -37372,10 +37372,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37384,10 +37384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">
@@ -42915,10 +42915,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1600" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1600" s="1">
         <x:v>0</x:v>
@@ -42927,10 +42927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1600" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1601" spans="1:7">
@@ -42938,10 +42938,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42950,10 +42950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30794,10 +30794,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1073" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1073" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1073" s="1">
         <x:v>0</x:v>
@@ -30806,10 +30806,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1073" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1073" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1074" spans="1:7">
@@ -30817,10 +30817,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1074" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1074" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1074" s="1">
         <x:v>0</x:v>
@@ -30829,10 +30829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1074" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1074" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1075" spans="1:7">
@@ -32312,10 +32312,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32324,10 +32324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32335,10 +32335,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32347,10 +32347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -37349,10 +37349,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1358" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1358" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1358" s="1">
         <x:v>0</x:v>
@@ -37361,10 +37361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1358" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1358" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1359" spans="1:7">
@@ -37372,10 +37372,10 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37384,10 +37384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">
@@ -40592,10 +40592,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1499" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1499" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1499" s="1">
         <x:v>0</x:v>
@@ -40604,10 +40604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1499" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1499" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1500" spans="1:7">
@@ -40615,10 +40615,10 @@
         <x:v>1539</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40627,10 +40627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -42915,10 +42915,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1600" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1600" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1600" s="1">
         <x:v>0</x:v>
@@ -42927,10 +42927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1600" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1600" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1601" spans="1:7">
@@ -42938,10 +42938,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42950,10 +42950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -43697,10 +43697,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1634" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1634" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1634" s="1">
         <x:v>0</x:v>
@@ -43709,10 +43709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1634" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1634" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1635" spans="1:7">
@@ -43720,10 +43720,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43732,10 +43732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -47147,10 +47147,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1784" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1784" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1784" s="1">
         <x:v>0</x:v>
@@ -47162,7 +47162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1784" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1785" spans="1:7">
@@ -47170,10 +47170,10 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47185,7 +47185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16971,10 +16971,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16983,10 +16983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16994,10 +16994,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17006,10 +17006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -30794,10 +30794,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1073" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1073" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1073" s="1">
         <x:v>0</x:v>
@@ -30806,10 +30806,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1073" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1073" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1074" spans="1:7">
@@ -30817,10 +30817,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1074" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1074" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1074" s="1">
         <x:v>0</x:v>
@@ -30829,10 +30829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1074" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1074" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1075" spans="1:7">
@@ -42915,10 +42915,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1600" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1600" s="1">
         <x:v>0</x:v>
@@ -42927,10 +42927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1600" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1600" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1601" spans="1:7">
@@ -42938,10 +42938,10 @@
         <x:v>1637</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42950,10 +42950,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -43697,10 +43697,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1634" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1634" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1634" s="1">
         <x:v>0</x:v>
@@ -43709,10 +43709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1634" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1634" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1635" spans="1:7">
@@ -43720,10 +43720,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43732,10 +43732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -45560,10 +45560,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1715" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1715" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1715" s="1">
         <x:v>0</x:v>
@@ -45572,10 +45572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1715" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1715" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1716" spans="1:7">
@@ -45583,10 +45583,10 @@
         <x:v>1748</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45595,10 +45595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45744,10 +45744,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45756,10 +45756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45767,10 +45767,10 @@
         <x:v>1755</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45779,10 +45779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8507,10 +8507,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8519,10 +8519,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8530,10 +8530,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8542,10 +8542,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -21870,10 +21870,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21882,10 +21882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21893,10 +21893,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21905,10 +21905,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -32312,10 +32312,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32324,10 +32324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32335,10 +32335,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32347,10 +32347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35532,10 +35532,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1279" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1279" s="1">
         <x:v>0</x:v>
@@ -35544,10 +35544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1279" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1279" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1280" spans="1:7">
@@ -35555,10 +35555,10 @@
         <x:v>1321</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35567,10 +35567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -43697,10 +43697,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1634" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1634" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1634" s="1">
         <x:v>0</x:v>
@@ -43709,10 +43709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1634" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1634" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1635" spans="1:7">
@@ -43720,10 +43720,10 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43732,10 +43732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -49194,10 +49194,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1873" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1873" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1873" s="1">
         <x:v>0</x:v>
@@ -49206,10 +49206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1873" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1873" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1874" spans="1:7">
@@ -49217,10 +49217,10 @@
         <x:v>1902</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49229,10 +49229,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8510,10 +8510,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8522,10 +8522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8533,10 +8533,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8545,10 +8545,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -25346,10 +25346,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -25358,10 +25358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -25369,10 +25369,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -25381,10 +25381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F837" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
@@ -35558,10 +35558,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35570,10 +35570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -35581,10 +35581,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1281" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1281" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1281" s="1">
         <x:v>0</x:v>
@@ -35593,10 +35593,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1281" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1281" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1282" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -41193,7 +41193,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1525" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1525" s="1">
         <x:v>0</x:v>
@@ -41205,10 +41205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1525" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1525" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1526" spans="1:7">
@@ -41216,7 +41216,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1526" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1526" s="1">
         <x:v>0</x:v>
@@ -41228,10 +41228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1526" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1526" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1527" spans="1:7">
@@ -44137,10 +44137,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44149,10 +44149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -44160,10 +44160,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1654" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1654" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1654" s="1">
         <x:v>0</x:v>
@@ -44172,10 +44172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1654" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1654" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1655" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">
@@ -49220,10 +49220,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49232,10 +49232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">
@@ -49243,10 +49243,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1875" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1875" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1875" s="1">
         <x:v>0</x:v>
@@ -49255,10 +49255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1875" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1875" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1876" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -41193,7 +41193,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1525" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1525" s="1">
         <x:v>0</x:v>
@@ -41205,10 +41205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1525" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1525" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1526" spans="1:7">
@@ -41216,7 +41216,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1526" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1526" s="1">
         <x:v>0</x:v>
@@ -41228,10 +41228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1526" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1526" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1527" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30797,10 +30797,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1073" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1073" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1073" s="1">
         <x:v>0</x:v>
@@ -30809,10 +30809,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1073" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1073" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1074" spans="1:7">
@@ -30820,10 +30820,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1074" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1074" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1074" s="1">
         <x:v>0</x:v>
@@ -30832,10 +30832,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1074" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1074" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1075" spans="1:7">
@@ -32315,10 +32315,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32327,10 +32327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32338,10 +32338,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32350,10 +32350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35558,10 +35558,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35570,10 +35570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -35581,10 +35581,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1281" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1281" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1281" s="1">
         <x:v>0</x:v>
@@ -35593,10 +35593,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1281" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1281" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1282" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -43723,10 +43723,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43735,10 +43735,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -43746,10 +43746,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1636" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1636" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1636" s="1">
         <x:v>0</x:v>
@@ -43758,10 +43758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1636" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1636" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1637" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">
@@ -49220,10 +49220,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49232,10 +49232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">
@@ -49243,10 +49243,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1875" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1875" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1875" s="1">
         <x:v>0</x:v>
@@ -49255,10 +49255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1875" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1875" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1876" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30199,10 +30199,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30211,10 +30211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30222,10 +30222,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30234,10 +30234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -30797,10 +30797,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1073" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1073" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1073" s="1">
         <x:v>0</x:v>
@@ -30809,10 +30809,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1073" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1073" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1074" spans="1:7">
@@ -30820,10 +30820,10 @@
         <x:v>1118</x:v>
       </x:c>
       <x:c r="B1074" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1074" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1074" s="1">
         <x:v>0</x:v>
@@ -30832,10 +30832,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1074" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1074" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1075" spans="1:7">
@@ -32315,10 +32315,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32327,10 +32327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32338,10 +32338,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32350,10 +32350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -37375,10 +37375,10 @@
         <x:v>1399</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37387,10 +37387,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">
@@ -37398,10 +37398,10 @@
         <x:v>1399</x:v>
       </x:c>
       <x:c r="B1360" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1360" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1360" s="1">
         <x:v>0</x:v>
@@ -37410,10 +37410,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1360" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1360" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1361" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -42941,10 +42941,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42953,10 +42953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -42964,10 +42964,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1602" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1602" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1602" s="1">
         <x:v>0</x:v>
@@ -42976,10 +42976,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1602" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1602" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1603" spans="1:7">
@@ -43723,10 +43723,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43735,10 +43735,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -43746,10 +43746,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1636" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1636" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1636" s="1">
         <x:v>0</x:v>
@@ -43758,10 +43758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1636" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1636" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1637" spans="1:7">
@@ -45425,10 +45425,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45437,10 +45437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45448,10 +45448,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45460,10 +45460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30199,10 +30199,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30211,10 +30211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30222,10 +30222,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30234,10 +30234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -32315,10 +32315,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32327,10 +32327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32338,10 +32338,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32350,10 +32350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -42941,10 +42941,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42953,10 +42953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -42964,10 +42964,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1602" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1602" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1602" s="1">
         <x:v>0</x:v>
@@ -42976,10 +42976,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1602" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1602" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1603" spans="1:7">
@@ -43723,10 +43723,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43735,10 +43735,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -43746,10 +43746,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1636" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1636" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1636" s="1">
         <x:v>0</x:v>
@@ -43758,10 +43758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1636" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1636" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1637" spans="1:7">
@@ -45425,10 +45425,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45437,10 +45437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45448,10 +45448,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45460,10 +45460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32315,10 +32315,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32327,10 +32327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32338,10 +32338,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32350,10 +32350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -37053,10 +37053,10 @@
         <x:v>1386</x:v>
       </x:c>
       <x:c r="B1345" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1345" s="1">
-        <x:v>0</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="D1345" s="1">
         <x:v>0</x:v>
@@ -37065,10 +37065,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1345" s="1">
-        <x:v>250</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="G1345" s="1">
-        <x:v>250</x:v>
+        <x:v>50600</x:v>
       </x:c>
     </x:row>
     <x:row r="1346" spans="1:7">
@@ -37076,10 +37076,10 @@
         <x:v>1386</x:v>
       </x:c>
       <x:c r="B1346" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1346" s="1">
-        <x:v>41500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1346" s="1">
         <x:v>0</x:v>
@@ -37088,10 +37088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1346" s="1">
-        <x:v>9100</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G1346" s="1">
-        <x:v>50600</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="1347" spans="1:7">
@@ -37375,10 +37375,10 @@
         <x:v>1399</x:v>
       </x:c>
       <x:c r="B1359" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1359" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1359" s="1">
         <x:v>0</x:v>
@@ -37387,10 +37387,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1359" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1360" spans="1:7">
@@ -37398,10 +37398,10 @@
         <x:v>1399</x:v>
       </x:c>
       <x:c r="B1360" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1360" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1360" s="1">
         <x:v>0</x:v>
@@ -37410,10 +37410,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1360" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1360" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1361" spans="1:7">
@@ -42941,10 +42941,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42953,10 +42953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -42964,10 +42964,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1602" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1602" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1602" s="1">
         <x:v>0</x:v>
@@ -42976,10 +42976,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1602" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1602" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1603" spans="1:7">
@@ -45770,10 +45770,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45782,10 +45782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45793,10 +45793,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45805,10 +45805,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">
@@ -49220,10 +49220,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49232,10 +49232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">
@@ -49243,10 +49243,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1875" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1875" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1875" s="1">
         <x:v>0</x:v>
@@ -49255,10 +49255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1875" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1875" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1876" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -9350,10 +9350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>3500</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G140" s="1">
-        <x:v>3500</x:v>
+        <x:v>8000</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -18975,7 +18975,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>0</x:v>
@@ -18987,10 +18987,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -18998,7 +18998,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>0</x:v>
@@ -19010,10 +19010,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -24024,10 +24024,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -34581,10 +34581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1237" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G1237" s="1">
-        <x:v>26000</x:v>
+        <x:v>33000</x:v>
       </x:c>
     </x:row>
     <x:row r="1238" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -37053,10 +37053,10 @@
         <x:v>1386</x:v>
       </x:c>
       <x:c r="B1345" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1345" s="1">
-        <x:v>41500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1345" s="1">
         <x:v>0</x:v>
@@ -37065,10 +37065,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1345" s="1">
-        <x:v>9100</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G1345" s="1">
-        <x:v>50600</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="1346" spans="1:7">
@@ -37076,10 +37076,10 @@
         <x:v>1386</x:v>
       </x:c>
       <x:c r="B1346" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1346" s="1">
-        <x:v>0</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="D1346" s="1">
         <x:v>0</x:v>
@@ -37088,10 +37088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1346" s="1">
-        <x:v>250</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="G1346" s="1">
-        <x:v>250</x:v>
+        <x:v>50600</x:v>
       </x:c>
     </x:row>
     <x:row r="1347" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -41193,7 +41193,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1525" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1525" s="1">
         <x:v>0</x:v>
@@ -41205,10 +41205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1525" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1525" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1526" spans="1:7">
@@ -41216,7 +41216,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1526" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1526" s="1">
         <x:v>0</x:v>
@@ -41228,10 +41228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1526" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1526" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1527" spans="1:7">
@@ -41527,10 +41527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>73050</x:v>
+        <x:v>83050</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>282640</x:v>
+        <x:v>292640</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -43723,10 +43723,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43735,10 +43735,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -43746,10 +43746,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1636" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1636" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1636" s="1">
         <x:v>0</x:v>
@@ -43758,10 +43758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1636" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1636" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1637" spans="1:7">
@@ -44137,10 +44137,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44149,10 +44149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -44160,10 +44160,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1654" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1654" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1654" s="1">
         <x:v>0</x:v>
@@ -44172,10 +44172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1654" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1654" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1655" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -18975,7 +18975,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>0</x:v>
@@ -18987,10 +18987,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -18998,7 +18998,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>0</x:v>
@@ -19010,10 +19010,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -30199,10 +30199,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30211,10 +30211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30222,10 +30222,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30234,10 +30234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -32315,10 +32315,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32327,10 +32327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32338,10 +32338,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32350,10 +32350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -41193,7 +41193,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1525" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1525" s="1">
         <x:v>0</x:v>
@@ -41205,10 +41205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1525" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1525" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1526" spans="1:7">
@@ -41216,7 +41216,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1526" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1526" s="1">
         <x:v>0</x:v>
@@ -41228,10 +41228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1526" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1526" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1527" spans="1:7">
@@ -44137,10 +44137,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44149,10 +44149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -44160,10 +44160,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1654" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1654" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1654" s="1">
         <x:v>0</x:v>
@@ -44172,10 +44172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1654" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1654" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1655" spans="1:7">
@@ -45425,10 +45425,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45437,10 +45437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45448,10 +45448,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45460,10 +45460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">
@@ -49220,10 +49220,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49232,10 +49232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">
@@ -49243,10 +49243,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1875" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1875" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1875" s="1">
         <x:v>0</x:v>
@@ -49255,10 +49255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1875" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1875" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1876" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -30199,10 +30199,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30211,10 +30211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30222,10 +30222,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30234,10 +30234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -32315,10 +32315,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32327,10 +32327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32338,10 +32338,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32350,10 +32350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -35558,10 +35558,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35570,10 +35570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -35581,10 +35581,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1281" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1281" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1281" s="1">
         <x:v>0</x:v>
@@ -35593,10 +35593,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1281" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1281" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1282" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -41193,7 +41193,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1525" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1525" s="1">
         <x:v>0</x:v>
@@ -41205,10 +41205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1525" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1525" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1526" spans="1:7">
@@ -41216,7 +41216,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1526" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1526" s="1">
         <x:v>0</x:v>
@@ -41228,10 +41228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1526" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1526" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1527" spans="1:7">
@@ -42941,10 +42941,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42953,10 +42953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -42964,10 +42964,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1602" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1602" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1602" s="1">
         <x:v>0</x:v>
@@ -42976,10 +42976,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1602" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1602" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1603" spans="1:7">
@@ -45425,10 +45425,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45437,10 +45437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45448,10 +45448,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45460,10 +45460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -45770,10 +45770,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45782,10 +45782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45793,10 +45793,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45805,10 +45805,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -21873,10 +21873,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21885,10 +21885,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21896,10 +21896,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21908,10 +21908,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -35558,10 +35558,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1280" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1280" s="1">
         <x:v>0</x:v>
@@ -35570,10 +35570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1280" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1280" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1281" spans="1:7">
@@ -35581,10 +35581,10 @@
         <x:v>1322</x:v>
       </x:c>
       <x:c r="B1281" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1281" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1281" s="1">
         <x:v>0</x:v>
@@ -35593,10 +35593,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1281" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1281" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1282" spans="1:7">
@@ -35995,7 +35995,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1299" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1299" s="1">
         <x:v>0</x:v>
@@ -36007,10 +36007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1299" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1300" spans="1:7">
@@ -36018,7 +36018,7 @@
         <x:v>1341</x:v>
       </x:c>
       <x:c r="B1300" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1300" s="1">
         <x:v>0</x:v>
@@ -36030,10 +36030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1300" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1301" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -41193,7 +41193,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1525" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1525" s="1">
         <x:v>0</x:v>
@@ -41205,10 +41205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1525" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1525" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1526" spans="1:7">
@@ -41216,7 +41216,7 @@
         <x:v>1564</x:v>
       </x:c>
       <x:c r="B1526" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1526" s="1">
         <x:v>0</x:v>
@@ -41228,10 +41228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1526" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1526" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1527" spans="1:7">
@@ -42941,10 +42941,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42953,10 +42953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -42964,10 +42964,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1602" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1602" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1602" s="1">
         <x:v>0</x:v>
@@ -42976,10 +42976,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1602" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1602" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1603" spans="1:7">
@@ -49220,10 +49220,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49232,10 +49232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">
@@ -49243,10 +49243,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1875" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1875" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1875" s="1">
         <x:v>0</x:v>
@@ -49255,10 +49255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1875" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1875" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1876" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21873,10 +21873,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21885,10 +21885,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21896,10 +21896,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21908,10 +21908,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -30199,10 +30199,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30211,10 +30211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30222,10 +30222,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30234,10 +30234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -40618,10 +40618,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1500" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1500" s="1">
         <x:v>0</x:v>
@@ -40630,10 +40630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1500" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1500" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1501" spans="1:7">
@@ -40641,10 +40641,10 @@
         <x:v>1540</x:v>
       </x:c>
       <x:c r="B1501" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1501" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1501" s="1">
         <x:v>0</x:v>
@@ -40653,10 +40653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1501" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1501" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1502" spans="1:7">
@@ -45425,10 +45425,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45437,10 +45437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45448,10 +45448,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45460,10 +45460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">
@@ -49220,10 +49220,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49232,10 +49232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">
@@ -49243,10 +49243,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1875" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1875" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1875" s="1">
         <x:v>0</x:v>
@@ -49255,10 +49255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1875" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1875" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1876" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -21873,10 +21873,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -21885,10 +21885,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -21896,10 +21896,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21908,10 +21908,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -30199,10 +30199,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1047" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1047" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1047" s="1">
         <x:v>0</x:v>
@@ -30211,10 +30211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1047" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1048" spans="1:7">
@@ -30222,10 +30222,10 @@
         <x:v>1093</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30234,10 +30234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -42941,10 +42941,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1601" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1601" s="1">
         <x:v>0</x:v>
@@ -42953,10 +42953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1601" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1601" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1602" spans="1:7">
@@ -42964,10 +42964,10 @@
         <x:v>1638</x:v>
       </x:c>
       <x:c r="B1602" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C1602" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1602" s="1">
         <x:v>0</x:v>
@@ -42976,10 +42976,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1602" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1602" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1603" spans="1:7">
@@ -43723,10 +43723,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1635" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1635" s="1">
         <x:v>0</x:v>
@@ -43735,10 +43735,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1635" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1635" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1636" spans="1:7">
@@ -43746,10 +43746,10 @@
         <x:v>1671</x:v>
       </x:c>
       <x:c r="B1636" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1636" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1636" s="1">
         <x:v>0</x:v>
@@ -43758,10 +43758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1636" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1636" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1637" spans="1:7">
@@ -44137,10 +44137,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44149,10 +44149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -44160,10 +44160,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1654" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1654" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1654" s="1">
         <x:v>0</x:v>
@@ -44172,10 +44172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1654" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1654" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1655" spans="1:7">
@@ -45425,10 +45425,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1709" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1709" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1709" s="1">
         <x:v>0</x:v>
@@ -45437,10 +45437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1709" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1710" spans="1:7">
@@ -45448,10 +45448,10 @@
         <x:v>1743</x:v>
       </x:c>
       <x:c r="B1710" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1710" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1710" s="1">
         <x:v>0</x:v>
@@ -45460,10 +45460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1710" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1710" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1711" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -45770,10 +45770,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45782,10 +45782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45793,10 +45793,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45805,10 +45805,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -49220,10 +49220,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1874" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1874" s="1">
         <x:v>0</x:v>
@@ -49232,10 +49232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1874" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1874" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1875" spans="1:7">
@@ -49243,10 +49243,10 @@
         <x:v>1903</x:v>
       </x:c>
       <x:c r="B1875" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1875" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1875" s="1">
         <x:v>0</x:v>
@@ -49255,10 +49255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1875" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1875" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1876" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8510,10 +8510,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8522,10 +8522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8533,10 +8533,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8545,10 +8545,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -9614,10 +9614,10 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C152" s="1">
-        <x:v>34000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D152" s="1">
         <x:v>0</x:v>
@@ -9626,10 +9626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>52400</x:v>
+        <x:v>10854</x:v>
       </x:c>
       <x:c r="G152" s="1">
-        <x:v>86400</x:v>
+        <x:v>10854</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
@@ -9637,10 +9637,10 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="B153" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C153" s="1">
-        <x:v>0</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D153" s="1">
         <x:v>0</x:v>
@@ -9649,10 +9649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>10854</x:v>
+        <x:v>52400</x:v>
       </x:c>
       <x:c r="G153" s="1">
-        <x:v>10854</x:v>
+        <x:v>86400</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:7">
@@ -16974,10 +16974,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D472" s="1">
         <x:v>0</x:v>
@@ -16986,10 +16986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -16997,10 +16997,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17009,10 +17009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -32315,10 +32315,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1139" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1139" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1139" s="1">
         <x:v>0</x:v>
@@ -32327,10 +32327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1139" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1139" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1140" spans="1:7">
@@ -32338,10 +32338,10 @@
         <x:v>1183</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32350,10 +32350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -44137,10 +44137,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1653" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1653" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1653" s="1">
         <x:v>0</x:v>
@@ -44149,10 +44149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1653" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1653" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1654" spans="1:7">
@@ -44160,10 +44160,10 @@
         <x:v>1688</x:v>
       </x:c>
       <x:c r="B1654" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1654" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1654" s="1">
         <x:v>0</x:v>
@@ -44172,10 +44172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1654" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1654" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1655" spans="1:7">
@@ -45586,10 +45586,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1716" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1716" s="1">
         <x:v>0</x:v>
@@ -45598,10 +45598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1716" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1716" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1717" spans="1:7">
@@ -45609,10 +45609,10 @@
         <x:v>1749</x:v>
       </x:c>
       <x:c r="B1717" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1717" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1717" s="1">
         <x:v>0</x:v>
@@ -45621,10 +45621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1717" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1717" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1718" spans="1:7">
@@ -45770,10 +45770,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45782,10 +45782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45793,10 +45793,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45805,10 +45805,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -47173,10 +47173,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1785" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="D1785" s="1">
         <x:v>0</x:v>
@@ -47188,7 +47188,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1785" s="1">
-        <x:v>8500</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="1786" spans="1:7">
@@ -47196,10 +47196,10 @@
         <x:v>1816</x:v>
       </x:c>
       <x:c r="B1786" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1786" s="1">
         <x:v>0</x:v>
@@ -47211,7 +47211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1786" s="1">
-        <x:v>21500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1787" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17009,10 +17009,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17021,10 +17021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -17032,10 +17032,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C474" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D474" s="1">
         <x:v>0</x:v>
@@ -17044,10 +17044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F474" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -30234,10 +30234,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30246,10 +30246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -30257,10 +30257,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1049" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1049" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1049" s="1">
         <x:v>0</x:v>
@@ -30269,10 +30269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1049" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1049" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1050" spans="1:7">
@@ -37433,10 +37433,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1361" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1361" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1361" s="1">
         <x:v>0</x:v>
@@ -37445,10 +37445,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1361" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1361" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1362" spans="1:7">
@@ -37456,10 +37456,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1362" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1362" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1362" s="1">
         <x:v>0</x:v>
@@ -37468,10 +37468,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1362" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1362" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1363" spans="1:7">
@@ -40676,10 +40676,10 @@
         <x:v>1542</x:v>
       </x:c>
       <x:c r="B1502" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1502" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1502" s="1">
         <x:v>0</x:v>
@@ -40688,10 +40688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1502" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1502" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1503" spans="1:7">
@@ -40699,10 +40699,10 @@
         <x:v>1542</x:v>
       </x:c>
       <x:c r="B1503" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1503" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1503" s="1">
         <x:v>0</x:v>
@@ -40711,10 +40711,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1503" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1503" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1504" spans="1:7">
@@ -45483,10 +45483,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45495,10 +45495,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -45506,10 +45506,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45518,10 +45518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45644,10 +45644,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45656,10 +45656,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45667,10 +45667,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45679,10 +45679,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17009,10 +17009,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17021,10 +17021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -17032,10 +17032,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C474" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D474" s="1">
         <x:v>0</x:v>
@@ -17044,10 +17044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F474" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -30234,10 +30234,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30246,10 +30246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -30257,10 +30257,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1049" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1049" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1049" s="1">
         <x:v>0</x:v>
@@ -30269,10 +30269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1049" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1049" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1050" spans="1:7">
@@ -35616,10 +35616,10 @@
         <x:v>1324</x:v>
       </x:c>
       <x:c r="B1282" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1282" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1282" s="1">
         <x:v>0</x:v>
@@ -35628,10 +35628,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1282" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1282" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1283" spans="1:7">
@@ -35639,10 +35639,10 @@
         <x:v>1324</x:v>
       </x:c>
       <x:c r="B1283" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1283" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1283" s="1">
         <x:v>0</x:v>
@@ -35651,10 +35651,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1283" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1283" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1284" spans="1:7">
@@ -37433,10 +37433,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1361" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1361" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1361" s="1">
         <x:v>0</x:v>
@@ -37445,10 +37445,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1361" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1361" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1362" spans="1:7">
@@ -37456,10 +37456,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1362" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1362" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1362" s="1">
         <x:v>0</x:v>
@@ -37468,10 +37468,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1362" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1362" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1363" spans="1:7">
@@ -44195,10 +44195,10 @@
         <x:v>1690</x:v>
       </x:c>
       <x:c r="B1655" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1655" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1655" s="1">
         <x:v>0</x:v>
@@ -44207,10 +44207,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1655" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1655" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1656" spans="1:7">
@@ -44218,10 +44218,10 @@
         <x:v>1690</x:v>
       </x:c>
       <x:c r="B1656" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1656" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1656" s="1">
         <x:v>0</x:v>
@@ -44230,10 +44230,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1656" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1656" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1657" spans="1:7">
@@ -45483,10 +45483,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1711" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C1711" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1711" s="1">
         <x:v>0</x:v>
@@ -45495,10 +45495,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1711" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1711" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1712" spans="1:7">
@@ -45506,10 +45506,10 @@
         <x:v>1745</x:v>
       </x:c>
       <x:c r="B1712" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1712" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1712" s="1">
         <x:v>0</x:v>
@@ -45518,10 +45518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1712" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1712" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1713" spans="1:7">
@@ -45644,10 +45644,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45656,10 +45656,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45667,10 +45667,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45679,10 +45679,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30234,10 +30234,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30246,10 +30246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -30257,10 +30257,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1049" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1049" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1049" s="1">
         <x:v>0</x:v>
@@ -30269,10 +30269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1049" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1049" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1050" spans="1:7">
@@ -35616,10 +35616,10 @@
         <x:v>1324</x:v>
       </x:c>
       <x:c r="B1282" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1282" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1282" s="1">
         <x:v>0</x:v>
@@ -35628,10 +35628,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1282" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1282" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1283" spans="1:7">
@@ -35639,10 +35639,10 @@
         <x:v>1324</x:v>
       </x:c>
       <x:c r="B1283" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1283" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1283" s="1">
         <x:v>0</x:v>
@@ -35651,10 +35651,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1283" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1283" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1284" spans="1:7">
@@ -37433,10 +37433,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1361" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1361" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1361" s="1">
         <x:v>0</x:v>
@@ -37445,10 +37445,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1361" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1361" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1362" spans="1:7">
@@ -37456,10 +37456,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1362" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1362" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1362" s="1">
         <x:v>0</x:v>
@@ -37468,10 +37468,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1362" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1362" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1363" spans="1:7">
@@ -40676,10 +40676,10 @@
         <x:v>1542</x:v>
       </x:c>
       <x:c r="B1502" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1502" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1502" s="1">
         <x:v>0</x:v>
@@ -40688,10 +40688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1502" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1502" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1503" spans="1:7">
@@ -40699,10 +40699,10 @@
         <x:v>1542</x:v>
       </x:c>
       <x:c r="B1503" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1503" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1503" s="1">
         <x:v>0</x:v>
@@ -40711,10 +40711,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1503" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1503" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1504" spans="1:7">
@@ -44195,10 +44195,10 @@
         <x:v>1690</x:v>
       </x:c>
       <x:c r="B1655" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1655" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1655" s="1">
         <x:v>0</x:v>
@@ -44207,10 +44207,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1655" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1655" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1656" spans="1:7">
@@ -44218,10 +44218,10 @@
         <x:v>1690</x:v>
       </x:c>
       <x:c r="B1656" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1656" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1656" s="1">
         <x:v>0</x:v>
@@ -44230,10 +44230,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1656" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1656" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1657" spans="1:7">
@@ -45828,10 +45828,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -45840,10 +45840,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -45851,10 +45851,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45863,10 +45863,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1727" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -49324,10 +49324,10 @@
         <x:v>1907</x:v>
       </x:c>
       <x:c r="B1878" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1878" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1878" s="1">
         <x:v>0</x:v>
@@ -49336,10 +49336,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1878" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1878" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1879" spans="1:7">
@@ -49347,10 +49347,10 @@
         <x:v>1907</x:v>
       </x:c>
       <x:c r="B1879" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1879" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1879" s="1">
         <x:v>0</x:v>
@@ -49359,10 +49359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1879" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1879" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1880" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8522,10 +8522,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8534,10 +8534,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8545,10 +8545,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8557,10 +8557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -17009,10 +17009,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -17021,10 +17021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -17032,10 +17032,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C474" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D474" s="1">
         <x:v>0</x:v>
@@ -17044,10 +17044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F474" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -21908,10 +21908,10 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21920,10 +21920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -21931,10 +21931,10 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D687" s="1">
         <x:v>0</x:v>
@@ -21943,10 +21943,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -30234,10 +30234,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1048" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C1048" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1048" s="1">
         <x:v>0</x:v>
@@ -30246,10 +30246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1048" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1049" spans="1:7">
@@ -30257,10 +30257,10 @@
         <x:v>1094</x:v>
       </x:c>
       <x:c r="B1049" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1049" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1049" s="1">
         <x:v>0</x:v>
@@ -30269,10 +30269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1049" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1049" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1050" spans="1:7">
@@ -32350,10 +32350,10 @@
         <x:v>1184</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32362,10 +32362,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -32373,10 +32373,10 @@
         <x:v>1184</x:v>
       </x:c>
       <x:c r="B1141" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1141" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1141" s="1">
         <x:v>0</x:v>
@@ -32385,10 +32385,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1141" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1141" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1142" spans="1:7">
@@ -37433,10 +37433,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1361" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C1361" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1361" s="1">
         <x:v>0</x:v>
@@ -37445,10 +37445,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1361" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1361" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1362" spans="1:7">
@@ -37456,10 +37456,10 @@
         <x:v>1401</x:v>
       </x:c>
       <x:c r="B1362" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1362" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1362" s="1">
         <x:v>0</x:v>
@@ -37468,10 +37468,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1362" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1362" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1363" spans="1:7">
@@ -40676,10 +40676,10 @@
         <x:v>1542</x:v>
       </x:c>
       <x:c r="B1502" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1502" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1502" s="1">
         <x:v>0</x:v>
@@ -40688,10 +40688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1502" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1502" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1503" spans="1:7">
@@ -40699,10 +40699,10 @@
         <x:v>1542</x:v>
       </x:c>
       <x:c r="B1503" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C1503" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1503" s="1">
         <x:v>0</x:v>
@@ -40711,10 +40711,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1503" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1503" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1504" spans="1:7">
@@ -43781,10 +43781,10 @@
         <x:v>1673</x:v>
       </x:c>
       <x:c r="B1637" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1637" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1637" s="1">
         <x:v>0</x:v>
@@ -43793,10 +43793,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1637" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1637" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1638" spans="1:7">
@@ -43804,10 +43804,10 @@
         <x:v>1673</x:v>
       </x:c>
       <x:c r="B1638" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C1638" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1638" s="1">
         <x:v>0</x:v>
@@ -43816,10 +43816,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1638" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1638" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1639" spans="1:7">
@@ -45644,10 +45644,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45656,10 +45656,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45667,10 +45667,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45679,10 +45679,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -47254,10 +47254,10 @@
         <x:v>1819</x:v>
       </x:c>
       <x:c r="B1788" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1788" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1788" s="1">
         <x:v>0</x:v>
@@ -47269,7 +47269,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1788" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1789" spans="1:7">
@@ -47277,10 +47277,10 @@
         <x:v>1819</x:v>
       </x:c>
       <x:c r="B1789" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1789" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1789" s="1">
         <x:v>0</x:v>
@@ -47292,7 +47292,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1789" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1790" spans="1:7">
@@ -49324,10 +49324,10 @@
         <x:v>1907</x:v>
       </x:c>
       <x:c r="B1878" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1878" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1878" s="1">
         <x:v>0</x:v>
@@ -49336,10 +49336,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1878" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1878" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1879" spans="1:7">
@@ -49347,10 +49347,10 @@
         <x:v>1907</x:v>
       </x:c>
       <x:c r="B1879" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1879" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1879" s="1">
         <x:v>0</x:v>
@@ -49359,10 +49359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1879" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1879" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1880" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32350,10 +32350,10 @@
         <x:v>1184</x:v>
       </x:c>
       <x:c r="B1140" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C1140" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1140" s="1">
         <x:v>0</x:v>
@@ -32362,10 +32362,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1140" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1141" spans="1:7">
@@ -32373,10 +32373,10 @@
         <x:v>1184</x:v>
       </x:c>
       <x:c r="B1141" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1141" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1141" s="1">
         <x:v>0</x:v>
@@ -32385,10 +32385,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1141" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1141" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1142" spans="1:7">
@@ -35616,10 +35616,10 @@
         <x:v>1324</x:v>
       </x:c>
       <x:c r="B1282" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1282" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1282" s="1">
         <x:v>0</x:v>
@@ -35628,10 +35628,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1282" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1282" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1283" spans="1:7">
@@ -35639,10 +35639,10 @@
         <x:v>1324</x:v>
       </x:c>
       <x:c r="B1283" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1283" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1283" s="1">
         <x:v>0</x:v>
@@ -35651,10 +35651,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1283" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1283" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1284" spans="1:7">
@@ -45644,10 +45644,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45656,10 +45656,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45667,10 +45667,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45679,10 +45679,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8522,10 +8522,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -8534,10 +8534,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -8545,10 +8545,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8557,10 +8557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -19010,7 +19010,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>0</x:v>
@@ -19022,10 +19022,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -19033,7 +19033,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C561" s="1">
         <x:v>0</x:v>
@@ -19045,10 +19045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -21908,10 +21908,10 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -21920,10 +21920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -21931,10 +21931,10 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D687" s="1">
         <x:v>0</x:v>
@@ -21943,10 +21943,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -27842,10 +27842,10 @@
         <x:v>991</x:v>
       </x:c>
       <x:c r="B944" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C944" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D944" s="1">
         <x:v>0</x:v>
@@ -27854,10 +27854,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F944" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G944" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="945" spans="1:7">
@@ -27865,10 +27865,10 @@
         <x:v>991</x:v>
       </x:c>
       <x:c r="B945" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C945" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D945" s="1">
         <x:v>0</x:v>
@@ -27877,10 +27877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F945" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G945" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="946" spans="1:7">
@@ -45644,10 +45644,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1718" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1718" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1718" s="1">
         <x:v>0</x:v>
@@ -45656,10 +45656,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1718" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1718" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1719" spans="1:7">
@@ -45667,10 +45667,10 @@
         <x:v>1751</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45679,10 +45679,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -47254,10 +47254,10 @@
         <x:v>1819</x:v>
       </x:c>
       <x:c r="B1788" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1788" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1788" s="1">
         <x:v>0</x:v>
@@ -47269,7 +47269,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1788" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1789" spans="1:7">
@@ -47277,10 +47277,10 @@
         <x:v>1819</x:v>
       </x:c>
       <x:c r="B1789" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1789" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1789" s="1">
         <x:v>0</x:v>
@@ -47292,7 +47292,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1789" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1790" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -27291,10 +27291,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B919" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C919" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D919" s="1">
         <x:v>0</x:v>
@@ -27303,10 +27303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F919" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G919" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:7">
@@ -27314,10 +27314,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27326,10 +27326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -40861,10 +40861,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1509" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1509" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1509" s="1">
         <x:v>0</x:v>
@@ -40873,10 +40873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1509" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1509" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1510" spans="1:7">
@@ -40884,10 +40884,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1510" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1510" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1510" s="1">
         <x:v>0</x:v>
@@ -40896,10 +40896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1510" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1510" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1511" spans="1:7">
@@ -43966,10 +43966,10 @@
         <x:v>1680</x:v>
       </x:c>
       <x:c r="B1644" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1644" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1644" s="1">
         <x:v>0</x:v>
@@ -43978,10 +43978,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1644" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1644" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1645" spans="1:7">
@@ -43989,10 +43989,10 @@
         <x:v>1680</x:v>
       </x:c>
       <x:c r="B1645" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1645" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1645" s="1">
         <x:v>0</x:v>
@@ -44001,10 +44001,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1645" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1645" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1646" spans="1:7">
@@ -47462,10 +47462,10 @@
         <x:v>1827</x:v>
       </x:c>
       <x:c r="B1796" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1796" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1796" s="1">
         <x:v>0</x:v>
@@ -47477,7 +47477,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1796" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1797" spans="1:7">
@@ -47485,10 +47485,10 @@
         <x:v>1827</x:v>
       </x:c>
       <x:c r="B1797" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1797" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1797" s="1">
         <x:v>0</x:v>
@@ -47500,7 +47500,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1797" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1798" spans="1:7">
@@ -49532,10 +49532,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1886" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1886" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1886" s="1">
         <x:v>0</x:v>
@@ -49544,10 +49544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1886" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1886" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1887" spans="1:7">
@@ -49555,10 +49555,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -49567,10 +49567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -27291,10 +27291,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B919" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C919" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D919" s="1">
         <x:v>0</x:v>
@@ -27303,10 +27303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F919" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G919" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:7">
@@ -27314,10 +27314,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27326,10 +27326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -30396,10 +30396,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30408,10 +30408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30419,10 +30419,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30431,10 +30431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -37618,10 +37618,10 @@
         <x:v>1408</x:v>
       </x:c>
       <x:c r="B1368" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1368" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1368" s="1">
         <x:v>0</x:v>
@@ -37630,10 +37630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1368" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1368" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1369" spans="1:7">
@@ -37641,10 +37641,10 @@
         <x:v>1408</x:v>
       </x:c>
       <x:c r="B1369" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1369" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1369" s="1">
         <x:v>0</x:v>
@@ -37653,10 +37653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1369" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1369" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1370" spans="1:7">
@@ -40861,10 +40861,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1509" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1509" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1509" s="1">
         <x:v>0</x:v>
@@ -40873,10 +40873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1509" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1509" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1510" spans="1:7">
@@ -40884,10 +40884,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1510" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1510" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1510" s="1">
         <x:v>0</x:v>
@@ -40896,10 +40896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1510" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1510" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1511" spans="1:7">
@@ -45691,10 +45691,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45703,10 +45703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -45714,10 +45714,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45726,10 +45726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -49532,10 +49532,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1886" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1886" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1886" s="1">
         <x:v>0</x:v>
@@ -49544,10 +49544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1886" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1886" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1887" spans="1:7">
@@ -49555,10 +49555,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -49567,10 +49567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17125,10 +17125,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17137,10 +17137,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17148,10 +17148,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17160,10 +17160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -27291,10 +27291,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B919" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C919" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D919" s="1">
         <x:v>0</x:v>
@@ -27303,10 +27303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F919" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G919" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:7">
@@ -27314,10 +27314,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27326,10 +27326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -30396,10 +30396,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30408,10 +30408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30419,10 +30419,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30431,10 +30431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -35801,10 +35801,10 @@
         <x:v>1331</x:v>
       </x:c>
       <x:c r="B1289" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1289" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1289" s="1">
         <x:v>0</x:v>
@@ -35813,10 +35813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1289" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1289" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1290" spans="1:7">
@@ -35824,10 +35824,10 @@
         <x:v>1331</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35836,10 +35836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -37618,10 +37618,10 @@
         <x:v>1408</x:v>
       </x:c>
       <x:c r="B1368" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1368" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1368" s="1">
         <x:v>0</x:v>
@@ -37630,10 +37630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1368" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1368" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1369" spans="1:7">
@@ -37641,10 +37641,10 @@
         <x:v>1408</x:v>
       </x:c>
       <x:c r="B1369" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1369" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1369" s="1">
         <x:v>0</x:v>
@@ -37653,10 +37653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1369" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1369" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1370" spans="1:7">
@@ -40861,10 +40861,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1509" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1509" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1509" s="1">
         <x:v>0</x:v>
@@ -40873,10 +40873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1509" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1509" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1510" spans="1:7">
@@ -40884,10 +40884,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1510" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1510" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1510" s="1">
         <x:v>0</x:v>
@@ -40896,10 +40896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1510" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1510" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1511" spans="1:7">
@@ -43184,10 +43184,10 @@
         <x:v>1647</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -43196,10 +43196,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -43207,10 +43207,10 @@
         <x:v>1647</x:v>
       </x:c>
       <x:c r="B1611" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1611" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1611" s="1">
         <x:v>0</x:v>
@@ -43219,10 +43219,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1611" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1611" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1612" spans="1:7">
@@ -45691,10 +45691,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45703,10 +45703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -45714,10 +45714,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45726,10 +45726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -47462,10 +47462,10 @@
         <x:v>1827</x:v>
       </x:c>
       <x:c r="B1796" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1796" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1796" s="1">
         <x:v>0</x:v>
@@ -47477,7 +47477,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1796" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1797" spans="1:7">
@@ -47485,10 +47485,10 @@
         <x:v>1827</x:v>
       </x:c>
       <x:c r="B1797" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1797" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1797" s="1">
         <x:v>0</x:v>
@@ -47500,7 +47500,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1797" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1798" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8569,10 +8569,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8581,10 +8581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8592,10 +8592,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8604,10 +8604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17125,10 +17125,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17137,10 +17137,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17148,10 +17148,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17160,10 +17160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -22024,10 +22024,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22036,10 +22036,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22047,10 +22047,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22059,10 +22059,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -35801,10 +35801,10 @@
         <x:v>1331</x:v>
       </x:c>
       <x:c r="B1289" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1289" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1289" s="1">
         <x:v>0</x:v>
@@ -35813,10 +35813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1289" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1289" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1290" spans="1:7">
@@ -35824,10 +35824,10 @@
         <x:v>1331</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35836,10 +35836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -45852,10 +45852,10 @@
         <x:v>1759</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -45864,10 +45864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -45875,10 +45875,10 @@
         <x:v>1759</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45887,10 +45887,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1727" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -47462,10 +47462,10 @@
         <x:v>1827</x:v>
       </x:c>
       <x:c r="B1796" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1796" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1796" s="1">
         <x:v>0</x:v>
@@ -47477,7 +47477,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1796" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1797" spans="1:7">
@@ -47485,10 +47485,10 @@
         <x:v>1827</x:v>
       </x:c>
       <x:c r="B1797" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1797" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1797" s="1">
         <x:v>0</x:v>
@@ -47500,7 +47500,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1797" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1798" spans="1:7">
@@ -49532,10 +49532,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1886" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1886" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1886" s="1">
         <x:v>0</x:v>
@@ -49544,10 +49544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1886" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1886" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1887" spans="1:7">
@@ -49555,10 +49555,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -49567,10 +49567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8569,10 +8569,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8581,10 +8581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8592,10 +8592,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8604,10 +8604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22024,10 +22024,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22036,10 +22036,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22047,10 +22047,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22059,10 +22059,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -30396,10 +30396,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30408,10 +30408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30419,10 +30419,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30431,10 +30431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -32535,10 +32535,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32547,10 +32547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32558,10 +32558,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32570,10 +32570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -43184,10 +43184,10 @@
         <x:v>1647</x:v>
       </x:c>
       <x:c r="B1610" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1610" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1610" s="1">
         <x:v>0</x:v>
@@ -43196,10 +43196,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1610" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1610" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1611" spans="1:7">
@@ -43207,10 +43207,10 @@
         <x:v>1647</x:v>
       </x:c>
       <x:c r="B1611" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1611" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1611" s="1">
         <x:v>0</x:v>
@@ -43219,10 +43219,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1611" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1611" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1612" spans="1:7">
@@ -45691,10 +45691,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45703,10 +45703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -45714,10 +45714,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45726,10 +45726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -45852,10 +45852,10 @@
         <x:v>1759</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -45864,10 +45864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -45875,10 +45875,10 @@
         <x:v>1759</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45887,10 +45887,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1727" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -49532,10 +49532,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1886" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1886" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1886" s="1">
         <x:v>0</x:v>
@@ -49544,10 +49544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1886" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1886" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1887" spans="1:7">
@@ -49555,10 +49555,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -49567,10 +49567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8569,10 +8569,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8581,10 +8581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8592,10 +8592,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8604,10 +8604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -25520,10 +25520,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C842" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D842" s="1">
         <x:v>0</x:v>
@@ -25532,10 +25532,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -25543,10 +25543,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25555,10 +25555,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -30396,10 +30396,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30408,10 +30408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30419,10 +30419,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30431,10 +30431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -32535,10 +32535,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32547,10 +32547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32558,10 +32558,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32570,10 +32570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -40861,10 +40861,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1509" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1509" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1509" s="1">
         <x:v>0</x:v>
@@ -40873,10 +40873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1509" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1509" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1510" spans="1:7">
@@ -40884,10 +40884,10 @@
         <x:v>1549</x:v>
       </x:c>
       <x:c r="B1510" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1510" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1510" s="1">
         <x:v>0</x:v>
@@ -40896,10 +40896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1510" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1510" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1511" spans="1:7">
@@ -43966,10 +43966,10 @@
         <x:v>1680</x:v>
       </x:c>
       <x:c r="B1644" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1644" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1644" s="1">
         <x:v>0</x:v>
@@ -43978,10 +43978,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1644" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1644" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1645" spans="1:7">
@@ -43989,10 +43989,10 @@
         <x:v>1680</x:v>
       </x:c>
       <x:c r="B1645" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1645" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1645" s="1">
         <x:v>0</x:v>
@@ -44001,10 +44001,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1645" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1645" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1646" spans="1:7">
@@ -44403,10 +44403,10 @@
         <x:v>1698</x:v>
       </x:c>
       <x:c r="B1663" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1663" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1663" s="1">
         <x:v>0</x:v>
@@ -44415,10 +44415,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1663" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1663" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1664" spans="1:7">
@@ -44426,10 +44426,10 @@
         <x:v>1698</x:v>
       </x:c>
       <x:c r="B1664" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1664" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1664" s="1">
         <x:v>0</x:v>
@@ -44438,10 +44438,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1664" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1664" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1665" spans="1:7">
@@ -45691,10 +45691,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1719" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1719" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1719" s="1">
         <x:v>0</x:v>
@@ -45703,10 +45703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1719" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1719" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1720" spans="1:7">
@@ -45714,10 +45714,10 @@
         <x:v>1753</x:v>
       </x:c>
       <x:c r="B1720" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1720" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1720" s="1">
         <x:v>0</x:v>
@@ -45726,10 +45726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1720" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1720" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1721" spans="1:7">
@@ -45852,10 +45852,10 @@
         <x:v>1759</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -45864,10 +45864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -45875,10 +45875,10 @@
         <x:v>1759</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -45887,10 +45887,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1727" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -49532,10 +49532,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1886" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1886" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1886" s="1">
         <x:v>0</x:v>
@@ -49544,10 +49544,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1886" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1886" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1887" spans="1:7">
@@ -49555,10 +49555,10 @@
         <x:v>1915</x:v>
       </x:c>
       <x:c r="B1887" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1887" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1887" s="1">
         <x:v>0</x:v>
@@ -49567,10 +49567,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1887" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1887" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1888" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -22033,10 +22033,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22045,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22056,10 +22056,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22068,10 +22068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -30405,10 +30405,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30417,10 +30417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30428,10 +30428,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -37650,10 +37650,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1369" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1369" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1369" s="1">
         <x:v>0</x:v>
@@ -37662,10 +37662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1369" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1369" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1370" spans="1:7">
@@ -37673,10 +37673,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37685,10 +37685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -45769,10 +45769,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45781,10 +45781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -45792,10 +45792,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45804,10 +45804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8578,10 +8578,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8601,10 +8601,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8613,10 +8613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17134,10 +17134,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17146,10 +17146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17157,10 +17157,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17169,10 +17169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -22033,10 +22033,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22045,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22056,10 +22056,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22068,10 +22068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -30405,10 +30405,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30417,10 +30417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30428,10 +30428,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -37650,10 +37650,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1369" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1369" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1369" s="1">
         <x:v>0</x:v>
@@ -37662,10 +37662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1369" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1369" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1370" spans="1:7">
@@ -37673,10 +37673,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37685,10 +37685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45769,10 +45769,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45781,10 +45781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -45792,10 +45792,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45804,10 +45804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -46114,10 +46114,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1737" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1737" s="1">
         <x:v>0</x:v>
@@ -46126,10 +46126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1737" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1738" spans="1:7">
@@ -46137,10 +46137,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1738" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1738" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1738" s="1">
         <x:v>0</x:v>
@@ -46149,10 +46149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1738" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1738" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1739" spans="1:7">
@@ -47540,10 +47540,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1799" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1799" s="1">
         <x:v>0</x:v>
@@ -47555,7 +47555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1800" spans="1:7">
@@ -47563,10 +47563,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1800" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1800" s="1">
         <x:v>0</x:v>
@@ -47578,7 +47578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1801" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8578,10 +8578,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8601,10 +8601,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8613,10 +8613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22033,10 +22033,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22045,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22056,10 +22056,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22068,10 +22068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17134,10 +17134,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17146,10 +17146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17157,10 +17157,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17169,10 +17169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -22033,10 +22033,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22045,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22056,10 +22056,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22068,10 +22068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -27300,10 +27300,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B919" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C919" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D919" s="1">
         <x:v>0</x:v>
@@ -27312,10 +27312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F919" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G919" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:7">
@@ -27323,10 +27323,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27335,10 +27335,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -46114,10 +46114,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1737" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1737" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1737" s="1">
         <x:v>0</x:v>
@@ -46126,10 +46126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1737" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1737" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1738" spans="1:7">
@@ -46137,10 +46137,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1738" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1738" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1738" s="1">
         <x:v>0</x:v>
@@ -46149,10 +46149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1738" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1738" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1739" spans="1:7">
@@ -47540,10 +47540,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1799" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1799" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1799" s="1">
         <x:v>0</x:v>
@@ -47555,7 +47555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1799" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1800" spans="1:7">
@@ -47563,10 +47563,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1800" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1800" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1800" s="1">
         <x:v>0</x:v>
@@ -47578,7 +47578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1800" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1801" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -22033,10 +22033,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22045,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22056,10 +22056,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22068,10 +22068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -27300,10 +27300,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B919" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C919" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D919" s="1">
         <x:v>0</x:v>
@@ -27312,10 +27312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F919" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G919" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:7">
@@ -27323,10 +27323,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27335,10 +27335,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -47540,10 +47540,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1799" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1799" s="1">
         <x:v>0</x:v>
@@ -47555,7 +47555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1800" spans="1:7">
@@ -47563,10 +47563,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1800" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1800" s="1">
         <x:v>0</x:v>
@@ -47578,7 +47578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1801" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -31003,10 +31003,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1080" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1080" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1080" s="1">
         <x:v>0</x:v>
@@ -31015,10 +31015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1080" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1080" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1081" spans="1:7">
@@ -31026,10 +31026,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31038,10 +31038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -42239,10 +42239,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1568" s="1">
-        <x:v>208240</x:v>
+        <x:v>209275</x:v>
       </x:c>
       <x:c r="G1568" s="1">
-        <x:v>215240</x:v>
+        <x:v>216275</x:v>
       </x:c>
     </x:row>
     <x:row r="1569" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -46114,10 +46114,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1737" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1737" s="1">
         <x:v>0</x:v>
@@ -46126,10 +46126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1737" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1738" spans="1:7">
@@ -46137,10 +46137,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1738" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1738" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1738" s="1">
         <x:v>0</x:v>
@@ -46149,10 +46149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1738" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1738" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1739" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8578,10 +8578,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8601,10 +8601,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8613,10 +8613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17134,10 +17134,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17146,10 +17146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17157,10 +17157,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17169,10 +17169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -25529,10 +25529,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C842" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D842" s="1">
         <x:v>0</x:v>
@@ -25541,10 +25541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -25552,10 +25552,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25564,10 +25564,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -31003,10 +31003,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1080" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1080" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1080" s="1">
         <x:v>0</x:v>
@@ -31015,10 +31015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1080" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1080" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1081" spans="1:7">
@@ -31026,10 +31026,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31038,10 +31038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -44481,10 +44481,10 @@
         <x:v>1701</x:v>
       </x:c>
       <x:c r="B1666" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1666" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1666" s="1">
         <x:v>0</x:v>
@@ -44493,10 +44493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1666" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1666" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1667" spans="1:7">
@@ -44504,10 +44504,10 @@
         <x:v>1701</x:v>
       </x:c>
       <x:c r="B1667" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1667" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1667" s="1">
         <x:v>0</x:v>
@@ -44516,10 +44516,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1667" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1667" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1668" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8578,10 +8578,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8601,10 +8601,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8613,10 +8613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -25529,10 +25529,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C842" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D842" s="1">
         <x:v>0</x:v>
@@ -25541,10 +25541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -25552,10 +25552,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25564,10 +25564,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8578,10 +8578,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8601,10 +8601,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8613,10 +8613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17134,10 +17134,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17146,10 +17146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17157,10 +17157,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17169,10 +17169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -19135,7 +19135,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C564" s="1">
         <x:v>0</x:v>
@@ -19147,10 +19147,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -19158,7 +19158,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19170,10 +19170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -25529,10 +25529,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C842" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D842" s="1">
         <x:v>0</x:v>
@@ -25541,10 +25541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -25552,10 +25552,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25564,10 +25564,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -27990,10 +27990,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B949" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C949" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D949" s="1">
         <x:v>0</x:v>
@@ -28002,10 +28002,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F949" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G949" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="950" spans="1:7">
@@ -28013,10 +28013,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B950" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C950" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D950" s="1">
         <x:v>0</x:v>
@@ -28025,10 +28025,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F950" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G950" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="951" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -46114,10 +46114,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1737" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1737" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1737" s="1">
         <x:v>0</x:v>
@@ -46126,10 +46126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1737" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1737" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1738" spans="1:7">
@@ -46137,10 +46137,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1738" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1738" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1738" s="1">
         <x:v>0</x:v>
@@ -46149,10 +46149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1738" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1738" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1739" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8578,10 +8578,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8601,10 +8601,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8613,10 +8613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17134,10 +17134,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17146,10 +17146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17157,10 +17157,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17169,10 +17169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -19135,7 +19135,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C564" s="1">
         <x:v>0</x:v>
@@ -19147,10 +19147,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -19158,7 +19158,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19170,10 +19170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -25529,10 +25529,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C842" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D842" s="1">
         <x:v>0</x:v>
@@ -25541,10 +25541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -25552,10 +25552,10 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25564,10 +25564,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -27990,10 +27990,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B949" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C949" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D949" s="1">
         <x:v>0</x:v>
@@ -28002,10 +28002,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F949" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G949" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="950" spans="1:7">
@@ -28013,10 +28013,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B950" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C950" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D950" s="1">
         <x:v>0</x:v>
@@ -28025,10 +28025,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F950" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G950" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="951" spans="1:7">
@@ -32544,10 +32544,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32556,10 +32556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32567,10 +32567,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32579,10 +32579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -37650,10 +37650,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1369" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1369" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1369" s="1">
         <x:v>0</x:v>
@@ -37662,10 +37662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1369" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1369" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1370" spans="1:7">
@@ -37673,10 +37673,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37685,10 +37685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44481,10 +44481,10 @@
         <x:v>1701</x:v>
       </x:c>
       <x:c r="B1666" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1666" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1666" s="1">
         <x:v>0</x:v>
@@ -44493,10 +44493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1666" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1666" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1667" spans="1:7">
@@ -44504,10 +44504,10 @@
         <x:v>1701</x:v>
       </x:c>
       <x:c r="B1667" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1667" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1667" s="1">
         <x:v>0</x:v>
@@ -44516,10 +44516,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1667" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1667" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1668" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -47540,10 +47540,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1799" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1799" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1799" s="1">
         <x:v>0</x:v>
@@ -47555,7 +47555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1799" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1800" spans="1:7">
@@ -47563,10 +47563,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1800" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1800" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1800" s="1">
         <x:v>0</x:v>
@@ -47578,7 +47578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1800" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1801" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17134,10 +17134,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D477" s="1">
         <x:v>0</x:v>
@@ -17146,10 +17146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -17157,10 +17157,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17169,10 +17169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -32544,10 +32544,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32556,10 +32556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32567,10 +32567,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32579,10 +32579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -37650,10 +37650,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1369" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1369" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1369" s="1">
         <x:v>0</x:v>
@@ -37662,10 +37662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1369" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1369" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1370" spans="1:7">
@@ -37673,10 +37673,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37685,10 +37685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -46114,10 +46114,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1737" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1737" s="1">
         <x:v>0</x:v>
@@ -46126,10 +46126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1737" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1738" spans="1:7">
@@ -46137,10 +46137,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1738" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1738" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1738" s="1">
         <x:v>0</x:v>
@@ -46149,10 +46149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1738" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1738" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1739" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -22033,10 +22033,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22045,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22056,10 +22056,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22068,10 +22068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -21208,7 +21208,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>3000</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D654" s="1">
         <x:v>0</x:v>
@@ -21220,7 +21220,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>3000</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -22033,10 +22033,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -22045,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -22056,10 +22056,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22068,10 +22068,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -29626,7 +29626,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C1020" s="1">
-        <x:v>158000</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="D1020" s="1">
         <x:v>0</x:v>
@@ -29638,7 +29638,7 @@
         <x:v>100191</x:v>
       </x:c>
       <x:c r="G1020" s="1">
-        <x:v>258191</x:v>
+        <x:v>260691</x:v>
       </x:c>
     </x:row>
     <x:row r="1021" spans="1:7">
@@ -30405,10 +30405,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30417,10 +30417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30428,10 +30428,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -32544,10 +32544,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32556,10 +32556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32567,10 +32567,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32579,10 +32579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -39861,7 +39861,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1465" s="1">
-        <x:v>5000</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="D1465" s="1">
         <x:v>0</x:v>
@@ -39873,7 +39873,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1465" s="1">
-        <x:v>5000</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="1466" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -45769,10 +45769,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45781,10 +45781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -45792,10 +45792,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45804,10 +45804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -47540,10 +47540,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1799" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1799" s="1">
         <x:v>0</x:v>
@@ -47555,7 +47555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1800" spans="1:7">
@@ -47563,10 +47563,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1800" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1800" s="1">
         <x:v>0</x:v>
@@ -47578,7 +47578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1801" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30405,10 +30405,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30417,10 +30417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30428,10 +30428,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -32544,10 +32544,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32556,10 +32556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32567,10 +32567,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32579,10 +32579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -45769,10 +45769,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45781,10 +45781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -45792,10 +45792,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45804,10 +45804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30405,10 +30405,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30417,10 +30417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30428,10 +30428,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -32544,10 +32544,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32556,10 +32556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32567,10 +32567,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32579,10 +32579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -40939,10 +40939,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1512" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1512" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1512" s="1">
         <x:v>0</x:v>
@@ -40951,10 +40951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1512" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1512" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1513" spans="1:7">
@@ -40962,10 +40962,10 @@
         <x:v>1552</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40974,10 +40974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -43262,10 +43262,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1613" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1613" s="1">
         <x:v>0</x:v>
@@ -43274,10 +43274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1613" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1613" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1614" spans="1:7">
@@ -43285,10 +43285,10 @@
         <x:v>1650</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43297,10 +43297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -45769,10 +45769,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45781,10 +45781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -45792,10 +45792,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45804,10 +45804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -47540,10 +47540,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1799" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1799" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1799" s="1">
         <x:v>0</x:v>
@@ -47555,7 +47555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1799" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1800" spans="1:7">
@@ -47563,10 +47563,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1800" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1800" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1800" s="1">
         <x:v>0</x:v>
@@ -47578,7 +47578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1800" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1801" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -20285,10 +20285,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D614" s="1">
         <x:v>0</x:v>
@@ -20297,10 +20297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -20308,10 +20308,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -20320,10 +20320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -27990,10 +27990,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B949" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C949" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D949" s="1">
         <x:v>0</x:v>
@@ -28002,10 +28002,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F949" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G949" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="950" spans="1:7">
@@ -28013,10 +28013,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B950" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C950" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D950" s="1">
         <x:v>0</x:v>
@@ -28025,10 +28025,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F950" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G950" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="951" spans="1:7">
@@ -30405,10 +30405,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30417,10 +30417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30428,10 +30428,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -32544,10 +32544,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1147" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1147" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1147" s="1">
         <x:v>0</x:v>
@@ -32556,10 +32556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1147" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1148" spans="1:7">
@@ -32567,10 +32567,10 @@
         <x:v>1191</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32579,10 +32579,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -35189,22 +35189,22 @@
         <x:v>1305</x:v>
       </x:c>
       <x:c r="B1262" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C1262" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1262" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1262" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F1262" s="1">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D1262" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1262" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F1262" s="1">
-        <x:v>6400</x:v>
-      </x:c>
       <x:c r="G1262" s="1">
-        <x:v>11400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1263" spans="1:7">
@@ -35212,10 +35212,10 @@
         <x:v>1305</x:v>
       </x:c>
       <x:c r="B1263" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1263" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1263" s="1">
         <x:v>0</x:v>
@@ -35224,10 +35224,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1263" s="1">
-        <x:v>5000</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="G1263" s="1">
-        <x:v>5000</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="1264" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45769,10 +45769,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45781,10 +45781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -45792,10 +45792,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45804,10 +45804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -46114,10 +46114,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1737" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1737" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1737" s="1">
         <x:v>0</x:v>
@@ -46126,10 +46126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1737" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1737" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1738" spans="1:7">
@@ -46137,10 +46137,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1738" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1738" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1738" s="1">
         <x:v>0</x:v>
@@ -46149,10 +46149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1738" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1738" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1739" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -20285,10 +20285,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D614" s="1">
         <x:v>0</x:v>
@@ -20297,10 +20297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -20308,10 +20308,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -20320,10 +20320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -27300,10 +27300,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B919" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C919" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D919" s="1">
         <x:v>0</x:v>
@@ -27312,10 +27312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F919" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G919" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:7">
@@ -27323,10 +27323,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27335,10 +27335,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -27990,10 +27990,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B949" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C949" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D949" s="1">
         <x:v>0</x:v>
@@ -28002,10 +28002,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F949" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G949" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="950" spans="1:7">
@@ -28013,10 +28013,10 @@
         <x:v>996</x:v>
       </x:c>
       <x:c r="B950" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C950" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D950" s="1">
         <x:v>0</x:v>
@@ -28025,10 +28025,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F950" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G950" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="951" spans="1:7">
@@ -35189,10 +35189,10 @@
         <x:v>1305</x:v>
       </x:c>
       <x:c r="B1262" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1262" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1262" s="1">
         <x:v>0</x:v>
@@ -35201,10 +35201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1262" s="1">
-        <x:v>5000</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="G1262" s="1">
-        <x:v>5000</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="1263" spans="1:7">
@@ -35212,22 +35212,22 @@
         <x:v>1305</x:v>
       </x:c>
       <x:c r="B1263" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C1263" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1263" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1263" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F1263" s="1">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D1263" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1263" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F1263" s="1">
-        <x:v>6400</x:v>
-      </x:c>
       <x:c r="G1263" s="1">
-        <x:v>11400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1264" spans="1:7">
@@ -44044,10 +44044,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1647" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1647" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1647" s="1">
         <x:v>0</x:v>
@@ -44056,10 +44056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1647" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1647" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1648" spans="1:7">
@@ -44067,10 +44067,10 @@
         <x:v>1683</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44079,10 +44079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -47540,10 +47540,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1799" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1799" s="1">
         <x:v>0</x:v>
@@ -47555,7 +47555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1799" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1800" spans="1:7">
@@ -47563,10 +47563,10 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="B1800" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1800" s="1">
         <x:v>0</x:v>
@@ -47578,7 +47578,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1800" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1801" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -27300,10 +27300,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B919" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C919" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D919" s="1">
         <x:v>0</x:v>
@@ -27312,10 +27312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F919" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G919" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:7">
@@ -27323,10 +27323,10 @@
         <x:v>967</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27335,10 +27335,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -31003,10 +31003,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1080" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1080" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1080" s="1">
         <x:v>0</x:v>
@@ -31015,10 +31015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1080" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1080" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1081" spans="1:7">
@@ -31026,10 +31026,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31038,10 +31038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30405,10 +30405,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1054" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1054" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1054" s="1">
         <x:v>0</x:v>
@@ -30417,10 +30417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1054" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1054" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1055" spans="1:7">
@@ -30428,10 +30428,10 @@
         <x:v>1100</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30440,10 +30440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -31003,10 +31003,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1080" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1080" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1080" s="1">
         <x:v>0</x:v>
@@ -31015,10 +31015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1080" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1080" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1081" spans="1:7">
@@ -31026,10 +31026,10 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31038,10 +31038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -35833,10 +35833,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1290" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1290" s="1">
         <x:v>0</x:v>
@@ -35845,10 +35845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1290" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1290" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1291" spans="1:7">
@@ -35856,10 +35856,10 @@
         <x:v>1332</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35868,10 +35868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -37650,10 +37650,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1369" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1369" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1369" s="1">
         <x:v>0</x:v>
@@ -37662,10 +37662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1369" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1369" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1370" spans="1:7">
@@ -37673,10 +37673,10 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37685,10 +37685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -45769,10 +45769,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1722" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1722" s="1">
         <x:v>0</x:v>
@@ -45781,10 +45781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1722" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1722" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1723" spans="1:7">
@@ -45792,10 +45792,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45804,10 +45804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45930,10 +45930,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1729" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1729" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1729" s="1">
         <x:v>0</x:v>
@@ -45942,10 +45942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1729" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1729" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1730" spans="1:7">
@@ -45953,10 +45953,10 @@
         <x:v>1762</x:v>
       </x:c>
       <x:c r="B1730" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1730" s="1">
         <x:v>0</x:v>
@@ -45965,10 +45965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1730" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1730" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1731" spans="1:7">
@@ -46114,10 +46114,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1737" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1737" s="1">
         <x:v>0</x:v>
@@ -46126,10 +46126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1737" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1737" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1738" spans="1:7">
@@ -46137,10 +46137,10 @@
         <x:v>1769</x:v>
       </x:c>
       <x:c r="B1738" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1738" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1738" s="1">
         <x:v>0</x:v>
@@ -46149,10 +46149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1738" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1738" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1739" spans="1:7">
@@ -49610,10 +49610,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1889" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1889" s="1">
         <x:v>0</x:v>
@@ -49622,10 +49622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1889" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1889" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1890" spans="1:7">
@@ -49633,10 +49633,10 @@
         <x:v>1918</x:v>
       </x:c>
       <x:c r="B1890" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1890" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1890" s="1">
         <x:v>0</x:v>
@@ -49645,10 +49645,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1890" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1890" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1891" spans="1:7">
